--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="627">
   <si>
     <t xml:space="preserve">Site artifacts: mapping workbook</t>
   </si>
@@ -87,6 +87,9 @@
     <t xml:space="preserve">Keep it uncluttered: personal context supports the work quietly, it never crowds it.</t>
   </si>
   <si>
+    <t xml:space="preserve">Latest decisions: one quiet line in About ("Based in Austin · English, Italian, learning Portuguese"), with Jaylee and Helga as one small sprite each beside it, not in the orbit. No languages on the Travel map; no sports on films or trips.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sheets</t>
   </si>
   <si>
@@ -441,7 +444,7 @@
     <t xml:space="preserve">End-to-end design and construction of a facility combining office, automated distribution, clean pack, sterilization and additive manufacturing, as owner rep.</t>
   </si>
   <si>
-    <t xml:space="preserve">200K sq ft; budget &gt;$20M; major utilities, equipment integration, controls, life safety; next-phase expansion and capacity planning; lean / continuous improvement.</t>
+    <t xml:space="preserve">200K sq ft; budget &gt;$10M; major utilities, equipment integration, controls, life safety; next-phase expansion and capacity planning; lean / continuous improvement.</t>
   </si>
   <si>
     <t xml:space="preserve">Design-build delivery, commissioning, validation</t>
@@ -1443,13 +1446,13 @@
     <t xml:space="preserve">USA</t>
   </si>
   <si>
-    <t xml:space="preserve">Inferred</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPEI Chicago; AWC internship (2016)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify</t>
+    <t xml:space="preserve">Confirmed: before Lawrence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPEI Chicago</t>
   </si>
   <si>
     <t xml:space="preserve">Milan</t>
@@ -1461,7 +1464,7 @@
     <t xml:space="preserve">MAPEI Corp; OnlyChargeEV</t>
   </si>
   <si>
-    <t xml:space="preserve">Until the Austin move (April 2025); start year inferred</t>
+    <t xml:space="preserve">Confirmed; until the Austin move (April 2025)</t>
   </si>
   <si>
     <t xml:space="preserve">Enovis</t>
@@ -1752,9 +1755,27 @@
     <t xml:space="preserve">No more personality words. The five themes are enough; the projects, photos, travel, languages, sports, startup and apps prove them.</t>
   </si>
   <si>
+    <t xml:space="preserve">One quiet line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At most one line in About: "Based in Austin · English, Italian, learning Portuguese". Languages stay off the Travel map; sports stay off the films and trips.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your answer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaylee and Helga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Named, as one small sprite of each beside the quiet line in About (not in the orbit).</t>
+  </si>
+  <si>
     <t xml:space="preserve">not sure how to diplay all the about profle stuff don’t want to make everythign to busy also!!</t>
   </si>
   <si>
+    <t xml:space="preserve">→ Decided: the one quiet line and the dogs (rows 24–25). Everything else here is shown by the work itself, not listed.</t>
+  </si>
+  <si>
     <t xml:space="preserve">#</t>
   </si>
   <si>
@@ -1764,9 +1785,6 @@
     <t xml:space="preserve">Affects</t>
   </si>
   <si>
-    <t xml:space="preserve">Your answer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Your portfolio PDF is marked "confidential, intended solely for the recipient". Is it OK to show these projects (photos, renders, numbers) on a public site?</t>
   </si>
   <si>
@@ -1920,10 +1938,16 @@
     <t xml:space="preserve">P2–P5</t>
   </si>
   <si>
+    <t xml:space="preserve">Yes (and Wilmette before Lawrence)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Enovis budget: you changed it to &gt;$20M; your resume still says &gt;$10M.</t>
   </si>
   <si>
     <t xml:space="preserve">E1, resume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$10M is fine: reverted to &gt;$10M</t>
   </si>
 </sst>
 </file>
@@ -2174,7 +2198,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2312,6 +2336,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2712,42 +2740,47 @@
         <v>5</v>
       </c>
     </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2755,27 +2788,27 @@
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2783,12 +2816,12 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2796,12 +2829,12 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -2848,78 +2881,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O1" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q1" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -2946,217 +2979,217 @@
     </row>
     <row r="3" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K3" s="17"/>
       <c r="L3" s="18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M3" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N3" s="20"/>
       <c r="O3" s="20"/>
       <c r="P3" s="20"/>
       <c r="Q3" s="20"/>
       <c r="R3" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S3" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T3" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U3" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V3" s="21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="W3" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K4" s="17"/>
       <c r="L4" s="18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M4" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N4" s="20"/>
       <c r="O4" s="20"/>
       <c r="P4" s="20"/>
       <c r="Q4" s="20"/>
       <c r="R4" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S4" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T4" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U4" s="17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="V4" s="21"/>
       <c r="W4" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
       <c r="L5" s="18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N5" s="20"/>
       <c r="O5" s="20"/>
       <c r="P5" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q5" s="20"/>
       <c r="R5" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S5" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U5" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V5" s="21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W5" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
       <c r="L6" s="18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M6" s="20"/>
       <c r="N6" s="20"/>
@@ -3164,56 +3197,56 @@
       <c r="P6" s="20"/>
       <c r="Q6" s="20"/>
       <c r="R6" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S6" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T6" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U6" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V6" s="21"/>
       <c r="W6" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K7" s="17"/>
       <c r="L7" s="18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M7" s="20"/>
       <c r="N7" s="20"/>
@@ -3221,103 +3254,103 @@
       <c r="P7" s="20"/>
       <c r="Q7" s="20"/>
       <c r="R7" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S7" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T7" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U7" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V7" s="21"/>
       <c r="W7" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
       <c r="L8" s="18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M8" s="20"/>
       <c r="N8" s="20"/>
       <c r="O8" s="20"/>
       <c r="P8" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q8" s="20"/>
       <c r="R8" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S8" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T8" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U8" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V8" s="21"/>
       <c r="W8" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E9" s="17"/>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
       <c r="H9" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
       <c r="L9" s="18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M9" s="20"/>
       <c r="N9" s="20"/>
@@ -3325,48 +3358,48 @@
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
       <c r="R9" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S9" s="17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V9" s="21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="W9" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E10" s="17"/>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
       <c r="H10" s="17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
       <c r="L10" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M10" s="20"/>
       <c r="N10" s="20"/>
@@ -3374,27 +3407,27 @@
       <c r="P10" s="20"/>
       <c r="Q10" s="20"/>
       <c r="R10" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S10" s="17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V10" s="21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="W10" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
@@ -3421,420 +3454,420 @@
     </row>
     <row r="12" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K12" s="17"/>
       <c r="L12" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="19" t="s">
         <v>57</v>
-      </c>
-      <c r="M12" s="19" t="s">
-        <v>56</v>
       </c>
       <c r="N12" s="20"/>
       <c r="O12" s="20"/>
       <c r="P12" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q12" s="20"/>
       <c r="R12" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S12" s="17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V12" s="21" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="W12" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K13" s="17"/>
       <c r="L13" s="20"/>
       <c r="M13" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N13" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O13" s="20"/>
       <c r="P13" s="20"/>
       <c r="Q13" s="20"/>
       <c r="R13" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S13" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V13" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="W13" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K14" s="17"/>
       <c r="L14" s="20"/>
       <c r="M14" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N14" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O14" s="20"/>
       <c r="P14" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q14" s="20"/>
       <c r="R14" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S14" s="17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="T14" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="U14" s="17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V14" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="W14" s="17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
       <c r="H15" s="17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I15" s="17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J15" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="20"/>
       <c r="M15" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N15" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O15" s="20"/>
       <c r="P15" s="20"/>
       <c r="Q15" s="20"/>
       <c r="R15" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S15" s="17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="T15" s="17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="U15" s="17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="V15" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="W15" s="17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
       <c r="H16" s="17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K16" s="17"/>
       <c r="L16" s="20"/>
       <c r="M16" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N16" s="20"/>
       <c r="O16" s="20"/>
       <c r="P16" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q16" s="20"/>
       <c r="R16" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S16" s="17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="V16" s="21" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W16" s="17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="20"/>
       <c r="M17" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N17" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O17" s="20"/>
       <c r="P17" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q17" s="20"/>
       <c r="R17" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S17" s="17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="V17" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="W17" s="17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
       <c r="H18" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K18" s="17"/>
       <c r="L18" s="20"/>
       <c r="M18" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N18" s="20"/>
       <c r="O18" s="20"/>
       <c r="P18" s="20"/>
       <c r="Q18" s="20"/>
       <c r="R18" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S18" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="V18" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="W18" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -3861,286 +3894,286 @@
     </row>
     <row r="20" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K20" s="17"/>
       <c r="L20" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="M20" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="N20" s="23" t="s">
         <v>57</v>
-      </c>
-      <c r="M20" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="N20" s="23" t="s">
-        <v>56</v>
       </c>
       <c r="O20" s="20"/>
       <c r="P20" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q20" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R20" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S20" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="V20" s="21" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="W20" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
       <c r="H21" s="17" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
       <c r="L21" s="20"/>
       <c r="M21" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N21" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O21" s="20"/>
       <c r="P21" s="20"/>
       <c r="Q21" s="20"/>
       <c r="R21" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S21" s="17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="T21" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U21" s="17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="V21" s="21"/>
       <c r="W21" s="17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
       <c r="H22" s="17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J22" s="17"/>
       <c r="K22" s="17"/>
       <c r="L22" s="20"/>
       <c r="M22" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N22" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O22" s="20"/>
       <c r="P22" s="20"/>
       <c r="Q22" s="20"/>
       <c r="R22" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S22" s="17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="T22" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U22" s="17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="V22" s="21"/>
       <c r="W22" s="17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
       <c r="H23" s="17" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
       <c r="L23" s="20"/>
       <c r="M23" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N23" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O23" s="20"/>
       <c r="P23" s="20"/>
       <c r="Q23" s="20"/>
       <c r="R23" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S23" s="17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="T23" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U23" s="17" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="V23" s="21"/>
       <c r="W23" s="17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
       <c r="H24" s="17" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J24" s="17"/>
       <c r="K24" s="17"/>
       <c r="L24" s="20"/>
       <c r="M24" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N24" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O24" s="20"/>
       <c r="P24" s="20"/>
       <c r="Q24" s="20"/>
       <c r="R24" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S24" s="17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="T24" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U24" s="17" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="V24" s="21"/>
       <c r="W24" s="17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -4167,133 +4200,133 @@
     </row>
     <row r="26" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K26" s="17"/>
       <c r="L26" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="M26" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="N26" s="23" t="s">
         <v>57</v>
-      </c>
-      <c r="M26" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="N26" s="23" t="s">
-        <v>56</v>
       </c>
       <c r="O26" s="20"/>
       <c r="P26" s="20"/>
       <c r="Q26" s="20"/>
       <c r="R26" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S26" s="17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="T26" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="U26" s="17" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="V26" s="21" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="W26" s="17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K27" s="17"/>
       <c r="L27" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="M27" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="N27" s="23" t="s">
         <v>57</v>
-      </c>
-      <c r="M27" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="N27" s="23" t="s">
-        <v>56</v>
       </c>
       <c r="O27" s="20"/>
       <c r="P27" s="20"/>
       <c r="Q27" s="20"/>
       <c r="R27" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S27" s="17" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="T27" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="U27" s="17" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="V27" s="21" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="W27" s="17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -4320,176 +4353,176 @@
     </row>
     <row r="29" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K29" s="17"/>
       <c r="L29" s="20"/>
       <c r="M29" s="20"/>
       <c r="N29" s="23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O29" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P29" s="20"/>
       <c r="Q29" s="20"/>
       <c r="R29" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S29" s="17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="T29" s="17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="U29" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V29" s="21" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="W29" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K30" s="17"/>
       <c r="L30" s="20"/>
       <c r="M30" s="20"/>
       <c r="N30" s="23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O30" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P30" s="20"/>
       <c r="Q30" s="20"/>
       <c r="R30" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S30" s="17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="T30" s="17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="U30" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V30" s="21" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="W30" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
       <c r="H31" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K31" s="17"/>
       <c r="L31" s="20"/>
       <c r="M31" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="N31" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="N31" s="23" t="s">
-        <v>56</v>
-      </c>
       <c r="O31" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P31" s="20"/>
       <c r="Q31" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R31" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S31" s="17" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="T31" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="U31" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V31" s="21" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="W31" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -4516,35 +4549,35 @@
     </row>
     <row r="33" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E33" s="17"/>
       <c r="F33" s="15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K33" s="26" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L33" s="20"/>
       <c r="M33" s="20"/>
@@ -4552,306 +4585,306 @@
       <c r="O33" s="20"/>
       <c r="P33" s="20"/>
       <c r="Q33" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R33" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S33" s="17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T33" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="U33" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="V33" s="21" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="W33" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E34" s="17"/>
       <c r="F34" s="15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K34" s="26" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L34" s="20"/>
       <c r="M34" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N34" s="20"/>
       <c r="O34" s="20"/>
       <c r="P34" s="20"/>
       <c r="Q34" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R34" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S34" s="17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T34" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="U34" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="V34" s="21" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="W34" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E35" s="17"/>
       <c r="F35" s="15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K35" s="26" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L35" s="20"/>
       <c r="M35" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N35" s="20"/>
       <c r="O35" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P35" s="20"/>
       <c r="Q35" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R35" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S35" s="17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T35" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="U35" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="V35" s="21" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="W35" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E36" s="17"/>
       <c r="F36" s="15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K36" s="26" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L36" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M36" s="20"/>
       <c r="N36" s="20"/>
       <c r="O36" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P36" s="20"/>
       <c r="Q36" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R36" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S36" s="17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T36" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="U36" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="V36" s="21" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="W36" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E37" s="17"/>
       <c r="F37" s="15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K37" s="26" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L37" s="20"/>
       <c r="M37" s="20"/>
       <c r="N37" s="20"/>
       <c r="O37" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P37" s="20"/>
       <c r="Q37" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R37" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S37" s="17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T37" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="U37" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="V37" s="21" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="W37" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E38" s="17"/>
       <c r="F38" s="15" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I38" s="17" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K38" s="26" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L38" s="20"/>
       <c r="M38" s="20"/>
@@ -4859,55 +4892,55 @@
       <c r="O38" s="20"/>
       <c r="P38" s="20"/>
       <c r="Q38" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R38" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S38" s="17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T38" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="U38" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="V38" s="21" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="W38" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E39" s="17"/>
       <c r="F39" s="15" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="20"/>
@@ -4916,114 +4949,114 @@
       <c r="O39" s="20"/>
       <c r="P39" s="20"/>
       <c r="Q39" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R39" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S39" s="17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T39" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="U39" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V39" s="21" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="W39" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E40" s="17"/>
       <c r="F40" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K40" s="17"/>
       <c r="L40" s="20"/>
       <c r="M40" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N40" s="20"/>
       <c r="O40" s="20"/>
       <c r="P40" s="20"/>
       <c r="Q40" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R40" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S40" s="17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T40" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="U40" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V40" s="21" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="W40" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E41" s="17"/>
       <c r="F41" s="15" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K41" s="17"/>
       <c r="L41" s="20"/>
@@ -5032,178 +5065,178 @@
       <c r="O41" s="20"/>
       <c r="P41" s="20"/>
       <c r="Q41" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R41" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S41" s="17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T41" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="U41" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V41" s="21" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="W41" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E42" s="17"/>
       <c r="F42" s="15" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K42" s="17"/>
       <c r="L42" s="20"/>
       <c r="M42" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N42" s="20"/>
       <c r="O42" s="20"/>
       <c r="P42" s="20"/>
       <c r="Q42" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R42" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S42" s="17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T42" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="U42" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V42" s="21" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="W42" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="15" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K43" s="26" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L43" s="20"/>
       <c r="M43" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N43" s="20"/>
       <c r="O43" s="20"/>
       <c r="P43" s="20"/>
       <c r="Q43" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R43" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S43" s="17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T43" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="U43" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="V43" s="21" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="W43" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E44" s="17"/>
       <c r="F44" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J44" s="17" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K44" s="26" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L44" s="20"/>
       <c r="M44" s="20"/>
@@ -5211,89 +5244,89 @@
       <c r="O44" s="20"/>
       <c r="P44" s="20"/>
       <c r="Q44" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R44" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S44" s="17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T44" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="U44" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="V44" s="21" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="W44" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I45" s="17" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K45" s="17"/>
       <c r="L45" s="20"/>
       <c r="M45" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N45" s="20"/>
       <c r="O45" s="20"/>
       <c r="P45" s="20"/>
       <c r="Q45" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R45" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S45" s="17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T45" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="U45" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V45" s="21" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="W45" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
@@ -5320,19 +5353,19 @@
     </row>
     <row r="47" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F47" s="15" t="n">
         <v>2026</v>
@@ -5341,57 +5374,57 @@
         <v>2026</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I47" s="17"/>
       <c r="J47" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K47" s="17"/>
       <c r="L47" s="20"/>
       <c r="M47" s="20"/>
       <c r="N47" s="20"/>
       <c r="O47" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P47" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q47" s="20"/>
       <c r="R47" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S47" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="T47" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="U47" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V47" s="21" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="W47" s="17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F48" s="15" t="n">
         <v>2026</v>
@@ -5400,236 +5433,236 @@
         <v>2026</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I48" s="17"/>
       <c r="J48" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K48" s="17"/>
       <c r="L48" s="20"/>
       <c r="M48" s="20"/>
       <c r="N48" s="20"/>
       <c r="O48" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P48" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q48" s="20"/>
       <c r="R48" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S48" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="T48" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="U48" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V48" s="21" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="W48" s="17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G49" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I49" s="17"/>
       <c r="J49" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K49" s="17"/>
       <c r="L49" s="20"/>
       <c r="M49" s="20"/>
       <c r="N49" s="20"/>
       <c r="O49" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P49" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q49" s="20"/>
       <c r="R49" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S49" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="T49" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="U49" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V49" s="21" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="W49" s="17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G50" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I50" s="17"/>
       <c r="J50" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K50" s="17"/>
       <c r="L50" s="20"/>
       <c r="M50" s="20"/>
       <c r="N50" s="20"/>
       <c r="O50" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P50" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q50" s="20"/>
       <c r="R50" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S50" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="T50" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="U50" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V50" s="21" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="W50" s="17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G51" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I51" s="17"/>
       <c r="J51" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M51" s="20"/>
       <c r="N51" s="20"/>
       <c r="O51" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P51" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q51" s="20"/>
       <c r="R51" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S51" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="T51" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="U51" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V51" s="21" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="W51" s="17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F52" s="15" t="n">
         <v>2024</v>
@@ -5638,57 +5671,57 @@
         <v>2024</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I52" s="17"/>
       <c r="J52" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K52" s="17"/>
       <c r="L52" s="20"/>
       <c r="M52" s="20"/>
       <c r="N52" s="20"/>
       <c r="O52" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P52" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q52" s="20"/>
       <c r="R52" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S52" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="T52" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="U52" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V52" s="21" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="W52" s="17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F53" s="15" t="n">
         <v>2023</v>
@@ -5697,57 +5730,57 @@
         <v>2023</v>
       </c>
       <c r="H53" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I53" s="17"/>
       <c r="J53" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K53" s="17"/>
       <c r="L53" s="20"/>
       <c r="M53" s="20"/>
       <c r="N53" s="20"/>
       <c r="O53" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P53" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q53" s="20"/>
       <c r="R53" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S53" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="T53" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="U53" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V53" s="21" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="W53" s="17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F54" s="15" t="n">
         <v>2023</v>
@@ -5756,57 +5789,57 @@
         <v>2023</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I54" s="17"/>
       <c r="J54" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K54" s="17"/>
       <c r="L54" s="20"/>
       <c r="M54" s="20"/>
       <c r="N54" s="20"/>
       <c r="O54" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P54" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q54" s="20"/>
       <c r="R54" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S54" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="T54" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="U54" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V54" s="21" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="W54" s="17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F55" s="15" t="n">
         <v>2022</v>
@@ -5815,57 +5848,57 @@
         <v>2022</v>
       </c>
       <c r="H55" s="17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I55" s="17"/>
       <c r="J55" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K55" s="17"/>
       <c r="L55" s="20"/>
       <c r="M55" s="20"/>
       <c r="N55" s="20"/>
       <c r="O55" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P55" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q55" s="20"/>
       <c r="R55" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S55" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="T55" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="U55" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V55" s="21" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="W55" s="17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F56" s="15" t="n">
         <v>2021</v>
@@ -5874,57 +5907,57 @@
         <v>2021</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I56" s="17"/>
       <c r="J56" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K56" s="17"/>
       <c r="L56" s="20"/>
       <c r="M56" s="20"/>
       <c r="N56" s="20"/>
       <c r="O56" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P56" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q56" s="20"/>
       <c r="R56" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S56" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="T56" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="U56" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V56" s="21" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="W56" s="17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="15" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F57" s="15" t="n">
         <v>2022</v>
@@ -5933,43 +5966,43 @@
         <v>2022</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="I57" s="17"/>
       <c r="J57" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K57" s="17"/>
       <c r="L57" s="20"/>
       <c r="M57" s="20"/>
       <c r="N57" s="20"/>
       <c r="O57" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P57" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q57" s="20"/>
       <c r="R57" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S57" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="T57" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="U57" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V57" s="21"/>
       <c r="W57" s="17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="13" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -5996,328 +6029,328 @@
     </row>
     <row r="59" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="15" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C59" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="D59" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="E59" s="17" t="s">
         <v>406</v>
-      </c>
-      <c r="D59" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="E59" s="17" t="s">
-        <v>405</v>
       </c>
       <c r="F59" s="15"/>
       <c r="G59" s="15"/>
       <c r="H59" s="17" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I59" s="17"/>
       <c r="J59" s="17"/>
       <c r="K59" s="17"/>
       <c r="L59" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M59" s="20"/>
       <c r="N59" s="20"/>
       <c r="O59" s="20"/>
       <c r="P59" s="22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q59" s="20"/>
       <c r="R59" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S59" s="17" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="T59" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U59" s="17"/>
       <c r="V59" s="21" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="W59" s="17" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G60" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="I60" s="17"/>
       <c r="J60" s="17"/>
       <c r="K60" s="17"/>
       <c r="L60" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M60" s="20"/>
       <c r="N60" s="20"/>
       <c r="O60" s="20"/>
       <c r="P60" s="22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q60" s="20"/>
       <c r="R60" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S60" s="17" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="T60" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U60" s="17"/>
       <c r="V60" s="21" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="W60" s="17" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="15" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G61" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I61" s="17"/>
       <c r="J61" s="17"/>
       <c r="K61" s="17"/>
       <c r="L61" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M61" s="20"/>
       <c r="N61" s="20"/>
       <c r="O61" s="20"/>
       <c r="P61" s="22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q61" s="20"/>
       <c r="R61" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S61" s="17" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="T61" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U61" s="17"/>
       <c r="V61" s="21" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="W61" s="17" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="15" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G62" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="I62" s="17"/>
       <c r="J62" s="17"/>
       <c r="K62" s="17"/>
       <c r="L62" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M62" s="20"/>
       <c r="N62" s="20"/>
       <c r="O62" s="20"/>
       <c r="P62" s="22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q62" s="20"/>
       <c r="R62" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S62" s="17" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="T62" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U62" s="17"/>
       <c r="V62" s="21" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="W62" s="17" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G63" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I63" s="17"/>
       <c r="J63" s="17"/>
       <c r="K63" s="17"/>
       <c r="L63" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M63" s="20"/>
       <c r="N63" s="20"/>
       <c r="O63" s="20"/>
       <c r="P63" s="22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q63" s="20"/>
       <c r="R63" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S63" s="17" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="T63" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U63" s="17"/>
       <c r="V63" s="21" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="W63" s="17" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G64" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="I64" s="17"/>
       <c r="J64" s="17"/>
       <c r="K64" s="17"/>
       <c r="L64" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M64" s="20"/>
       <c r="N64" s="20"/>
       <c r="O64" s="20"/>
       <c r="P64" s="22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q64" s="20"/>
       <c r="R64" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S64" s="17" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="T64" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U64" s="17"/>
       <c r="V64" s="21" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="W64" s="17" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -6373,33 +6406,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="29" t="n">
         <f aca="false">COUNTIF(Artifacts!$L$2:$L$124,"●")</f>
@@ -6424,12 +6457,12 @@
         <v>Add</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="29" t="n">
         <f aca="false">COUNTIF(Artifacts!$M$2:$M$124,"●")</f>
@@ -6454,12 +6487,12 @@
         <v>OK</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="29" t="n">
         <f aca="false">COUNTIF(Artifacts!$N$2:$N$124,"●")</f>
@@ -6484,12 +6517,12 @@
         <v>OK</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="29" t="n">
         <f aca="false">COUNTIF(Artifacts!$O$2:$O$124,"●")</f>
@@ -6514,12 +6547,12 @@
         <v>OK</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="29" t="n">
         <f aca="false">COUNTIF(Artifacts!$P$2:$P$124,"●")</f>
@@ -6544,12 +6577,12 @@
         <v>OK</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="29" t="n">
         <f aca="false">COUNTIF(Artifacts!$Q$2:$Q$124,"●")</f>
@@ -6574,7 +6607,7 @@
         <v>OK</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6589,7 +6622,7 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">COUNTA(Artifacts!$C$2:$C$124)</f>
@@ -6604,7 +6637,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -6640,50 +6673,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J1" s="27" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="E2" s="17" t="s">
+        <v>104</v>
+      </c>
       <c r="F2" s="17" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G2" s="17" t="n">
         <v>42.08</v>
@@ -6692,28 +6727,30 @@
         <v>-87.72</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="J2" s="21"/>
+        <v>59</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>459</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>426</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="17" t="s">
         <v>102</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>457</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>425</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>101</v>
       </c>
       <c r="G3" s="17" t="n">
         <v>38.97</v>
@@ -6722,30 +6759,30 @@
         <v>-95.24</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="G4" s="17" t="n">
         <v>41.88</v>
@@ -6754,7 +6791,7 @@
         <v>-87.63</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="21" t="s">
         <v>460</v>
@@ -6762,22 +6799,22 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>45.46</v>
@@ -6786,30 +6823,30 @@
         <v>9.19</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G6" s="17" t="n">
         <v>32.78</v>
@@ -6818,30 +6855,30 @@
         <v>-96.8</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>30.27</v>
@@ -6850,26 +6887,26 @@
         <v>-97.74</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="17" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>29.76</v>
@@ -6878,24 +6915,24 @@
         <v>-95.37</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J8" s="21"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="17" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>33.43</v>
@@ -6904,24 +6941,24 @@
         <v>-111.94</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="17" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G10" s="17" t="n">
         <v>32.76</v>
@@ -6930,28 +6967,28 @@
         <v>-97.33</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>40.81</v>
@@ -6960,28 +6997,28 @@
         <v>-96.7</v>
       </c>
       <c r="I11" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G12" s="17" t="n">
         <v>39.57</v>
@@ -6990,28 +7027,28 @@
         <v>2.65</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J12" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>38.72</v>
@@ -7020,112 +7057,112 @@
         <v>-9.14</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J13" s="21"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
       <c r="I14" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G15" s="17"/>
       <c r="H15" s="17"/>
       <c r="I15" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J15" s="21" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
       <c r="I16" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J16" s="21" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>-22.97</v>
@@ -7134,58 +7171,58 @@
         <v>-43.18</v>
       </c>
       <c r="I17" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
       <c r="I18" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>26.71</v>
@@ -7194,28 +7231,28 @@
         <v>-80.04</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G20" s="17" t="n">
         <v>19.43</v>
@@ -7224,28 +7261,28 @@
         <v>-99.13</v>
       </c>
       <c r="I20" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J20" s="21"/>
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>41.89</v>
@@ -7254,46 +7291,46 @@
         <v>12.49</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
       <c r="I22" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J22" s="21"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
@@ -7326,36 +7363,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D2" s="32" t="n">
         <v>2026</v>
@@ -7364,19 +7401,19 @@
         <v>65</v>
       </c>
       <c r="F2" s="34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G2" s="32"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="32" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D3" s="32" t="n">
         <v>2026</v>
@@ -7385,82 +7422,82 @@
         <v>64</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" s="32"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>267</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G4" s="32"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>84</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G5" s="32"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>39</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6" s="32"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>2024</v>
@@ -7469,19 +7506,19 @@
         <v>177</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7" s="32"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>2023</v>
@@ -7490,19 +7527,19 @@
         <v>106</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G8" s="32"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>2023</v>
@@ -7511,19 +7548,19 @@
         <v>39</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G9" s="32"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D10" s="32" t="n">
         <v>2022</v>
@@ -7532,19 +7569,19 @@
         <v>59</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10" s="32"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D11" s="32" t="n">
         <v>2021</v>
@@ -7553,19 +7590,19 @@
         <v>59</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11" s="32"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D12" s="32" t="n">
         <v>2022</v>
@@ -7574,13 +7611,13 @@
         <v>53</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G12" s="32"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D13" s="28" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E13" s="28" t="n">
         <f aca="false">SUM(E2:E12)</f>
@@ -7589,7 +7626,7 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D14" s="28" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E14" s="28" t="n">
         <f aca="false">COUNTIF(F2:F12,"Yes")</f>
@@ -7598,12 +7635,12 @@
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -7634,393 +7671,427 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B3" s="16" t="s">
+        <v>514</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>515</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>513</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>514</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D22" s="21"/>
       <c r="E22" s="17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="17" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+        <v>513</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="s">
+        <v>557</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>563</v>
+      </c>
+      <c r="D24" s="21"/>
+      <c r="E24" s="17" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>565</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>566</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>564</v>
+      </c>
+    </row>
     <row r="26" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>561</v>
+        <v>567</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>568</v>
       </c>
     </row>
   </sheetData>
@@ -8050,16 +8121,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="C1" s="27" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1" s="27" t="s">
         <v>564</v>
-      </c>
-      <c r="D1" s="27" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8067,13 +8138,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8081,13 +8152,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8095,13 +8166,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8109,13 +8180,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8123,13 +8194,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8137,13 +8208,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8151,13 +8222,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8165,13 +8236,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8179,13 +8250,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8193,13 +8264,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8207,13 +8278,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8221,13 +8292,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8235,13 +8306,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8249,13 +8320,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8263,13 +8334,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8277,13 +8348,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8291,13 +8362,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8305,13 +8376,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8319,10 +8390,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="D20" s="21"/>
     </row>
@@ -8331,24 +8402,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>616</v>
-      </c>
-      <c r="D21" s="21"/>
+        <v>622</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>623</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>618</v>
-      </c>
-      <c r="D22" s="21"/>
+        <v>625</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>626</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -13,8 +13,9 @@
     <sheet name="Section summary" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Places" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Films" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Profile" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Open questions" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Countries" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Profile" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Open questions" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Artifacts!$A$1:$W$64</definedName>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="669">
   <si>
     <t xml:space="preserve">Site artifacts: mapping workbook</t>
   </si>
@@ -87,7 +88,7 @@
     <t xml:space="preserve">Keep it uncluttered: personal context supports the work quietly, it never crowds it.</t>
   </si>
   <si>
-    <t xml:space="preserve">Latest decisions: one quiet line in About ("Based in Austin · English, Italian, learning Portuguese"), with Jaylee and Helga as one small sprite each beside it, not in the orbit. No languages on the Travel map; no sports on films or trips.</t>
+    <t xml:space="preserve">Latest decisions: one quiet line in About ("Based in Austin · English, Italian, learning Portuguese"), with Jaylee and Helga as one small sprite each beside it, not in the orbit. No languages on the Travel map; no sports on films or trips. The Travel map is small dots (lived, photos, worked), lines only for the moves between places lived, and the countries visited shaded.</t>
   </si>
   <si>
     <t xml:space="preserve">Sheets</t>
@@ -105,6 +106,9 @@
     <t xml:space="preserve">Films: the 35mm albums with photo counts.</t>
   </si>
   <si>
+    <t xml:space="preserve">Countries: the 34 countries visited, all on the Travel map.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Profile: personal context (themes, languages, interests, values), kept apart from resume facts.</t>
   </si>
   <si>
@@ -1563,7 +1567,7 @@
     <t xml:space="preserve">Film F11</t>
   </si>
   <si>
-    <t xml:space="preserve">Lived vs travelled are kept separate. Your country list (34 entries counted earlier, 33 in your note) still needs adding so every country can go on the map.</t>
+    <t xml:space="preserve">Lived vs travelled are kept separate. Countries visited (34) are on the Countries sheet and all shaded on the Travel map.</t>
   </si>
   <si>
     <t xml:space="preserve">Coordinates are approximate city centres for the map; blank where the city is unknown.</t>
@@ -1587,6 +1591,129 @@
     <t xml:space="preserve">I hace them on google just add place holders viaul now we can give you folder or links later for the phtoos.</t>
   </si>
   <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On the Travel map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North America</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shaded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bahamas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caribbean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominican Republic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Too small for the map outlines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St Lucia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St Kitts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamaica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central America</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honduras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guatemala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South America</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Films F3, F7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argentina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Africa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Africa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lived (Milan); film F10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croatia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czech Republic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switzerland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denmark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">England (UK)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netherlands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your list, 34 countries (count verified). Every one is on the Travel map: shaded, or a dot for the four islands too small for its outlines.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Group</t>
   </si>
   <si>
@@ -1776,9 +1903,6 @@
     <t xml:space="preserve">→ Decided: the one quiet line and the dogs (rows 24–25). Everything else here is shown by the work itself, not listed.</t>
   </si>
   <si>
-    <t xml:space="preserve">#</t>
-  </si>
-  <si>
     <t xml:space="preserve">Question</t>
   </si>
   <si>
@@ -1930,6 +2054,9 @@
   </si>
   <si>
     <t xml:space="preserve">I don't have the country list itself: it was in an earlier conversation. Paste it and I'll verify the count and put every country on the map.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Received: 34 countries (count verified). All on the map; see the Countries sheet.</t>
   </si>
   <si>
     <t xml:space="preserve">Only Austin was confirmed. Are Lawrence 2014–18, Chicago 2018–19, Milan 2019–21 and Dallas 2021–25 right?</t>
@@ -2198,7 +2325,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2336,10 +2463,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2704,7 +2827,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="120"/>
@@ -2740,7 +2863,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -2784,15 +2907,15 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3"/>
+      <c r="A17" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="A18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2812,29 +2935,34 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3"/>
+      <c r="A23" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="A24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3"/>
+      <c r="A26" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="A27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="5" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2881,78 +3009,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O1" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q1" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -2979,217 +3107,217 @@
     </row>
     <row r="3" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K3" s="17"/>
       <c r="L3" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M3" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N3" s="20"/>
       <c r="O3" s="20"/>
       <c r="P3" s="20"/>
       <c r="Q3" s="20"/>
       <c r="R3" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S3" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T3" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U3" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V3" s="21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W3" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K4" s="17"/>
       <c r="L4" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M4" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N4" s="20"/>
       <c r="O4" s="20"/>
       <c r="P4" s="20"/>
       <c r="Q4" s="20"/>
       <c r="R4" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S4" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T4" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U4" s="17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V4" s="21"/>
       <c r="W4" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
       <c r="L5" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N5" s="20"/>
       <c r="O5" s="20"/>
       <c r="P5" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q5" s="20"/>
       <c r="R5" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S5" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U5" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V5" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W5" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
       <c r="L6" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M6" s="20"/>
       <c r="N6" s="20"/>
@@ -3197,56 +3325,56 @@
       <c r="P6" s="20"/>
       <c r="Q6" s="20"/>
       <c r="R6" s="20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S6" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T6" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U6" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V6" s="21"/>
       <c r="W6" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K7" s="17"/>
       <c r="L7" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M7" s="20"/>
       <c r="N7" s="20"/>
@@ -3254,103 +3382,103 @@
       <c r="P7" s="20"/>
       <c r="Q7" s="20"/>
       <c r="R7" s="20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S7" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T7" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U7" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V7" s="21"/>
       <c r="W7" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
       <c r="L8" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M8" s="20"/>
       <c r="N8" s="20"/>
       <c r="O8" s="20"/>
       <c r="P8" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q8" s="20"/>
       <c r="R8" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S8" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T8" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U8" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V8" s="21"/>
       <c r="W8" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E9" s="17"/>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
       <c r="H9" s="17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
       <c r="L9" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M9" s="20"/>
       <c r="N9" s="20"/>
@@ -3358,48 +3486,48 @@
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
       <c r="R9" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S9" s="17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V9" s="21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="W9" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E10" s="17"/>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
       <c r="H10" s="17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
       <c r="L10" s="18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M10" s="20"/>
       <c r="N10" s="20"/>
@@ -3407,27 +3535,27 @@
       <c r="P10" s="20"/>
       <c r="Q10" s="20"/>
       <c r="R10" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S10" s="17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V10" s="21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="W10" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
@@ -3454,420 +3582,420 @@
     </row>
     <row r="12" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K12" s="17"/>
       <c r="L12" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="M12" s="19" t="s">
         <v>58</v>
-      </c>
-      <c r="M12" s="19" t="s">
-        <v>57</v>
       </c>
       <c r="N12" s="20"/>
       <c r="O12" s="20"/>
       <c r="P12" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q12" s="20"/>
       <c r="R12" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S12" s="17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V12" s="21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="W12" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K13" s="17"/>
       <c r="L13" s="20"/>
       <c r="M13" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N13" s="23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O13" s="20"/>
       <c r="P13" s="20"/>
       <c r="Q13" s="20"/>
       <c r="R13" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S13" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V13" s="21" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="W13" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K14" s="17"/>
       <c r="L14" s="20"/>
       <c r="M14" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N14" s="23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O14" s="20"/>
       <c r="P14" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q14" s="20"/>
       <c r="R14" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S14" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="T14" s="17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="U14" s="17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="V14" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="W14" s="17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
       <c r="H15" s="17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I15" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J15" s="17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="20"/>
       <c r="M15" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N15" s="23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O15" s="20"/>
       <c r="P15" s="20"/>
       <c r="Q15" s="20"/>
       <c r="R15" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S15" s="17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T15" s="17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U15" s="17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V15" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="W15" s="17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
       <c r="H16" s="17" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K16" s="17"/>
       <c r="L16" s="20"/>
       <c r="M16" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N16" s="20"/>
       <c r="O16" s="20"/>
       <c r="P16" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q16" s="20"/>
       <c r="R16" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S16" s="17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V16" s="21" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="W16" s="17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="20"/>
       <c r="M17" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N17" s="23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O17" s="20"/>
       <c r="P17" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q17" s="20"/>
       <c r="R17" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S17" s="17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="V17" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="W17" s="17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
       <c r="H18" s="17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K18" s="17"/>
       <c r="L18" s="20"/>
       <c r="M18" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N18" s="20"/>
       <c r="O18" s="20"/>
       <c r="P18" s="20"/>
       <c r="Q18" s="20"/>
       <c r="R18" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S18" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="V18" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="W18" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -3894,286 +4022,286 @@
     </row>
     <row r="20" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K20" s="17"/>
       <c r="L20" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="M20" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="N20" s="23" t="s">
         <v>58</v>
-      </c>
-      <c r="M20" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="N20" s="23" t="s">
-        <v>57</v>
       </c>
       <c r="O20" s="20"/>
       <c r="P20" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q20" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R20" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S20" s="17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="V20" s="21" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="W20" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
       <c r="H21" s="17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
       <c r="L21" s="20"/>
       <c r="M21" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N21" s="23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O21" s="20"/>
       <c r="P21" s="20"/>
       <c r="Q21" s="20"/>
       <c r="R21" s="20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S21" s="17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="T21" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U21" s="17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="V21" s="21"/>
       <c r="W21" s="17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
       <c r="H22" s="17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J22" s="17"/>
       <c r="K22" s="17"/>
       <c r="L22" s="20"/>
       <c r="M22" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N22" s="23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O22" s="20"/>
       <c r="P22" s="20"/>
       <c r="Q22" s="20"/>
       <c r="R22" s="20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S22" s="17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="T22" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U22" s="17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="V22" s="21"/>
       <c r="W22" s="17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
       <c r="H23" s="17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
       <c r="L23" s="20"/>
       <c r="M23" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N23" s="23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O23" s="20"/>
       <c r="P23" s="20"/>
       <c r="Q23" s="20"/>
       <c r="R23" s="20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S23" s="17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="T23" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U23" s="17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="V23" s="21"/>
       <c r="W23" s="17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
       <c r="H24" s="17" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J24" s="17"/>
       <c r="K24" s="17"/>
       <c r="L24" s="20"/>
       <c r="M24" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N24" s="23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O24" s="20"/>
       <c r="P24" s="20"/>
       <c r="Q24" s="20"/>
       <c r="R24" s="20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S24" s="17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="T24" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U24" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="V24" s="21"/>
       <c r="W24" s="17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -4200,133 +4328,133 @@
     </row>
     <row r="26" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K26" s="17"/>
       <c r="L26" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="M26" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="N26" s="23" t="s">
         <v>58</v>
-      </c>
-      <c r="M26" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="N26" s="23" t="s">
-        <v>57</v>
       </c>
       <c r="O26" s="20"/>
       <c r="P26" s="20"/>
       <c r="Q26" s="20"/>
       <c r="R26" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S26" s="17" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="T26" s="17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="U26" s="17" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="V26" s="21" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="W26" s="17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K27" s="17"/>
       <c r="L27" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="M27" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="N27" s="23" t="s">
         <v>58</v>
-      </c>
-      <c r="M27" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="N27" s="23" t="s">
-        <v>57</v>
       </c>
       <c r="O27" s="20"/>
       <c r="P27" s="20"/>
       <c r="Q27" s="20"/>
       <c r="R27" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S27" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="T27" s="17" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="U27" s="17" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="V27" s="21" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="W27" s="17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -4353,176 +4481,176 @@
     </row>
     <row r="29" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K29" s="17"/>
       <c r="L29" s="20"/>
       <c r="M29" s="20"/>
       <c r="N29" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O29" s="25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P29" s="20"/>
       <c r="Q29" s="20"/>
       <c r="R29" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S29" s="17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="T29" s="17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="U29" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V29" s="21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="W29" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K30" s="17"/>
       <c r="L30" s="20"/>
       <c r="M30" s="20"/>
       <c r="N30" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O30" s="25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P30" s="20"/>
       <c r="Q30" s="20"/>
       <c r="R30" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S30" s="17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="T30" s="17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="U30" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V30" s="21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="W30" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
       <c r="H31" s="17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K31" s="17"/>
       <c r="L31" s="20"/>
       <c r="M31" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="N31" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="N31" s="23" t="s">
-        <v>57</v>
-      </c>
       <c r="O31" s="25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P31" s="20"/>
       <c r="Q31" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R31" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S31" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="T31" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="U31" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V31" s="21" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W31" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -4549,35 +4677,35 @@
     </row>
     <row r="33" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E33" s="17"/>
       <c r="F33" s="15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K33" s="26" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L33" s="20"/>
       <c r="M33" s="20"/>
@@ -4585,306 +4713,306 @@
       <c r="O33" s="20"/>
       <c r="P33" s="20"/>
       <c r="Q33" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R33" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S33" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T33" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U33" s="17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="V33" s="21" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="W33" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E34" s="17"/>
       <c r="F34" s="15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K34" s="26" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L34" s="20"/>
       <c r="M34" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N34" s="20"/>
       <c r="O34" s="20"/>
       <c r="P34" s="20"/>
       <c r="Q34" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R34" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S34" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T34" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U34" s="17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="V34" s="21" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="W34" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E35" s="17"/>
       <c r="F35" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K35" s="26" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L35" s="20"/>
       <c r="M35" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N35" s="20"/>
       <c r="O35" s="25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P35" s="20"/>
       <c r="Q35" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R35" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S35" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T35" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U35" s="17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="V35" s="21" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="W35" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E36" s="17"/>
       <c r="F36" s="15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K36" s="26" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L36" s="18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M36" s="20"/>
       <c r="N36" s="20"/>
       <c r="O36" s="25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P36" s="20"/>
       <c r="Q36" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R36" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S36" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T36" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U36" s="17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="V36" s="21" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="W36" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E37" s="17"/>
       <c r="F37" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K37" s="26" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L37" s="20"/>
       <c r="M37" s="20"/>
       <c r="N37" s="20"/>
       <c r="O37" s="25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P37" s="20"/>
       <c r="Q37" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R37" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S37" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T37" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U37" s="17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="V37" s="21" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="W37" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E38" s="17"/>
       <c r="F38" s="15" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I38" s="17" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K38" s="26" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L38" s="20"/>
       <c r="M38" s="20"/>
@@ -4892,55 +5020,55 @@
       <c r="O38" s="20"/>
       <c r="P38" s="20"/>
       <c r="Q38" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R38" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S38" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T38" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U38" s="17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="V38" s="21" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="W38" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E39" s="17"/>
       <c r="F39" s="15" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="20"/>
@@ -4949,114 +5077,114 @@
       <c r="O39" s="20"/>
       <c r="P39" s="20"/>
       <c r="Q39" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R39" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S39" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T39" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U39" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V39" s="21" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="W39" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E40" s="17"/>
       <c r="F40" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K40" s="17"/>
       <c r="L40" s="20"/>
       <c r="M40" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N40" s="20"/>
       <c r="O40" s="20"/>
       <c r="P40" s="20"/>
       <c r="Q40" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R40" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S40" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T40" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U40" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V40" s="21" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="W40" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E41" s="17"/>
       <c r="F41" s="15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K41" s="17"/>
       <c r="L41" s="20"/>
@@ -5065,178 +5193,178 @@
       <c r="O41" s="20"/>
       <c r="P41" s="20"/>
       <c r="Q41" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R41" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S41" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T41" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U41" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V41" s="21" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="W41" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E42" s="17"/>
       <c r="F42" s="15" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K42" s="17"/>
       <c r="L42" s="20"/>
       <c r="M42" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N42" s="20"/>
       <c r="O42" s="20"/>
       <c r="P42" s="20"/>
       <c r="Q42" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R42" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S42" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T42" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U42" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V42" s="21" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="W42" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="15" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K43" s="26" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L43" s="20"/>
       <c r="M43" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N43" s="20"/>
       <c r="O43" s="20"/>
       <c r="P43" s="20"/>
       <c r="Q43" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R43" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S43" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T43" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U43" s="17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="V43" s="21" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="W43" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E44" s="17"/>
       <c r="F44" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J44" s="17" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K44" s="26" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L44" s="20"/>
       <c r="M44" s="20"/>
@@ -5244,89 +5372,89 @@
       <c r="O44" s="20"/>
       <c r="P44" s="20"/>
       <c r="Q44" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R44" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S44" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T44" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U44" s="17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="V44" s="21" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="W44" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I45" s="17" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K45" s="17"/>
       <c r="L45" s="20"/>
       <c r="M45" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N45" s="20"/>
       <c r="O45" s="20"/>
       <c r="P45" s="20"/>
       <c r="Q45" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R45" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S45" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T45" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U45" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V45" s="21" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="W45" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
@@ -5353,19 +5481,19 @@
     </row>
     <row r="47" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F47" s="15" t="n">
         <v>2026</v>
@@ -5374,57 +5502,57 @@
         <v>2026</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I47" s="17"/>
       <c r="J47" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K47" s="17"/>
       <c r="L47" s="20"/>
       <c r="M47" s="20"/>
       <c r="N47" s="20"/>
       <c r="O47" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P47" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q47" s="20"/>
       <c r="R47" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S47" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T47" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="U47" s="17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="V47" s="21" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="W47" s="17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F48" s="15" t="n">
         <v>2026</v>
@@ -5433,236 +5561,236 @@
         <v>2026</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I48" s="17"/>
       <c r="J48" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K48" s="17"/>
       <c r="L48" s="20"/>
       <c r="M48" s="20"/>
       <c r="N48" s="20"/>
       <c r="O48" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P48" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q48" s="20"/>
       <c r="R48" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S48" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T48" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="U48" s="17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="V48" s="21" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="W48" s="17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G49" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I49" s="17"/>
       <c r="J49" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K49" s="17"/>
       <c r="L49" s="20"/>
       <c r="M49" s="20"/>
       <c r="N49" s="20"/>
       <c r="O49" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P49" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q49" s="20"/>
       <c r="R49" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S49" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T49" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="U49" s="17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="V49" s="21" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="W49" s="17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G50" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I50" s="17"/>
       <c r="J50" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K50" s="17"/>
       <c r="L50" s="20"/>
       <c r="M50" s="20"/>
       <c r="N50" s="20"/>
       <c r="O50" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P50" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q50" s="20"/>
       <c r="R50" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S50" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T50" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="U50" s="17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="V50" s="21" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="W50" s="17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G51" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I51" s="17"/>
       <c r="J51" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M51" s="20"/>
       <c r="N51" s="20"/>
       <c r="O51" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P51" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q51" s="20"/>
       <c r="R51" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S51" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T51" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="U51" s="17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="V51" s="21" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="W51" s="17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F52" s="15" t="n">
         <v>2024</v>
@@ -5671,57 +5799,57 @@
         <v>2024</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I52" s="17"/>
       <c r="J52" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K52" s="17"/>
       <c r="L52" s="20"/>
       <c r="M52" s="20"/>
       <c r="N52" s="20"/>
       <c r="O52" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P52" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q52" s="20"/>
       <c r="R52" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S52" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T52" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="U52" s="17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="V52" s="21" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="W52" s="17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F53" s="15" t="n">
         <v>2023</v>
@@ -5730,57 +5858,57 @@
         <v>2023</v>
       </c>
       <c r="H53" s="17" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I53" s="17"/>
       <c r="J53" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K53" s="17"/>
       <c r="L53" s="20"/>
       <c r="M53" s="20"/>
       <c r="N53" s="20"/>
       <c r="O53" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P53" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q53" s="20"/>
       <c r="R53" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S53" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T53" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="U53" s="17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="V53" s="21" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="W53" s="17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F54" s="15" t="n">
         <v>2023</v>
@@ -5789,57 +5917,57 @@
         <v>2023</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I54" s="17"/>
       <c r="J54" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K54" s="17"/>
       <c r="L54" s="20"/>
       <c r="M54" s="20"/>
       <c r="N54" s="20"/>
       <c r="O54" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P54" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q54" s="20"/>
       <c r="R54" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S54" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T54" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="U54" s="17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="V54" s="21" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="W54" s="17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F55" s="15" t="n">
         <v>2022</v>
@@ -5848,57 +5976,57 @@
         <v>2022</v>
       </c>
       <c r="H55" s="17" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I55" s="17"/>
       <c r="J55" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K55" s="17"/>
       <c r="L55" s="20"/>
       <c r="M55" s="20"/>
       <c r="N55" s="20"/>
       <c r="O55" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P55" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q55" s="20"/>
       <c r="R55" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S55" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T55" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="U55" s="17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="V55" s="21" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="W55" s="17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F56" s="15" t="n">
         <v>2021</v>
@@ -5907,57 +6035,57 @@
         <v>2021</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I56" s="17"/>
       <c r="J56" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K56" s="17"/>
       <c r="L56" s="20"/>
       <c r="M56" s="20"/>
       <c r="N56" s="20"/>
       <c r="O56" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P56" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q56" s="20"/>
       <c r="R56" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S56" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T56" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="U56" s="17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="V56" s="21" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="W56" s="17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="15" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F57" s="15" t="n">
         <v>2022</v>
@@ -5966,43 +6094,43 @@
         <v>2022</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I57" s="17"/>
       <c r="J57" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K57" s="17"/>
       <c r="L57" s="20"/>
       <c r="M57" s="20"/>
       <c r="N57" s="20"/>
       <c r="O57" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P57" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q57" s="20"/>
       <c r="R57" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S57" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T57" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="U57" s="17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="V57" s="21"/>
       <c r="W57" s="17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="13" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -6029,328 +6157,328 @@
     </row>
     <row r="59" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="15" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C59" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="D59" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="E59" s="17" t="s">
         <v>407</v>
-      </c>
-      <c r="D59" s="17" t="s">
-        <v>408</v>
-      </c>
-      <c r="E59" s="17" t="s">
-        <v>406</v>
       </c>
       <c r="F59" s="15"/>
       <c r="G59" s="15"/>
       <c r="H59" s="17" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="I59" s="17"/>
       <c r="J59" s="17"/>
       <c r="K59" s="17"/>
       <c r="L59" s="18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M59" s="20"/>
       <c r="N59" s="20"/>
       <c r="O59" s="20"/>
       <c r="P59" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q59" s="20"/>
       <c r="R59" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S59" s="17" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="T59" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U59" s="17"/>
       <c r="V59" s="21" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="W59" s="17" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G60" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I60" s="17"/>
       <c r="J60" s="17"/>
       <c r="K60" s="17"/>
       <c r="L60" s="18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M60" s="20"/>
       <c r="N60" s="20"/>
       <c r="O60" s="20"/>
       <c r="P60" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q60" s="20"/>
       <c r="R60" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S60" s="17" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="T60" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U60" s="17"/>
       <c r="V60" s="21" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="W60" s="17" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="15" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G61" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I61" s="17"/>
       <c r="J61" s="17"/>
       <c r="K61" s="17"/>
       <c r="L61" s="18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M61" s="20"/>
       <c r="N61" s="20"/>
       <c r="O61" s="20"/>
       <c r="P61" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q61" s="20"/>
       <c r="R61" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S61" s="17" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="T61" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U61" s="17"/>
       <c r="V61" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="W61" s="17" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="15" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G62" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I62" s="17"/>
       <c r="J62" s="17"/>
       <c r="K62" s="17"/>
       <c r="L62" s="18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M62" s="20"/>
       <c r="N62" s="20"/>
       <c r="O62" s="20"/>
       <c r="P62" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q62" s="20"/>
       <c r="R62" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S62" s="17" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="T62" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U62" s="17"/>
       <c r="V62" s="21" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="W62" s="17" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G63" s="15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I63" s="17"/>
       <c r="J63" s="17"/>
       <c r="K63" s="17"/>
       <c r="L63" s="18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M63" s="20"/>
       <c r="N63" s="20"/>
       <c r="O63" s="20"/>
       <c r="P63" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q63" s="20"/>
       <c r="R63" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S63" s="17" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="T63" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U63" s="17"/>
       <c r="V63" s="21" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="W63" s="17" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G64" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I64" s="17"/>
       <c r="J64" s="17"/>
       <c r="K64" s="17"/>
       <c r="L64" s="18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M64" s="20"/>
       <c r="N64" s="20"/>
       <c r="O64" s="20"/>
       <c r="P64" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q64" s="20"/>
       <c r="R64" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S64" s="17" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="T64" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U64" s="17"/>
       <c r="V64" s="21" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="W64" s="17" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -6406,33 +6534,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="29" t="n">
         <f aca="false">COUNTIF(Artifacts!$L$2:$L$124,"●")</f>
@@ -6457,12 +6585,12 @@
         <v>Add</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="29" t="n">
         <f aca="false">COUNTIF(Artifacts!$M$2:$M$124,"●")</f>
@@ -6487,12 +6615,12 @@
         <v>OK</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="29" t="n">
         <f aca="false">COUNTIF(Artifacts!$N$2:$N$124,"●")</f>
@@ -6517,12 +6645,12 @@
         <v>OK</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" s="29" t="n">
         <f aca="false">COUNTIF(Artifacts!$O$2:$O$124,"●")</f>
@@ -6547,12 +6675,12 @@
         <v>OK</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="29" t="n">
         <f aca="false">COUNTIF(Artifacts!$P$2:$P$124,"●")</f>
@@ -6577,12 +6705,12 @@
         <v>OK</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" s="29" t="n">
         <f aca="false">COUNTIF(Artifacts!$Q$2:$Q$124,"●")</f>
@@ -6607,7 +6735,7 @@
         <v>OK</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6622,7 +6750,7 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">COUNTA(Artifacts!$C$2:$C$124)</f>
@@ -6637,7 +6765,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -6673,52 +6801,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="J1" s="27" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D2" s="17"/>
       <c r="E2" s="17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G2" s="17" t="n">
         <v>42.08</v>
@@ -6727,30 +6855,30 @@
         <v>-87.72</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>459</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3" s="17" t="s">
         <v>103</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>458</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>426</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>102</v>
       </c>
       <c r="G3" s="17" t="n">
         <v>38.97</v>
@@ -6759,30 +6887,30 @@
         <v>-95.24</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G4" s="17" t="n">
         <v>41.88</v>
@@ -6791,30 +6919,30 @@
         <v>-87.63</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>45.46</v>
@@ -6823,30 +6951,30 @@
         <v>9.19</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G6" s="17" t="n">
         <v>32.78</v>
@@ -6855,30 +6983,30 @@
         <v>-96.8</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>30.27</v>
@@ -6887,26 +7015,26 @@
         <v>-97.74</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="17" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>29.76</v>
@@ -6915,24 +7043,24 @@
         <v>-95.37</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J8" s="21"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="17" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>33.43</v>
@@ -6941,24 +7069,24 @@
         <v>-111.94</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="17" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G10" s="17" t="n">
         <v>32.76</v>
@@ -6967,28 +7095,28 @@
         <v>-97.33</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>40.81</v>
@@ -6997,28 +7125,28 @@
         <v>-96.7</v>
       </c>
       <c r="I11" s="21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G12" s="17" t="n">
         <v>39.57</v>
@@ -7027,28 +7155,28 @@
         <v>2.65</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J12" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>38.72</v>
@@ -7057,112 +7185,112 @@
         <v>-9.14</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J13" s="21"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
       <c r="I14" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G15" s="17"/>
       <c r="H15" s="17"/>
       <c r="I15" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J15" s="21" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
       <c r="I16" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J16" s="21" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>-22.97</v>
@@ -7171,58 +7299,58 @@
         <v>-43.18</v>
       </c>
       <c r="I17" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
       <c r="I18" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>26.71</v>
@@ -7231,28 +7359,28 @@
         <v>-80.04</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G20" s="17" t="n">
         <v>19.43</v>
@@ -7261,28 +7389,28 @@
         <v>-99.13</v>
       </c>
       <c r="I20" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J20" s="21"/>
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>41.89</v>
@@ -7291,46 +7419,46 @@
         <v>12.49</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
       <c r="I22" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J22" s="21"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -7363,36 +7491,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D2" s="32" t="n">
         <v>2026</v>
@@ -7401,19 +7529,19 @@
         <v>65</v>
       </c>
       <c r="F2" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G2" s="32"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="32" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D3" s="32" t="n">
         <v>2026</v>
@@ -7422,82 +7550,82 @@
         <v>64</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G3" s="32"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>267</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4" s="32"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>84</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G5" s="32"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>39</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G6" s="32"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>2024</v>
@@ -7506,19 +7634,19 @@
         <v>177</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7" s="32"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>2023</v>
@@ -7527,19 +7655,19 @@
         <v>106</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G8" s="32"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>2023</v>
@@ -7548,19 +7676,19 @@
         <v>39</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G9" s="32"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D10" s="32" t="n">
         <v>2022</v>
@@ -7569,19 +7697,19 @@
         <v>59</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G10" s="32"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D11" s="32" t="n">
         <v>2021</v>
@@ -7590,19 +7718,19 @@
         <v>59</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G11" s="32"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D12" s="32" t="n">
         <v>2022</v>
@@ -7611,13 +7739,13 @@
         <v>53</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G12" s="32"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D13" s="28" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E13" s="28" t="n">
         <f aca="false">SUM(E2:E12)</f>
@@ -7626,7 +7754,7 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D14" s="28" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E14" s="28" t="n">
         <f aca="false">COUNTIF(F2:F12,"Yes")</f>
@@ -7635,12 +7763,12 @@
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>
@@ -7659,22 +7787,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="70"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="32"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>507</v>
+        <v>451</v>
       </c>
       <c r="C1" s="27" t="s">
         <v>508</v>
@@ -7683,415 +7810,573 @@
         <v>509</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>459</v>
+      </c>
+      <c r="C2" s="33" t="s">
         <v>510</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="D2" s="33" t="s">
         <v>511</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="E2" s="33"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="33" t="s">
         <v>512</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="17" t="s">
+      <c r="C3" s="33" t="s">
+        <v>510</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E3" s="33"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>378</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>510</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E4" s="33"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="33" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="s">
-        <v>510</v>
-      </c>
-      <c r="B3" s="16" t="s">
+      <c r="C5" s="33" t="s">
         <v>514</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="D5" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E5" s="33"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="33" t="s">
         <v>515</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>510</v>
-      </c>
-      <c r="B4" s="16" t="s">
+      <c r="C6" s="33" t="s">
+        <v>514</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E6" s="33"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="33" t="s">
         <v>516</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C7" s="33" t="s">
+        <v>514</v>
+      </c>
+      <c r="D7" s="33" t="s">
         <v>517</v>
       </c>
-      <c r="D4" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
-        <v>510</v>
-      </c>
-      <c r="B5" s="16" t="s">
+      <c r="E7" s="33" t="s">
         <v>518</v>
       </c>
-      <c r="C5" s="17" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="33" t="s">
         <v>519</v>
       </c>
-      <c r="D5" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>510</v>
-      </c>
-      <c r="B6" s="16" t="s">
+      <c r="C8" s="33" t="s">
+        <v>514</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>517</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="33" t="s">
         <v>520</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C9" s="33" t="s">
+        <v>514</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>517</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="33" t="s">
         <v>521</v>
       </c>
-      <c r="D6" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
+      <c r="C10" s="33" t="s">
+        <v>514</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>517</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="33" t="s">
         <v>522</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="C11" s="33" t="s">
+        <v>514</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E11" s="33"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="33" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="33" t="s">
         <v>523</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C12" s="33" t="s">
         <v>524</v>
       </c>
-      <c r="D7" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="B8" s="16" t="s">
+      <c r="D12" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E12" s="33"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="33" t="s">
         <v>525</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C13" s="33" t="s">
+        <v>524</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E13" s="33"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="33" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="33" t="s">
         <v>526</v>
       </c>
-      <c r="D8" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="B9" s="16" t="s">
+      <c r="C14" s="33" t="s">
+        <v>524</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E14" s="33"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="33" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="33" t="s">
         <v>527</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C15" s="33" t="s">
+        <v>524</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E15" s="33"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="33" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>403</v>
+      </c>
+      <c r="C16" s="33" t="s">
         <v>528</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="B10" s="16" t="s">
+      <c r="D16" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="33" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>390</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>528</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E17" s="33" t="s">
         <v>529</v>
       </c>
-      <c r="C10" s="17" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="33" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>386</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>528</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="33" t="s">
         <v>530</v>
       </c>
-      <c r="D10" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="s">
+      <c r="C19" s="33" t="s">
+        <v>528</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="33" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="33" t="s">
         <v>531</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="C20" s="33" t="s">
+        <v>528</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="33" t="s">
         <v>532</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
-        <v>531</v>
-      </c>
-      <c r="B12" s="16" t="s">
+      <c r="C21" s="33" t="s">
         <v>533</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="D21" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E21" s="33"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="33" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="33" t="s">
+        <v>361</v>
+      </c>
+      <c r="C22" s="33" t="s">
         <v>534</v>
       </c>
-      <c r="D12" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="s">
-        <v>531</v>
-      </c>
-      <c r="B13" s="16" t="s">
+      <c r="D22" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="33" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="33" t="s">
+        <v>370</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="33" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="33" t="s">
+        <v>400</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="D24" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E24" s="33" t="s">
         <v>535</v>
       </c>
-      <c r="C13" s="17" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="33" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="33" t="s">
         <v>536</v>
       </c>
-      <c r="D13" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
-        <v>531</v>
-      </c>
-      <c r="B14" s="16" t="s">
+      <c r="C25" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="D25" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E25" s="33"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="33" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="33" t="s">
         <v>537</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C26" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E26" s="33"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="33" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="33" t="s">
         <v>538</v>
       </c>
-      <c r="D14" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17" t="s">
+      <c r="C27" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="D27" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E27" s="33"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="33" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="33" t="s">
         <v>539</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>539</v>
-      </c>
-      <c r="C15" s="17" t="s">
+      <c r="C28" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="D28" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E28" s="33"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="33" t="s">
         <v>540</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="s">
+      <c r="C29" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="D29" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E29" s="33"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="33" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="33" t="s">
         <v>541</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>541</v>
-      </c>
-      <c r="C16" s="17" t="s">
+      <c r="C30" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="D30" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E30" s="33"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="33" t="s">
         <v>542</v>
       </c>
-      <c r="D16" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="s">
+      <c r="C31" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="D31" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E31" s="33"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="33" t="s">
         <v>543</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="C32" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="D32" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E32" s="33"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="33" t="s">
         <v>544</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C33" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="D33" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E33" s="33"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="33" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="33" t="s">
         <v>545</v>
       </c>
-      <c r="D17" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="s">
-        <v>543</v>
-      </c>
-      <c r="B18" s="16" t="s">
+      <c r="C34" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="D34" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E34" s="33"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="33" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="33" t="s">
         <v>546</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C35" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="D35" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="E35" s="33"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="28" t="s">
+        <v>503</v>
+      </c>
+      <c r="C37" s="28" t="n">
+        <f aca="false">COUNTA(B2:B35)</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C38" s="1" t="n">
+        <f aca="false">COUNTIF(D2:D35,"Shaded")</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C39" s="1" t="n">
+        <f aca="false">COUNTIF(D2:D35,"Dot")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="31" t="s">
         <v>547</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
-        <v>543</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>548</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>549</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
-        <v>543</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>550</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>551</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="s">
-        <v>552</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>553</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>554</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>555</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17" t="s">
-        <v>557</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>558</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>559</v>
-      </c>
-      <c r="D22" s="21"/>
-      <c r="E22" s="17" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="s">
-        <v>557</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>560</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>561</v>
-      </c>
-      <c r="D23" s="21"/>
-      <c r="E23" s="17" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17" t="s">
-        <v>557</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>562</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>563</v>
-      </c>
-      <c r="D24" s="21"/>
-      <c r="E24" s="17" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>565</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>566</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="B26" s="35" t="s">
-        <v>568</v>
       </c>
     </row>
   </sheetData>
@@ -8110,6 +8395,457 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="27" t="s">
+        <v>548</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>549</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>550</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>551</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="17" t="s">
+        <v>552</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>553</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>554</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="17" t="s">
+        <v>552</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>556</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>557</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="17" t="s">
+        <v>552</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>559</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="s">
+        <v>552</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>560</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>561</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
+        <v>552</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>563</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="s">
+        <v>564</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>565</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>566</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="s">
+        <v>564</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>567</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>568</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="17" t="s">
+        <v>564</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>570</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>572</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="C11" s="17"/>
+      <c r="D11" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>575</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>577</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>578</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>579</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>580</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="17" t="s">
+        <v>581</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>581</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>582</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="s">
+        <v>583</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>583</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>584</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>586</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>587</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>588</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>589</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>590</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>591</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>592</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>593</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="s">
+        <v>594</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>595</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>596</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>597</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
+        <v>599</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>600</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="D22" s="21"/>
+      <c r="E22" s="17" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="17" t="s">
+        <v>599</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>603</v>
+      </c>
+      <c r="D23" s="21"/>
+      <c r="E23" s="17" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="s">
+        <v>599</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>604</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>605</v>
+      </c>
+      <c r="D24" s="21"/>
+      <c r="E24" s="17" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>607</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>608</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="B26" s="29" t="s">
+        <v>610</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:D22"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -8121,16 +8857,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>569</v>
+        <v>507</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>570</v>
+        <v>611</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>571</v>
+        <v>612</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>564</v>
+        <v>606</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8138,13 +8874,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>572</v>
+        <v>613</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>573</v>
+        <v>614</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8152,13 +8888,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>574</v>
+        <v>615</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>575</v>
+        <v>616</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>576</v>
+        <v>617</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8166,13 +8902,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>577</v>
+        <v>618</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>578</v>
+        <v>619</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>579</v>
+        <v>620</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8180,13 +8916,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>580</v>
+        <v>621</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>581</v>
+        <v>622</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>582</v>
+        <v>623</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8194,13 +8930,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>583</v>
+        <v>624</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>584</v>
+        <v>625</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>585</v>
+        <v>626</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8208,13 +8944,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>586</v>
+        <v>627</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>587</v>
+        <v>628</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8222,13 +8958,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>588</v>
+        <v>629</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>589</v>
+        <v>630</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>590</v>
+        <v>631</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8236,13 +8972,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>591</v>
+        <v>632</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>592</v>
+        <v>633</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8250,13 +8986,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>593</v>
+        <v>634</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>594</v>
+        <v>635</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>595</v>
+        <v>636</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8264,13 +9000,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>596</v>
+        <v>637</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>597</v>
+        <v>638</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>598</v>
+        <v>639</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8278,13 +9014,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>599</v>
+        <v>640</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>600</v>
+        <v>641</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8292,13 +9028,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>601</v>
+        <v>642</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>602</v>
+        <v>643</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>603</v>
+        <v>644</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8306,13 +9042,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>604</v>
+        <v>645</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>605</v>
+        <v>646</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>606</v>
+        <v>647</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8320,13 +9056,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>607</v>
+        <v>648</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>608</v>
+        <v>649</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>609</v>
+        <v>650</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8334,13 +9070,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>610</v>
+        <v>651</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>611</v>
+        <v>652</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>612</v>
+        <v>653</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8348,13 +9084,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>613</v>
+        <v>654</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>614</v>
+        <v>655</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8362,13 +9098,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>615</v>
+        <v>656</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>616</v>
+        <v>657</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8376,13 +9112,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>617</v>
+        <v>658</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>618</v>
+        <v>659</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>619</v>
+        <v>660</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8390,25 +9126,27 @@
         <v>19</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>620</v>
+        <v>661</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>578</v>
-      </c>
-      <c r="D20" s="21"/>
+        <v>619</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>662</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>621</v>
+        <v>663</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>622</v>
+        <v>664</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>623</v>
+        <v>665</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8416,13 +9154,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>624</v>
+        <v>666</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>625</v>
+        <v>667</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>626</v>
+        <v>668</v>
       </c>
     </row>
   </sheetData>

--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -88,7 +88,7 @@
     <t xml:space="preserve">Keep it uncluttered: personal context supports the work quietly, it never crowds it.</t>
   </si>
   <si>
-    <t xml:space="preserve">Latest decisions: one quiet line in About ("Based in Austin · English, Italian, learning Portuguese"), with Jaylee and Helga as one small sprite each beside it, not in the orbit. No languages on the Travel map; no sports on films or trips. The Travel map is small dots (lived, photos, worked), lines only for the moves between places lived, and the countries visited shaded.</t>
+    <t xml:space="preserve">Latest decisions: one quiet line in About ("Based in Austin · English, Italian, learning Portuguese"), with Jaylee and Helga as one small sprite each sitting on the 2021 ring (not a tile). No languages on the Travel map; no sports on films or trips. The Travel map is small dots (lived, photos, worked), lines only for the moves between places lived, and the countries visited shaded.</t>
   </si>
   <si>
     <t xml:space="preserve">Sheets</t>
@@ -1894,7 +1894,7 @@
     <t xml:space="preserve">Jaylee and Helga</t>
   </si>
   <si>
-    <t xml:space="preserve">Named, as one small sprite of each beside the quiet line in About (not in the orbit).</t>
+    <t xml:space="preserve">Named, as one small sprite of each sitting on the 2021 ring in About (name on hover), never as a tile.</t>
   </si>
   <si>
     <t xml:space="preserve">not sure how to diplay all the about profle stuff don’t want to make everythign to busy also!!</t>

--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -88,7 +88,7 @@
     <t xml:space="preserve">Keep it uncluttered: personal context supports the work quietly, it never crowds it.</t>
   </si>
   <si>
-    <t xml:space="preserve">Latest decisions: one quiet line in About ("Based in Austin · English, Italian, learning Portuguese"), with Jaylee and Helga as one small sprite each sitting on the 2021 ring (not a tile). No languages on the Travel map; no sports on films or trips. The Travel map is small dots (lived, photos, worked), lines only for the moves between places lived, and the countries visited shaded.</t>
+    <t xml:space="preserve">Latest decisions: one quiet line in About ("Based in Austin · English, Italian, learning Portuguese"), with Jaylee and Helga as one small sprite each sitting on the 2021 ring (not a tile). No languages on the Travel map; no sports on films or trips. The Travel map is small dots (lived, photos, worked; homes you also worked in get the worked square, Wilmette is marked born), lines only for the moves between places lived, the countries visited shaded, and it zooms and pans.</t>
   </si>
   <si>
     <t xml:space="preserve">Sheets</t>
@@ -1450,7 +1450,7 @@
     <t xml:space="preserve">USA</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirmed: before Lawrence</t>
+    <t xml:space="preserve">Confirmed: before Lawrence. Marked "born" on the map (phones say "Chicago · born")</t>
   </si>
   <si>
     <t xml:space="preserve">Confirmed</t>

--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -18,7 +18,7 @@
     <sheet name="Open questions" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Artifacts!$A$1:$W$64</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Artifacts!$A$1:$W$65</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="679">
   <si>
     <t xml:space="preserve">Site artifacts: mapping workbook</t>
   </si>
@@ -1138,6 +1138,30 @@
     <t xml:space="preserve">Python, Llama 3.x, fine-tuning, quantization, web scraping</t>
   </si>
   <si>
+    <t xml:space="preserve">A14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factory digital twin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal (verify)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital twin of a factory (details to come).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screen with real screenshot / 3D view</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maybe (it is a model)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What it models, tech, year, link, screenshots. Personal, or tied to an employer (confidential)?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your note in chat</t>
+  </si>
+  <si>
     <t xml:space="preserve">Films (35mm albums)</t>
   </si>
   <si>
@@ -2075,6 +2099,12 @@
   </si>
   <si>
     <t xml:space="preserve">$10M is fine: reverted to &gt;$10M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factory digital twin (A14): what does it model, what is it built with, when, is there a link or screenshots, and is it personal or tied to an employer?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A14, Apps</t>
   </si>
 </sst>
 </file>
@@ -2981,7 +3011,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W64"/>
+  <dimension ref="A1:W65"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
@@ -5452,107 +5482,97 @@
         <v>281</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="13" t="s">
+    <row r="46" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="14"/>
-      <c r="J46" s="14"/>
-      <c r="K46" s="14"/>
-      <c r="L46" s="14"/>
-      <c r="M46" s="14"/>
-      <c r="N46" s="14"/>
-      <c r="O46" s="14"/>
-      <c r="P46" s="14"/>
-      <c r="Q46" s="14"/>
-      <c r="R46" s="14"/>
-      <c r="S46" s="14"/>
-      <c r="T46" s="14"/>
-      <c r="U46" s="14"/>
-      <c r="V46" s="14"/>
-      <c r="W46" s="14"/>
-    </row>
-    <row r="47" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="15" t="s">
+      <c r="B46" s="16" t="s">
         <v>357</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="C46" s="17" t="s">
+        <v>271</v>
+      </c>
+      <c r="D46" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="E46" s="17"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="17" t="s">
         <v>359</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="20"/>
+      <c r="M46" s="19"/>
+      <c r="N46" s="20"/>
+      <c r="O46" s="20"/>
+      <c r="P46" s="20"/>
+      <c r="Q46" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="R46" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="S46" s="17" t="s">
         <v>360</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="T46" s="17" t="s">
         <v>361</v>
       </c>
-      <c r="F47" s="15" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G47" s="15" t="n">
-        <v>2026</v>
-      </c>
-      <c r="H47" s="17" t="s">
+      <c r="U46" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="V46" s="21" t="s">
         <v>362</v>
       </c>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17" t="s">
-        <v>360</v>
-      </c>
-      <c r="K47" s="17"/>
-      <c r="L47" s="20"/>
-      <c r="M47" s="20"/>
-      <c r="N47" s="20"/>
-      <c r="O47" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="P47" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q47" s="20"/>
-      <c r="R47" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="S47" s="17" t="s">
+      <c r="W46" s="17" t="s">
         <v>363</v>
       </c>
-      <c r="T47" s="17" t="s">
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="U47" s="17" t="s">
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="14"/>
+      <c r="L47" s="14"/>
+      <c r="M47" s="14"/>
+      <c r="N47" s="14"/>
+      <c r="O47" s="14"/>
+      <c r="P47" s="14"/>
+      <c r="Q47" s="14"/>
+      <c r="R47" s="14"/>
+      <c r="S47" s="14"/>
+      <c r="T47" s="14"/>
+      <c r="U47" s="14"/>
+      <c r="V47" s="14"/>
+      <c r="W47" s="14"/>
+    </row>
+    <row r="48" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="15" t="s">
         <v>365</v>
       </c>
-      <c r="V47" s="21" t="s">
+      <c r="B48" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="W47" s="17" t="s">
+      <c r="C48" s="17" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="15" t="s">
+      <c r="D48" s="17" t="s">
         <v>368</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="E48" s="17" t="s">
         <v>369</v>
-      </c>
-      <c r="C48" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="D48" s="17" t="s">
-        <v>360</v>
-      </c>
-      <c r="E48" s="17" t="s">
-        <v>370</v>
       </c>
       <c r="F48" s="15" t="n">
         <v>2026</v>
@@ -5561,11 +5581,11 @@
         <v>2026</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I48" s="17"/>
       <c r="J48" s="17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="K48" s="17"/>
       <c r="L48" s="20"/>
@@ -5582,49 +5602,49 @@
         <v>60</v>
       </c>
       <c r="S48" s="17" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="T48" s="17" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="U48" s="17" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="V48" s="21" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="W48" s="17" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="C49" s="17" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="15" t="s">
-        <v>372</v>
-      </c>
-      <c r="B49" s="16" t="s">
-        <v>373</v>
-      </c>
-      <c r="C49" s="17" t="s">
-        <v>359</v>
-      </c>
       <c r="D49" s="17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>374</v>
-      </c>
-      <c r="F49" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G49" s="15" t="s">
-        <v>53</v>
+        <v>378</v>
+      </c>
+      <c r="F49" s="15" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G49" s="15" t="n">
+        <v>2026</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="I49" s="17"/>
       <c r="J49" s="17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="K49" s="17"/>
       <c r="L49" s="20"/>
@@ -5641,36 +5661,36 @@
         <v>60</v>
       </c>
       <c r="S49" s="17" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="T49" s="17" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="U49" s="17" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="V49" s="21" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="W49" s="17" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>381</v>
+      </c>
+      <c r="C50" s="17" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="15" t="s">
-        <v>376</v>
-      </c>
-      <c r="B50" s="16" t="s">
-        <v>377</v>
-      </c>
-      <c r="C50" s="17" t="s">
-        <v>359</v>
-      </c>
       <c r="D50" s="17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F50" s="15" t="s">
         <v>53</v>
@@ -5679,11 +5699,11 @@
         <v>53</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="I50" s="17"/>
       <c r="J50" s="17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="K50" s="17"/>
       <c r="L50" s="20"/>
@@ -5700,36 +5720,36 @@
         <v>60</v>
       </c>
       <c r="S50" s="17" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="T50" s="17" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="U50" s="17" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="V50" s="21" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="W50" s="17" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="C51" s="17" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="15" t="s">
-        <v>380</v>
-      </c>
-      <c r="B51" s="16" t="s">
-        <v>381</v>
-      </c>
-      <c r="C51" s="17" t="s">
-        <v>359</v>
-      </c>
       <c r="D51" s="17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F51" s="15" t="s">
         <v>53</v>
@@ -5738,16 +5758,14 @@
         <v>53</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="I51" s="17"/>
       <c r="J51" s="17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="K51" s="17"/>
-      <c r="L51" s="18" t="s">
-        <v>59</v>
-      </c>
+      <c r="L51" s="20"/>
       <c r="M51" s="20"/>
       <c r="N51" s="20"/>
       <c r="O51" s="25" t="s">
@@ -5761,52 +5779,54 @@
         <v>60</v>
       </c>
       <c r="S51" s="17" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="T51" s="17" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="U51" s="17" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="V51" s="21" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="W51" s="17" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="C52" s="17" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="15" t="s">
-        <v>384</v>
-      </c>
-      <c r="B52" s="16" t="s">
-        <v>385</v>
-      </c>
-      <c r="C52" s="17" t="s">
-        <v>359</v>
-      </c>
       <c r="D52" s="17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>386</v>
-      </c>
-      <c r="F52" s="15" t="n">
-        <v>2024</v>
-      </c>
-      <c r="G52" s="15" t="n">
-        <v>2024</v>
+        <v>390</v>
+      </c>
+      <c r="F52" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G52" s="15" t="s">
+        <v>53</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="I52" s="17"/>
       <c r="J52" s="17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="K52" s="17"/>
-      <c r="L52" s="20"/>
+      <c r="L52" s="18" t="s">
+        <v>59</v>
+      </c>
       <c r="M52" s="20"/>
       <c r="N52" s="20"/>
       <c r="O52" s="25" t="s">
@@ -5820,49 +5840,49 @@
         <v>60</v>
       </c>
       <c r="S52" s="17" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="T52" s="17" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="U52" s="17" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="V52" s="21" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="W52" s="17" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H53" s="17" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="I53" s="17"/>
       <c r="J53" s="17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="K53" s="17"/>
       <c r="L53" s="20"/>
@@ -5879,36 +5899,36 @@
         <v>60</v>
       </c>
       <c r="S53" s="17" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="T53" s="17" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="U53" s="17" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="V53" s="21" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="W53" s="17" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F54" s="15" t="n">
         <v>2023</v>
@@ -5917,11 +5937,11 @@
         <v>2023</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="I54" s="17"/>
       <c r="J54" s="17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="K54" s="17"/>
       <c r="L54" s="20"/>
@@ -5938,49 +5958,49 @@
         <v>60</v>
       </c>
       <c r="S54" s="17" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="T54" s="17" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="U54" s="17" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="V54" s="21" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="W54" s="17" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H55" s="17" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="I55" s="17"/>
       <c r="J55" s="17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="K55" s="17"/>
       <c r="L55" s="20"/>
@@ -5997,49 +6017,49 @@
         <v>60</v>
       </c>
       <c r="S55" s="17" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="T55" s="17" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="U55" s="17" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="V55" s="21" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="W55" s="17" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="F56" s="15" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="I56" s="17"/>
       <c r="J56" s="17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="K56" s="17"/>
       <c r="L56" s="20"/>
@@ -6056,49 +6076,49 @@
         <v>60</v>
       </c>
       <c r="S56" s="17" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="T56" s="17" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="U56" s="17" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="V56" s="21" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="W56" s="17" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="15" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F57" s="15" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I57" s="17"/>
       <c r="J57" s="17" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="K57" s="17"/>
       <c r="L57" s="20"/>
@@ -6115,121 +6135,125 @@
         <v>60</v>
       </c>
       <c r="S57" s="17" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="T57" s="17" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="U57" s="17" t="s">
-        <v>365</v>
-      </c>
-      <c r="V57" s="21"/>
+        <v>373</v>
+      </c>
+      <c r="V57" s="21" t="s">
+        <v>374</v>
+      </c>
       <c r="W57" s="17" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="C58" s="17" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="14"/>
-      <c r="J58" s="14"/>
-      <c r="K58" s="14"/>
-      <c r="L58" s="14"/>
-      <c r="M58" s="14"/>
-      <c r="N58" s="14"/>
-      <c r="O58" s="14"/>
-      <c r="P58" s="14"/>
-      <c r="Q58" s="14"/>
-      <c r="R58" s="14"/>
-      <c r="S58" s="14"/>
-      <c r="T58" s="14"/>
-      <c r="U58" s="14"/>
-      <c r="V58" s="14"/>
-      <c r="W58" s="14"/>
-    </row>
-    <row r="59" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="15" t="s">
-        <v>406</v>
-      </c>
-      <c r="B59" s="16" t="s">
-        <v>407</v>
-      </c>
-      <c r="C59" s="17" t="s">
-        <v>408</v>
-      </c>
-      <c r="D59" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="E59" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="17" t="s">
-        <v>410</v>
-      </c>
-      <c r="I59" s="17"/>
-      <c r="J59" s="17"/>
-      <c r="K59" s="17"/>
-      <c r="L59" s="18" t="s">
+      <c r="D58" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="E58" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="F58" s="15" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G58" s="15" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H58" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="I58" s="17"/>
+      <c r="J58" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="K58" s="17"/>
+      <c r="L58" s="20"/>
+      <c r="M58" s="20"/>
+      <c r="N58" s="20"/>
+      <c r="O58" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="P58" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="M59" s="20"/>
-      <c r="N59" s="20"/>
-      <c r="O59" s="20"/>
-      <c r="P59" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q59" s="20"/>
-      <c r="R59" s="20" t="s">
+      <c r="Q58" s="20"/>
+      <c r="R58" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="S59" s="17" t="s">
-        <v>411</v>
-      </c>
-      <c r="T59" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="U59" s="17"/>
-      <c r="V59" s="21" t="s">
-        <v>412</v>
-      </c>
-      <c r="W59" s="17" t="s">
+      <c r="S58" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="T58" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="U58" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="V58" s="21"/>
+      <c r="W58" s="17" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="13" t="s">
         <v>413</v>
       </c>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
+      <c r="L59" s="14"/>
+      <c r="M59" s="14"/>
+      <c r="N59" s="14"/>
+      <c r="O59" s="14"/>
+      <c r="P59" s="14"/>
+      <c r="Q59" s="14"/>
+      <c r="R59" s="14"/>
+      <c r="S59" s="14"/>
+      <c r="T59" s="14"/>
+      <c r="U59" s="14"/>
+      <c r="V59" s="14"/>
+      <c r="W59" s="14"/>
     </row>
     <row r="60" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="s">
         <v>414</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>104</v>
+        <v>415</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="D60" s="17" t="s">
+        <v>417</v>
+      </c>
+      <c r="E60" s="17" t="s">
         <v>415</v>
       </c>
-      <c r="E60" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="F60" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="G60" s="15" t="s">
-        <v>88</v>
-      </c>
+      <c r="F60" s="15"/>
+      <c r="G60" s="15"/>
       <c r="H60" s="17" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="I60" s="17"/>
       <c r="J60" s="17"/>
@@ -6248,43 +6272,43 @@
         <v>60</v>
       </c>
       <c r="S60" s="17" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="T60" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U60" s="17"/>
       <c r="V60" s="21" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="W60" s="17" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="15" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="F61" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="G61" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="G61" s="15" t="s">
-        <v>80</v>
-      </c>
       <c r="H61" s="17" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="I61" s="17"/>
       <c r="J61" s="17"/>
@@ -6303,43 +6327,43 @@
         <v>60</v>
       </c>
       <c r="S61" s="17" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="T61" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U61" s="17"/>
       <c r="V61" s="21" t="s">
+        <v>425</v>
+      </c>
+      <c r="W61" s="17" t="s">
         <v>421</v>
-      </c>
-      <c r="W61" s="17" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="15" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F62" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="G62" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="G62" s="15" t="s">
-        <v>70</v>
-      </c>
       <c r="H62" s="17" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="I62" s="17"/>
       <c r="J62" s="17"/>
@@ -6358,43 +6382,43 @@
         <v>60</v>
       </c>
       <c r="S62" s="17" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="T62" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U62" s="17"/>
       <c r="V62" s="21" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="W62" s="17" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F63" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G63" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="G63" s="15" t="s">
-        <v>71</v>
-      </c>
       <c r="H63" s="17" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="I63" s="17"/>
       <c r="J63" s="17"/>
@@ -6413,43 +6437,43 @@
         <v>60</v>
       </c>
       <c r="S63" s="17" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="T63" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U63" s="17"/>
       <c r="V63" s="21" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="W63" s="17" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G64" s="15" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="I64" s="17"/>
       <c r="J64" s="17"/>
@@ -6468,21 +6492,76 @@
         <v>60</v>
       </c>
       <c r="S64" s="17" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="T64" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U64" s="17"/>
       <c r="V64" s="21" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="W64" s="17" t="s">
-        <v>413</v>
+        <v>421</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="B65" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="D65" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="E65" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F65" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G65" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="H65" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="I65" s="17"/>
+      <c r="J65" s="17"/>
+      <c r="K65" s="17"/>
+      <c r="L65" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="M65" s="20"/>
+      <c r="N65" s="20"/>
+      <c r="O65" s="20"/>
+      <c r="P65" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q65" s="20"/>
+      <c r="R65" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="S65" s="17" t="s">
+        <v>419</v>
+      </c>
+      <c r="T65" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="U65" s="17"/>
+      <c r="V65" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="W65" s="17" t="s">
+        <v>421</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W64"/>
+  <autoFilter ref="A1:W65"/>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L2:Q124" type="list">
       <formula1>"●,○"</formula1>
@@ -6534,28 +6613,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6585,7 +6664,7 @@
         <v>Add</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6615,7 +6694,7 @@
         <v>OK</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6645,7 +6724,7 @@
         <v>OK</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6675,7 +6754,7 @@
         <v>OK</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6705,7 +6784,7 @@
         <v>OK</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6714,15 +6793,15 @@
       </c>
       <c r="B7" s="29" t="n">
         <f aca="false">COUNTIF(Artifacts!$Q$2:$Q$124,"●")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="29" t="n">
         <f aca="false">COUNTIF(Artifacts!$Q$2:$Q$124,"●")+COUNTIF(Artifacts!$Q$2:$Q$124,"○")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" s="29" t="n">
         <f aca="false">COUNTIFS(Artifacts!$Q$2:$Q$124,"●",Artifacts!$R$2:$R$124,"Yes")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" s="30" t="n">
         <v>2</v>
@@ -6732,10 +6811,10 @@
       </c>
       <c r="G7" s="29" t="str">
         <f aca="false">IF(D7&lt;E7,"Add",IF(D7&gt;F7,"Trim","OK"))</f>
-        <v>OK</v>
+        <v>Trim</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6750,11 +6829,11 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">COUNTA(Artifacts!$C$2:$C$124)</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C9" s="29"/>
       <c r="D9" s="29"/>
@@ -6765,7 +6844,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -6801,52 +6880,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="J1" s="27" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="D2" s="17"/>
       <c r="E2" s="17" t="s">
         <v>105</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="G2" s="17" t="n">
         <v>42.08</v>
@@ -6858,7 +6937,7 @@
         <v>60</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6866,10 +6945,10 @@
         <v>104</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>105</v>
@@ -6890,7 +6969,7 @@
         <v>60</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6898,10 +6977,10 @@
         <v>87</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="D4" s="17" t="s">
         <v>88</v>
@@ -6910,7 +6989,7 @@
         <v>80</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="G4" s="17" t="n">
         <v>41.88</v>
@@ -6922,18 +7001,18 @@
         <v>60</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>80</v>
@@ -6942,7 +7021,7 @@
         <v>70</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>45.46</v>
@@ -6954,7 +7033,7 @@
         <v>60</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6962,10 +7041,10 @@
         <v>69</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>70</v>
@@ -6974,7 +7053,7 @@
         <v>53</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="G6" s="17" t="n">
         <v>32.78</v>
@@ -6986,7 +7065,7 @@
         <v>60</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6994,10 +7073,10 @@
         <v>52</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>53</v>
@@ -7006,7 +7085,7 @@
         <v>54</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>30.27</v>
@@ -7018,7 +7097,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7026,15 +7105,15 @@
         <v>142</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="17" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>29.76</v>
@@ -7052,15 +7131,15 @@
         <v>153</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="17" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>33.43</v>
@@ -7078,15 +7157,15 @@
         <v>213</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="17" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="G10" s="17" t="n">
         <v>32.76</v>
@@ -7101,13 +7180,13 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>88</v>
@@ -7116,7 +7195,7 @@
         <v>88</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>40.81</v>
@@ -7131,22 +7210,22 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="G12" s="17" t="n">
         <v>39.57</v>
@@ -7161,22 +7240,22 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>38.72</v>
@@ -7191,13 +7270,13 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>53</v>
@@ -7206,7 +7285,7 @@
         <v>53</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
@@ -7214,18 +7293,18 @@
         <v>60</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>53</v>
@@ -7234,7 +7313,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="G15" s="17"/>
       <c r="H15" s="17"/>
@@ -7242,18 +7321,18 @@
         <v>60</v>
       </c>
       <c r="J15" s="21" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>53</v>
@@ -7262,7 +7341,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
@@ -7270,18 +7349,18 @@
         <v>60</v>
       </c>
       <c r="J16" s="21" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>71</v>
@@ -7290,7 +7369,7 @@
         <v>71</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>-22.97</v>
@@ -7302,27 +7381,27 @@
         <v>60</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
@@ -7330,27 +7409,27 @@
         <v>60</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>26.71</v>
@@ -7365,13 +7444,13 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D20" s="17" t="s">
         <v>191</v>
@@ -7380,7 +7459,7 @@
         <v>191</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="G20" s="17" t="n">
         <v>19.43</v>
@@ -7395,13 +7474,13 @@
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D21" s="17" t="s">
         <v>70</v>
@@ -7410,7 +7489,7 @@
         <v>70</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>41.89</v>
@@ -7422,18 +7501,18 @@
         <v>60</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D22" s="17" t="s">
         <v>191</v>
@@ -7442,7 +7521,7 @@
         <v>191</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
@@ -7453,12 +7532,12 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>
@@ -7494,33 +7573,33 @@
         <v>24</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="F1" s="27" t="s">
         <v>41</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="D2" s="32" t="n">
         <v>2026</v>
@@ -7535,13 +7614,13 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="32" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="D3" s="32" t="n">
         <v>2026</v>
@@ -7556,13 +7635,13 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>53</v>
@@ -7577,13 +7656,13 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>53</v>
@@ -7598,13 +7677,13 @@
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="D6" s="32" t="s">
         <v>53</v>
@@ -7619,13 +7698,13 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>2024</v>
@@ -7640,13 +7719,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>2023</v>
@@ -7661,13 +7740,13 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>2023</v>
@@ -7682,13 +7761,13 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="D10" s="32" t="n">
         <v>2022</v>
@@ -7703,13 +7782,13 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="D11" s="32" t="n">
         <v>2021</v>
@@ -7724,13 +7803,13 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="D12" s="32" t="n">
         <v>2022</v>
@@ -7745,7 +7824,7 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D13" s="28" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="E13" s="28" t="n">
         <f aca="false">SUM(E2:E12)</f>
@@ -7754,7 +7833,7 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D14" s="28" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="E14" s="28" t="n">
         <f aca="false">COUNTIF(F2:F12,"Yes")</f>
@@ -7763,12 +7842,12 @@
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -7798,19 +7877,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7818,13 +7897,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E2" s="33"/>
     </row>
@@ -7833,13 +7912,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E3" s="33"/>
     </row>
@@ -7848,13 +7927,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E4" s="33"/>
     </row>
@@ -7863,13 +7942,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E5" s="33"/>
     </row>
@@ -7878,13 +7957,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E6" s="33"/>
     </row>
@@ -7893,16 +7972,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7910,16 +7989,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7927,16 +8006,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7944,16 +8023,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7961,13 +8040,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="33" t="s">
+        <v>530</v>
+      </c>
+      <c r="C11" s="33" t="s">
         <v>522</v>
       </c>
-      <c r="C11" s="33" t="s">
-        <v>514</v>
-      </c>
       <c r="D11" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E11" s="33"/>
     </row>
@@ -7976,13 +8055,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E12" s="33"/>
     </row>
@@ -7991,13 +8070,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E13" s="33"/>
     </row>
@@ -8006,13 +8085,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E14" s="33"/>
     </row>
@@ -8021,13 +8100,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E15" s="33"/>
     </row>
@@ -8036,16 +8115,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8053,16 +8132,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8070,16 +8149,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8087,16 +8166,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8104,16 +8183,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8121,13 +8200,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E21" s="33"/>
     </row>
@@ -8136,16 +8215,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8153,16 +8232,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8170,16 +8249,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8187,13 +8266,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E25" s="33"/>
     </row>
@@ -8202,13 +8281,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E26" s="33"/>
     </row>
@@ -8217,13 +8296,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E27" s="33"/>
     </row>
@@ -8232,13 +8311,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E28" s="33"/>
     </row>
@@ -8247,13 +8326,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E29" s="33"/>
     </row>
@@ -8262,13 +8341,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E30" s="33"/>
     </row>
@@ -8277,13 +8356,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="33" t="s">
+        <v>550</v>
+      </c>
+      <c r="C31" s="33" t="s">
         <v>542</v>
       </c>
-      <c r="C31" s="33" t="s">
-        <v>534</v>
-      </c>
       <c r="D31" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E31" s="33"/>
     </row>
@@ -8292,13 +8371,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E32" s="33"/>
     </row>
@@ -8307,13 +8386,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E33" s="33"/>
     </row>
@@ -8322,13 +8401,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E34" s="33"/>
     </row>
@@ -8337,19 +8416,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E35" s="33"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="28" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="C37" s="28" t="n">
         <f aca="false">COUNTA(B2:B35)</f>
@@ -8358,7 +8437,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="C38" s="1" t="n">
         <f aca="false">COUNTIF(D2:D35,"Shaded")</f>
@@ -8367,7 +8446,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="1" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="C39" s="1" t="n">
         <f aca="false">COUNTIF(D2:D35,"Dot")</f>
@@ -8376,7 +8455,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>
@@ -8407,16 +8486,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="E1" s="27" t="s">
         <v>46</v>
@@ -8424,98 +8503,98 @@
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>60</v>
@@ -8526,13 +8605,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>60</v>
@@ -8543,19 +8622,19 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8563,110 +8642,110 @@
         <v>247</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="D13" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>60</v>
@@ -8677,13 +8756,13 @@
     </row>
     <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>60</v>
@@ -8694,13 +8773,13 @@
     </row>
     <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>60</v>
@@ -8711,13 +8790,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>60</v>
@@ -8728,13 +8807,13 @@
     </row>
     <row r="20" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>60</v>
@@ -8745,64 +8824,64 @@
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="D22" s="21"/>
       <c r="E22" s="17" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="17" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="D24" s="21"/>
       <c r="E24" s="17" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8810,24 +8889,24 @@
         <v>247</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="D25" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
     </row>
   </sheetData>
@@ -8846,7 +8925,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
@@ -8857,16 +8936,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8874,10 +8953,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>60</v>
@@ -8888,13 +8967,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8902,13 +8981,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8916,13 +8995,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8930,13 +9009,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8944,13 +9023,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>206</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8958,13 +9037,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8972,13 +9051,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>177</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8986,13 +9065,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9000,13 +9079,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9014,13 +9093,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>233</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9028,13 +9107,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9042,13 +9121,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9056,13 +9135,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9070,13 +9149,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9084,13 +9163,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9098,13 +9177,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9112,13 +9191,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9126,13 +9205,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9140,13 +9219,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9154,14 +9233,26 @@
         <v>21</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>668</v>
-      </c>
+        <v>676</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>677</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>678</v>
+      </c>
+      <c r="D23" s="21"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="682">
   <si>
     <t xml:space="preserve">Site artifacts: mapping workbook</t>
   </si>
@@ -259,576 +259,582 @@
     <t xml:space="preserve">No</t>
   </si>
   <si>
+    <t xml:space="preserve">Enovis logo (in repo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What can be shown publicly about Enovis work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPEI Corp: Project Engineering Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPEI Corp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallas, TX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Industrial construction and manufacturing capital projects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;$30M of capital projects (mechanical, electrical, process piping, equipment). See E3–E7.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolidWorks, AutoCAD, MS Project, P&amp;IDs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio pages 4–5; MAPEI logo (in repo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPEI SpA: Project Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPEI SpA (HQ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milan, Italy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trained across day-to-day manufacturing operations; capital projects; static mixing R&amp;D.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supported design, prototyping and testing of new static mixing technology (became E6).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timeline card + Milan on map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPEI logo (in repo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any photos from Milan / the plant?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPEI Corp: Junior Project Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chicago, IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical studies and medium-scale capital projects for the Chicago site.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Process improvement and infrastructure upgrades.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maybe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWC Industries: Mechanical Engineering Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWC Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer internship designing components and assemblies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cut raw-material waste with design-for-manufacture parts; designed replacement parts to prevent downtime.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolidWorks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B.S. Mechanical Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Kansas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lawrence, KS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSME.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula SAE electric powertrain (U1); biomechanical research (U2); SAE and Society of Biomedical Engineering.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMP certification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Management Professional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Badge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not on the site (this is not a resume).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOA Board Director</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leadership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercer Square Condominium Association</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Board director for a condominium association.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line in About</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional engineering projects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations facility build-out (200K sq ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End-to-end design and construction of a facility combining office, automated distribution, clean pack, sterilization and additive manufacturing, as owner rep.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200K sq ft; budget &gt;$10M; major utilities, equipment integration, controls, life safety; next-phase expansion and capacity planning; lean / continuous improvement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design-build delivery, commissioning, validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miniature diorama of the building</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate (simple diorama)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public-safe photos or layouts? NDA limits?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Industrial additive manufacturing center (EBM + SLS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built out an AM center with EBM and SLS systems for patient-specific implants.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilities, equipment siting, install sequencing, material-flow layout, production validation; scalable workflows aligned with regulatory, quality and environmental standards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBM, SLS, process validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printer / lattice part</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate (generic lattice, no real implant)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What can be shown (medical device confidentiality).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated dry mix production plant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPEI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houston, TX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ground-up automated dry mix production and packaging plant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">European / North American vendors; Italian electrical contractors for power and automation; air permitting and FAA approval; delivered on budget and schedule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolidWorks, AutoCAD, P&amp;IDs, commissioning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silo tower (strong hero)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Have CAD (render in portfolio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.4: elevation, P&amp;ID, 3D render, tower photo, interior photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dates: placeholder for now.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robotic palletizer and bag applicator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tempe, AZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added automated robotic palletizing and bag application to an existing dry mix plant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doubled the plant's total output capacity; removed two manual operations; prefab kept downtime minimal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolidWorks, AutoCAD, MS Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robot cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Have vendor render (portfolio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.4: render + photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site development: 315K sq ft brownfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houston, TX (from Dallas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turned a speculative brownfield building into a full production and distribution facility.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315K sq ft; design-build; vendor selection and contracts; multiple concurrent projects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS Project, design-build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building / diorama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.5: building photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lived in Dallas, travelled to Houston for this project. Dates: placeholder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-line static mixing process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milan → Dallas, TX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First production version of a new static mixing technology, prototyped in Milan and built in Dallas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production time −35%; manual operations removed; enabled bulk material purchasing; equipment procured from Europe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">European vendors, electromechanical contractors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixing skid (prototype → production story)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.5: drawing, 3D render, photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquid admixtures plant expansion ($5M)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX (verify)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plant expansion introducing automated blending and bulk transfer systems to the Southern U.S.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$5M; design, construction, commissioning and lifecycle management.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Process automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Process skid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You have photos (to send)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Startup: OnlyChargeEV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnlyChargeEV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallas, TX (Austin, Houston, San Antonio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial EV charging service company across major Texas hubs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partners: ChargePoint, Ford Pro, Xeal Energy, Verdek. Commercial, fleet and multifamily clients. Automated payments, accounting, compliance, estimating and proposals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRM automation, email campaigns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charger pedestal + Texas map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate (charger)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio pp.2–3; OnlyChargeEV logo (in repo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logo coming; use a lightning-bolt placeholder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FedEx Office HQ workplace charging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV install</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modernized workplace charging for FedEx Office HQ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 Enel X JuiceBox Pro 40 L2 chargers on dual stands (4 replaced + 4 added = 8 ports); trenching, concrete, electrical; permits.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Case inside S1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.2: site plan + photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stallion Infrastructure Services fleet charging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fleet charging across a company campus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 Ford Pro 11.5 kW (80A) wall-mounted L2 chargers; conduit, wiring, bollards; permitting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.2: photos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University multi-use commercial garage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fort Worth, TX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential charging in a new multifamily parking garage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 Xeal (32A) L2 chargers; power sharing to avoid electrical upgrades; commissioning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.3: plan + photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gateway Cedars multifamily</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charging for a multifamily development.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two dual-port ChargePoint CT4000 units (4 ports); electrical upgrades; permitting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.3: aerial plan + photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University projects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula SAE electric racecar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electric powertrain for KU's Formula SAE electric racecar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Led 5 electrical engineers; in-house motor controller; battery storage and management system; raced at Formula SAE Electric (Lincoln, NE).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolidWorks, MATLAB, FEA, 3D printing, CNC, laser, water jet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Racecar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.6: car render, controller and PCB photos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAD file? Race results?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assistive piano-pedal device</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KU biomechanical research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assistive devices that let a paraplegic pianist operate piano pedals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Played piano pedals for the first time; two additive prototypes, final part machined; team of 4; national news coverage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolidWorks, 3D printing, CNC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedal device</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Have CAD (renders in portfolio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.6: renders, photos, news still</t>
+  </si>
+  <si>
+    <t xml:space="preserve">News links: dummy placeholders until you send real ones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maker builds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resin Light 1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maker build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First functional prototype of the Resin Lights: illuminated art and lighting pieces that combine cast resin with integrated LED lighting, the resin acting as both the visual material and the diffuser, so the object glows instead of exposing a fixture.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built to test the concept and learn how materials, lighting and fabrication behave in practice: resin casting technique, mold design, LED placement, diffusion, brightness, heat management, structure, surface finish, assembly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mold making, resin casting, LED integration, thermal and electrical design, fabrication, finishing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Object photo or 3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate from photos</t>
+  </si>
+  <si>
     <t xml:space="preserve">None yet</t>
   </si>
   <si>
-    <t xml:space="preserve">What can be shown publicly about Enovis work.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPEI Corp: Project Engineering Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPEI Corp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallas, TX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Industrial construction and manufacturing capital projects.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt;$30M of capital projects (mechanical, electrical, process piping, equipment). See E3–E7.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolidWorks, AutoCAD, MS Project, P&amp;IDs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio pages 4–5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPEI SpA: Project Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPEI SpA (HQ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milan, Italy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trained across day-to-day manufacturing operations; capital projects; static mixing R&amp;D.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supported design, prototyping and testing of new static mixing technology (became E6).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timeline card + Milan on map</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any photos from Milan / the plant?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPEI Corp: Junior Project Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chicago, IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical studies and medium-scale capital projects for the Chicago site.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Process improvement and infrastructure upgrades.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maybe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWC Industries: Mechanical Engineering Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWC Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summer internship designing components and assemblies.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cut raw-material waste with design-for-manufacture parts; designed replacement parts to prevent downtime.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolidWorks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B.S. Mechanical Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Education</t>
-  </si>
-  <si>
-    <t xml:space="preserve">University of Kansas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lawrence, KS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSME.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formula SAE electric powertrain (U1); biomechanical research (U2); SAE and Society of Biomedical Engineering.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PMP certification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project Management Professional.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Badge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not on the site (this is not a resume).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOA Board Director</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leadership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mercer Square Condominium Association</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Board director for a condominium association.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Line in About</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Professional engineering projects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations facility build-out (200K sq ft)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End-to-end design and construction of a facility combining office, automated distribution, clean pack, sterilization and additive manufacturing, as owner rep.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200K sq ft; budget &gt;$10M; major utilities, equipment integration, controls, life safety; next-phase expansion and capacity planning; lean / continuous improvement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design-build delivery, commissioning, validation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miniature diorama of the building</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate (simple diorama)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public-safe photos or layouts? NDA limits?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Industrial additive manufacturing center (EBM + SLS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built out an AM center with EBM and SLS systems for patient-specific implants.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utilities, equipment siting, install sequencing, material-flow layout, production validation; scalable workflows aligned with regulatory, quality and environmental standards.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EBM, SLS, process validation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printer / lattice part</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate (generic lattice, no real implant)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What can be shown (medical device confidentiality).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automated dry mix production plant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPEI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Houston, TX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ground-up automated dry mix production and packaging plant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">European / North American vendors; Italian electrical contractors for power and automation; air permitting and FAA approval; delivered on budget and schedule.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolidWorks, AutoCAD, P&amp;IDs, commissioning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silo tower (strong hero)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Have CAD (render in portfolio)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.4: elevation, P&amp;ID, 3D render, tower photo, interior photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dates: placeholder for now.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robotic palletizer and bag applicator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tempe, AZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added automated robotic palletizing and bag application to an existing dry mix plant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doubled the plant's total output capacity; removed two manual operations; prefab kept downtime minimal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolidWorks, AutoCAD, MS Project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robot cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Have vendor render (portfolio)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.4: render + photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site development: 315K sq ft brownfield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Houston, TX (from Dallas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turned a speculative brownfield building into a full production and distribution facility.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315K sq ft; design-build; vendor selection and contracts; multiple concurrent projects.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS Project, design-build</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Building / diorama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.5: building photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lived in Dallas, travelled to Houston for this project. Dates: placeholder.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-line static mixing process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milan → Dallas, TX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First production version of a new static mixing technology, prototyped in Milan and built in Dallas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production time −35%; manual operations removed; enabled bulk material purchasing; equipment procured from Europe.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">European vendors, electromechanical contractors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mixing skid (prototype → production story)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.5: drawing, 3D render, photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liquid admixtures plant expansion ($5M)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TX (verify)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plant expansion introducing automated blending and bulk transfer systems to the Southern U.S.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$5M; design, construction, commissioning and lifecycle management.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Process automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Process skid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You have photos (to send)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Startup: OnlyChargeEV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnlyChargeEV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Founder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallas, TX (Austin, Houston, San Antonio)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial EV charging service company across major Texas hubs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partners: ChargePoint, Ford Pro, Xeal Energy, Verdek. Commercial, fleet and multifamily clients. Automated payments, accounting, compliance, estimating and proposals.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRM automation, email campaigns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charger pedestal + Texas map</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate (charger)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio pp.2–3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logo coming; use a lightning-bolt placeholder.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S1a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FedEx Office HQ workplace charging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EV install</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modernized workplace charging for FedEx Office HQ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 Enel X JuiceBox Pro 40 L2 chargers on dual stands (4 replaced + 4 added = 8 ports); trenching, concrete, electrical; permits.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Case inside S1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.2: site plan + photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S1b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stallion Infrastructure Services fleet charging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fleet charging across a company campus.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 Ford Pro 11.5 kW (80A) wall-mounted L2 chargers; conduit, wiring, bollards; permitting.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.2: photos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S1c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">University multi-use commercial garage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fort Worth, TX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential charging in a new multifamily parking garage.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 Xeal (32A) L2 chargers; power sharing to avoid electrical upgrades; commissioning.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.3: plan + photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S1d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gateway Cedars multifamily</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charging for a multifamily development.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two dual-port ChargePoint CT4000 units (4 ports); electrical upgrades; permitting.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.3: aerial plan + photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">University projects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formula SAE electric racecar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">University project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electric powertrain for KU's Formula SAE electric racecar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Led 5 electrical engineers; in-house motor controller; battery storage and management system; raced at Formula SAE Electric (Lincoln, NE).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolidWorks, MATLAB, FEA, 3D printing, CNC, laser, water jet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Racecar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.6: car render, controller and PCB photos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAD file? Race results?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assistive piano-pedal device</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KU biomechanical research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assistive devices that let a paraplegic pianist operate piano pedals.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Played piano pedals for the first time; two additive prototypes, final part machined; team of 4; national news coverage.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolidWorks, 3D printing, CNC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pedal device</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Have CAD (renders in portfolio)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.6: renders, photos, news still</t>
-  </si>
-  <si>
-    <t xml:space="preserve">News links: dummy placeholders until you send real ones.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maker builds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resin Light 1.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maker build</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First functional prototype of the Resin Lights: illuminated art and lighting pieces that combine cast resin with integrated LED lighting, the resin acting as both the visual material and the diffuser, so the object glows instead of exposing a fixture.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built to test the concept and learn how materials, lighting and fabrication behave in practice: resin casting technique, mold design, LED placement, diffusion, brightness, heat management, structure, surface finish, assembly.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mold making, resin casting, LED integration, thermal and electrical design, fabrication, finishing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Object photo or 3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate from photos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Photos coming.</t>
   </si>
   <si>
@@ -907,28 +913,31 @@
     <t xml:space="preserve">No (screen)</t>
   </si>
   <si>
+    <t xml:space="preserve">Live site; app icon (redrawn from your screenshot: send the original file)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screenshot / short screen recording.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apps table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobPaper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChatGPT app that turns contractor notes and photos into estimates, change orders and job reports, with editable documents and PDF export.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TypeScript, MCP, ChatGPT Apps, jsPDF, Vercel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-paper.vercel.app</t>
+  </si>
+  <si>
     <t xml:space="preserve">Live site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Screenshot / short screen recording.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apps table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobPaper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChatGPT app that turns contractor notes and photos into estimates, change orders and job reports, with editable documents and PDF export.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TypeScript, MCP, ChatGPT Apps, jsPDF, Vercel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-paper.vercel.app</t>
   </si>
   <si>
     <t xml:space="preserve">A3</t>
@@ -3307,10 +3316,10 @@
         <v>62</v>
       </c>
       <c r="U5" s="17" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="V5" s="21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W5" s="17" t="s">
         <v>65</v>
@@ -3318,10 +3327,10 @@
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>50</v>
@@ -3330,19 +3339,19 @@
         <v>68</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G6" s="15" t="s">
         <v>80</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
@@ -3355,7 +3364,7 @@
       <c r="P6" s="20"/>
       <c r="Q6" s="20"/>
       <c r="R6" s="20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="S6" s="17" t="s">
         <v>61</v>
@@ -3364,7 +3373,7 @@
         <v>62</v>
       </c>
       <c r="U6" s="17" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="V6" s="21"/>
       <c r="W6" s="17" t="s">
@@ -3385,7 +3394,7 @@
         <v>95</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>96</v>
@@ -3412,7 +3421,7 @@
       <c r="P7" s="20"/>
       <c r="Q7" s="20"/>
       <c r="R7" s="20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="S7" s="17" t="s">
         <v>61</v>
@@ -3421,7 +3430,7 @@
         <v>62</v>
       </c>
       <c r="U7" s="17" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="V7" s="21"/>
       <c r="W7" s="17" t="s">
@@ -3430,31 +3439,31 @@
     </row>
     <row r="8" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
@@ -3478,7 +3487,7 @@
         <v>62</v>
       </c>
       <c r="U8" s="17" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="V8" s="21"/>
       <c r="W8" s="17" t="s">
@@ -3487,22 +3496,22 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E9" s="17"/>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
       <c r="H9" s="17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
@@ -3519,16 +3528,16 @@
         <v>62</v>
       </c>
       <c r="S9" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T9" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="V9" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="W9" s="17" t="s">
         <v>65</v>
@@ -3536,22 +3545,22 @@
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E10" s="17"/>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
       <c r="H10" s="17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
@@ -3568,16 +3577,16 @@
         <v>62</v>
       </c>
       <c r="S10" s="17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="T10" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="V10" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="W10" s="17" t="s">
         <v>65</v>
@@ -3585,7 +3594,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
@@ -3612,13 +3621,13 @@
     </row>
     <row r="12" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>51</v>
@@ -3633,13 +3642,13 @@
         <v>54</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K12" s="17"/>
       <c r="L12" s="18" t="s">
@@ -3658,16 +3667,16 @@
         <v>60</v>
       </c>
       <c r="S12" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="U12" s="17" t="s">
         <v>63</v>
       </c>
       <c r="V12" s="21" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="W12" s="17" t="s">
         <v>65</v>
@@ -3675,13 +3684,13 @@
     </row>
     <row r="13" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D13" s="17" t="s">
         <v>51</v>
@@ -3696,13 +3705,13 @@
         <v>54</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K13" s="17"/>
       <c r="L13" s="20"/>
@@ -3719,16 +3728,16 @@
         <v>60</v>
       </c>
       <c r="S13" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="U13" s="17" t="s">
         <v>63</v>
       </c>
       <c r="V13" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="W13" s="17" t="s">
         <v>65</v>
@@ -3736,30 +3745,30 @@
     </row>
     <row r="14" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K14" s="17"/>
       <c r="L14" s="20"/>
@@ -3778,47 +3787,47 @@
         <v>60</v>
       </c>
       <c r="S14" s="17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="T14" s="17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="U14" s="17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="V14" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="W14" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
       <c r="H15" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I15" s="17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J15" s="17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="20"/>
@@ -3835,47 +3844,47 @@
         <v>60</v>
       </c>
       <c r="S15" s="17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T15" s="17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="U15" s="17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="V15" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="W15" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
       <c r="H16" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K16" s="17"/>
       <c r="L16" s="20"/>
@@ -3892,49 +3901,49 @@
         <v>60</v>
       </c>
       <c r="S16" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="V16" s="21" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="W16" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>80</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="20"/>
@@ -3953,47 +3962,47 @@
         <v>60</v>
       </c>
       <c r="S17" s="17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="V17" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="W17" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
       <c r="H18" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K18" s="17"/>
       <c r="L18" s="20"/>
@@ -4008,16 +4017,16 @@
         <v>60</v>
       </c>
       <c r="S18" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="V18" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="W18" s="17" t="s">
         <v>65</v>
@@ -4025,7 +4034,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -4052,34 +4061,34 @@
     </row>
     <row r="20" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G20" s="15" t="s">
         <v>71</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K20" s="17"/>
       <c r="L20" s="18" t="s">
@@ -4102,16 +4111,16 @@
         <v>60</v>
       </c>
       <c r="S20" s="17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="V20" s="21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="W20" s="17" t="s">
         <v>65</v>
@@ -4119,16 +4128,16 @@
     </row>
     <row r="21" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>69</v>
@@ -4136,10 +4145,10 @@
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
       <c r="H21" s="17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
@@ -4154,45 +4163,45 @@
       <c r="P21" s="20"/>
       <c r="Q21" s="20"/>
       <c r="R21" s="20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="S21" s="17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="T21" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U21" s="17" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="V21" s="21"/>
       <c r="W21" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
       <c r="H22" s="17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J22" s="17"/>
       <c r="K22" s="17"/>
@@ -4207,45 +4216,45 @@
       <c r="P22" s="20"/>
       <c r="Q22" s="20"/>
       <c r="R22" s="20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="S22" s="17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="T22" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U22" s="17" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="V22" s="21"/>
       <c r="W22" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
       <c r="H23" s="17" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
@@ -4260,34 +4269,34 @@
       <c r="P23" s="20"/>
       <c r="Q23" s="20"/>
       <c r="R23" s="20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="S23" s="17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="T23" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U23" s="17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="V23" s="21"/>
       <c r="W23" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>69</v>
@@ -4295,10 +4304,10 @@
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
       <c r="H24" s="17" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J24" s="17"/>
       <c r="K24" s="17"/>
@@ -4313,25 +4322,25 @@
       <c r="P24" s="20"/>
       <c r="Q24" s="20"/>
       <c r="R24" s="20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="S24" s="17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="T24" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U24" s="17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="V24" s="21"/>
       <c r="W24" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -4358,34 +4367,34 @@
     </row>
     <row r="26" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K26" s="17"/>
       <c r="L26" s="18" t="s">
@@ -4404,51 +4413,51 @@
         <v>60</v>
       </c>
       <c r="S26" s="17" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="T26" s="17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="U26" s="17" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="V26" s="21" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="W26" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F27" s="15" t="s">
         <v>96</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K27" s="17"/>
       <c r="L27" s="18" t="s">
@@ -4467,24 +4476,24 @@
         <v>60</v>
       </c>
       <c r="S27" s="17" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="T27" s="17" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="U27" s="17" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="V27" s="21" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="W27" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -4511,28 +4520,28 @@
     </row>
     <row r="29" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K29" s="17"/>
       <c r="L29" s="20"/>
@@ -4549,45 +4558,45 @@
         <v>60</v>
       </c>
       <c r="S29" s="17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="T29" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="U29" s="17" t="s">
-        <v>63</v>
+        <v>254</v>
       </c>
       <c r="V29" s="21" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="W29" s="17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K30" s="17"/>
       <c r="L30" s="20"/>
@@ -4604,45 +4613,45 @@
         <v>60</v>
       </c>
       <c r="S30" s="17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="T30" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="U30" s="17" t="s">
-        <v>63</v>
+        <v>254</v>
       </c>
       <c r="V30" s="21" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="W30" s="17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
       <c r="H31" s="17" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K31" s="17"/>
       <c r="L31" s="20"/>
@@ -4663,24 +4672,24 @@
         <v>60</v>
       </c>
       <c r="S31" s="17" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="T31" s="17" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="U31" s="17" t="s">
-        <v>63</v>
+        <v>254</v>
       </c>
       <c r="V31" s="21" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="W31" s="17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -4707,35 +4716,35 @@
     </row>
     <row r="33" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E33" s="17"/>
       <c r="F33" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K33" s="26" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="L33" s="20"/>
       <c r="M33" s="20"/>
@@ -4749,52 +4758,52 @@
         <v>60</v>
       </c>
       <c r="S33" s="17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="T33" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="U33" s="17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="V33" s="21" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="W33" s="17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E34" s="17"/>
       <c r="F34" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K34" s="26" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L34" s="20"/>
       <c r="M34" s="19" t="s">
@@ -4810,52 +4819,52 @@
         <v>60</v>
       </c>
       <c r="S34" s="17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="T34" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="U34" s="17" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="V34" s="21" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="W34" s="17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E35" s="17"/>
       <c r="F35" s="15" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K35" s="26" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="L35" s="20"/>
       <c r="M35" s="19" t="s">
@@ -4873,52 +4882,52 @@
         <v>60</v>
       </c>
       <c r="S35" s="17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="T35" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="U35" s="17" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="V35" s="21" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="W35" s="17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E36" s="17"/>
       <c r="F36" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K36" s="26" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="L36" s="18" t="s">
         <v>59</v>
@@ -4936,52 +4945,52 @@
         <v>62</v>
       </c>
       <c r="S36" s="17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="T36" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="U36" s="17" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="V36" s="21" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="W36" s="17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E37" s="17"/>
       <c r="F37" s="15" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="K37" s="26" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L37" s="20"/>
       <c r="M37" s="20"/>
@@ -4997,52 +5006,52 @@
         <v>60</v>
       </c>
       <c r="S37" s="17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="T37" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="U37" s="17" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="V37" s="21" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="W37" s="17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E38" s="17"/>
       <c r="F38" s="15" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I38" s="17" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="K38" s="26" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="L38" s="20"/>
       <c r="M38" s="20"/>
@@ -5056,49 +5065,49 @@
         <v>62</v>
       </c>
       <c r="S38" s="17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="T38" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="U38" s="17" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="V38" s="21" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="W38" s="17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E39" s="17"/>
       <c r="F39" s="15" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="20"/>
@@ -5113,49 +5122,49 @@
         <v>62</v>
       </c>
       <c r="S39" s="17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="T39" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="U39" s="17" t="s">
-        <v>63</v>
+        <v>254</v>
       </c>
       <c r="V39" s="21" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="W39" s="17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E40" s="17"/>
       <c r="F40" s="15" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="K40" s="17"/>
       <c r="L40" s="20"/>
@@ -5172,49 +5181,49 @@
         <v>62</v>
       </c>
       <c r="S40" s="17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="T40" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="U40" s="17" t="s">
-        <v>63</v>
+        <v>254</v>
       </c>
       <c r="V40" s="21" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="W40" s="17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E41" s="17"/>
       <c r="F41" s="15" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K41" s="17"/>
       <c r="L41" s="20"/>
@@ -5229,49 +5238,49 @@
         <v>62</v>
       </c>
       <c r="S41" s="17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="T41" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="U41" s="17" t="s">
-        <v>63</v>
+        <v>254</v>
       </c>
       <c r="V41" s="21" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="W41" s="17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E42" s="17"/>
       <c r="F42" s="15" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="K42" s="17"/>
       <c r="L42" s="20"/>
@@ -5288,52 +5297,52 @@
         <v>62</v>
       </c>
       <c r="S42" s="17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="T42" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="U42" s="17" t="s">
-        <v>63</v>
+        <v>254</v>
       </c>
       <c r="V42" s="21" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="W42" s="17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="15" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K43" s="26" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L43" s="20"/>
       <c r="M43" s="19" t="s">
@@ -5349,52 +5358,52 @@
         <v>60</v>
       </c>
       <c r="S43" s="17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="T43" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="U43" s="17" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="V43" s="21" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="W43" s="17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E44" s="17"/>
       <c r="F44" s="15" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="J44" s="17" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K44" s="26" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="L44" s="20"/>
       <c r="M44" s="20"/>
@@ -5408,49 +5417,49 @@
         <v>62</v>
       </c>
       <c r="S44" s="17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="T44" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="U44" s="17" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="V44" s="21" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="W44" s="17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="15" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="I45" s="17" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K45" s="17"/>
       <c r="L45" s="20"/>
@@ -5467,39 +5476,39 @@
         <v>60</v>
       </c>
       <c r="S45" s="17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="T45" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="U45" s="17" t="s">
-        <v>63</v>
+        <v>254</v>
       </c>
       <c r="V45" s="21" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="W45" s="17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E46" s="17"/>
       <c r="F46" s="15"/>
       <c r="G46" s="15"/>
       <c r="H46" s="17" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="I46" s="17"/>
       <c r="J46" s="17"/>
@@ -5516,24 +5525,24 @@
         <v>60</v>
       </c>
       <c r="S46" s="17" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="T46" s="17" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="U46" s="17" t="s">
-        <v>63</v>
+        <v>254</v>
       </c>
       <c r="V46" s="21" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="W46" s="17" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -5560,19 +5569,19 @@
     </row>
     <row r="48" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F48" s="15" t="n">
         <v>2026</v>
@@ -5581,11 +5590,11 @@
         <v>2026</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="I48" s="17"/>
       <c r="J48" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K48" s="17"/>
       <c r="L48" s="20"/>
@@ -5602,36 +5611,36 @@
         <v>60</v>
       </c>
       <c r="S48" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="T48" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="U48" s="17" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="V48" s="21" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="W48" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F49" s="15" t="n">
         <v>2026</v>
@@ -5640,11 +5649,11 @@
         <v>2026</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="I49" s="17"/>
       <c r="J49" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K49" s="17"/>
       <c r="L49" s="20"/>
@@ -5661,36 +5670,36 @@
         <v>60</v>
       </c>
       <c r="S49" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="T49" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="U49" s="17" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="V49" s="21" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="W49" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F50" s="15" t="s">
         <v>53</v>
@@ -5699,11 +5708,11 @@
         <v>53</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="I50" s="17"/>
       <c r="J50" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K50" s="17"/>
       <c r="L50" s="20"/>
@@ -5720,36 +5729,36 @@
         <v>60</v>
       </c>
       <c r="S50" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="T50" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="U50" s="17" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="V50" s="21" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="W50" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F51" s="15" t="s">
         <v>53</v>
@@ -5758,11 +5767,11 @@
         <v>53</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I51" s="17"/>
       <c r="J51" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="20"/>
@@ -5779,36 +5788,36 @@
         <v>60</v>
       </c>
       <c r="S51" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="T51" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="U51" s="17" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="V51" s="21" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="W51" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F52" s="15" t="s">
         <v>53</v>
@@ -5817,11 +5826,11 @@
         <v>53</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="I52" s="17"/>
       <c r="J52" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K52" s="17"/>
       <c r="L52" s="18" t="s">
@@ -5840,36 +5849,36 @@
         <v>60</v>
       </c>
       <c r="S52" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="T52" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="U52" s="17" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="V52" s="21" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="W52" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F53" s="15" t="n">
         <v>2024</v>
@@ -5878,11 +5887,11 @@
         <v>2024</v>
       </c>
       <c r="H53" s="17" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="I53" s="17"/>
       <c r="J53" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K53" s="17"/>
       <c r="L53" s="20"/>
@@ -5899,36 +5908,36 @@
         <v>60</v>
       </c>
       <c r="S53" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="T53" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="U53" s="17" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="V53" s="21" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="W53" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F54" s="15" t="n">
         <v>2023</v>
@@ -5937,11 +5946,11 @@
         <v>2023</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="I54" s="17"/>
       <c r="J54" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K54" s="17"/>
       <c r="L54" s="20"/>
@@ -5958,36 +5967,36 @@
         <v>60</v>
       </c>
       <c r="S54" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="T54" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="U54" s="17" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="V54" s="21" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="W54" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F55" s="15" t="n">
         <v>2023</v>
@@ -5996,11 +6005,11 @@
         <v>2023</v>
       </c>
       <c r="H55" s="17" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="I55" s="17"/>
       <c r="J55" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K55" s="17"/>
       <c r="L55" s="20"/>
@@ -6017,36 +6026,36 @@
         <v>60</v>
       </c>
       <c r="S55" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="T55" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="U55" s="17" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="V55" s="21" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="W55" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F56" s="15" t="n">
         <v>2022</v>
@@ -6055,11 +6064,11 @@
         <v>2022</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="I56" s="17"/>
       <c r="J56" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K56" s="17"/>
       <c r="L56" s="20"/>
@@ -6076,36 +6085,36 @@
         <v>60</v>
       </c>
       <c r="S56" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="T56" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="U56" s="17" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="V56" s="21" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="W56" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="15" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F57" s="15" t="n">
         <v>2021</v>
@@ -6114,11 +6123,11 @@
         <v>2021</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="I57" s="17"/>
       <c r="J57" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K57" s="17"/>
       <c r="L57" s="20"/>
@@ -6135,36 +6144,36 @@
         <v>60</v>
       </c>
       <c r="S57" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="T57" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="U57" s="17" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="V57" s="21" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="W57" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="15" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F58" s="15" t="n">
         <v>2022</v>
@@ -6173,11 +6182,11 @@
         <v>2022</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="I58" s="17"/>
       <c r="J58" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K58" s="17"/>
       <c r="L58" s="20"/>
@@ -6194,22 +6203,22 @@
         <v>60</v>
       </c>
       <c r="S58" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="T58" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="U58" s="17" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="V58" s="21"/>
       <c r="W58" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -6236,24 +6245,24 @@
     </row>
     <row r="60" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F60" s="15"/>
       <c r="G60" s="15"/>
       <c r="H60" s="17" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="I60" s="17"/>
       <c r="J60" s="17"/>
@@ -6272,43 +6281,43 @@
         <v>60</v>
       </c>
       <c r="S60" s="17" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="T60" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U60" s="17"/>
       <c r="V60" s="21" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="W60" s="17" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="15" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G61" s="15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="I61" s="17"/>
       <c r="J61" s="17"/>
@@ -6327,43 +6336,43 @@
         <v>60</v>
       </c>
       <c r="S61" s="17" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="T61" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U61" s="17"/>
       <c r="V61" s="21" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="W61" s="17" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="15" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G62" s="15" t="s">
         <v>80</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="I62" s="17"/>
       <c r="J62" s="17"/>
@@ -6382,31 +6391,31 @@
         <v>60</v>
       </c>
       <c r="S62" s="17" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="T62" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U62" s="17"/>
       <c r="V62" s="21" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="W62" s="17" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B63" s="16" t="s">
         <v>79</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E63" s="17" t="s">
         <v>79</v>
@@ -6418,7 +6427,7 @@
         <v>70</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="I63" s="17"/>
       <c r="J63" s="17"/>
@@ -6437,31 +6446,31 @@
         <v>60</v>
       </c>
       <c r="S63" s="17" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="T63" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U63" s="17"/>
       <c r="V63" s="21" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="W63" s="17" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B64" s="16" t="s">
         <v>69</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E64" s="17" t="s">
         <v>69</v>
@@ -6473,7 +6482,7 @@
         <v>71</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="I64" s="17"/>
       <c r="J64" s="17"/>
@@ -6492,31 +6501,31 @@
         <v>60</v>
       </c>
       <c r="S64" s="17" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="T64" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U64" s="17"/>
       <c r="V64" s="21" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="W64" s="17" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="15" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B65" s="16" t="s">
         <v>52</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E65" s="17" t="s">
         <v>52</v>
@@ -6528,7 +6537,7 @@
         <v>54</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="I65" s="17"/>
       <c r="J65" s="17"/>
@@ -6547,17 +6556,17 @@
         <v>60</v>
       </c>
       <c r="S65" s="17" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="T65" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U65" s="17"/>
       <c r="V65" s="21" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="W65" s="17" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -6613,28 +6622,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6664,7 +6673,7 @@
         <v>Add</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6694,7 +6703,7 @@
         <v>OK</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6724,7 +6733,7 @@
         <v>OK</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6754,7 +6763,7 @@
         <v>OK</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6784,7 +6793,7 @@
         <v>OK</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6814,7 +6823,7 @@
         <v>Trim</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6829,7 +6838,7 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">COUNTA(Artifacts!$C$2:$C$124)</f>
@@ -6844,7 +6853,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -6880,52 +6889,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="J1" s="27" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D2" s="17"/>
       <c r="E2" s="17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G2" s="17" t="n">
         <v>42.08</v>
@@ -6937,27 +6946,27 @@
         <v>60</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>470</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" s="17" t="s">
         <v>104</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>467</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>435</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>103</v>
       </c>
       <c r="G3" s="17" t="n">
         <v>38.97</v>
@@ -6969,27 +6978,27 @@
         <v>60</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>80</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="G4" s="17" t="n">
         <v>41.88</v>
@@ -7001,18 +7010,18 @@
         <v>60</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>80</v>
@@ -7021,7 +7030,7 @@
         <v>70</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>45.46</v>
@@ -7033,7 +7042,7 @@
         <v>60</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7041,10 +7050,10 @@
         <v>69</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>70</v>
@@ -7053,7 +7062,7 @@
         <v>53</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="G6" s="17" t="n">
         <v>32.78</v>
@@ -7065,7 +7074,7 @@
         <v>60</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7073,10 +7082,10 @@
         <v>52</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>53</v>
@@ -7085,7 +7094,7 @@
         <v>54</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>30.27</v>
@@ -7097,23 +7106,23 @@
         <v>60</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="17" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>29.76</v>
@@ -7122,24 +7131,24 @@
         <v>-95.37</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J8" s="21"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="17" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>33.43</v>
@@ -7148,24 +7157,24 @@
         <v>-111.94</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="17" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="G10" s="17" t="n">
         <v>32.76</v>
@@ -7180,22 +7189,22 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>40.81</v>
@@ -7210,22 +7219,22 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G12" s="17" t="n">
         <v>39.57</v>
@@ -7240,22 +7249,22 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
+        <v>491</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="C13" s="17" t="s">
         <v>488</v>
       </c>
-      <c r="B13" s="17" t="s">
-        <v>378</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>485</v>
-      </c>
       <c r="D13" s="17" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>38.72</v>
@@ -7270,13 +7279,13 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>53</v>
@@ -7285,7 +7294,7 @@
         <v>53</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
@@ -7293,18 +7302,18 @@
         <v>60</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>53</v>
@@ -7313,7 +7322,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="G15" s="17"/>
       <c r="H15" s="17"/>
@@ -7321,18 +7330,18 @@
         <v>60</v>
       </c>
       <c r="J15" s="21" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>53</v>
@@ -7341,7 +7350,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
@@ -7349,18 +7358,18 @@
         <v>60</v>
       </c>
       <c r="J16" s="21" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>71</v>
@@ -7369,7 +7378,7 @@
         <v>71</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>-22.97</v>
@@ -7381,27 +7390,27 @@
         <v>60</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
@@ -7409,27 +7418,27 @@
         <v>60</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>26.71</v>
@@ -7438,28 +7447,28 @@
         <v>-80.04</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="G20" s="17" t="n">
         <v>19.43</v>
@@ -7474,13 +7483,13 @@
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D21" s="17" t="s">
         <v>70</v>
@@ -7489,7 +7498,7 @@
         <v>70</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>41.89</v>
@@ -7501,27 +7510,27 @@
         <v>60</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
@@ -7532,12 +7541,12 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
   </sheetData>
@@ -7573,33 +7582,33 @@
         <v>24</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F1" s="27" t="s">
         <v>41</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D2" s="32" t="n">
         <v>2026</v>
@@ -7614,13 +7623,13 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="32" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D3" s="32" t="n">
         <v>2026</v>
@@ -7635,13 +7644,13 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>53</v>
@@ -7656,13 +7665,13 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>53</v>
@@ -7677,13 +7686,13 @@
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D6" s="32" t="s">
         <v>53</v>
@@ -7698,13 +7707,13 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>2024</v>
@@ -7719,13 +7728,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>2023</v>
@@ -7740,13 +7749,13 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>2023</v>
@@ -7761,13 +7770,13 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D10" s="32" t="n">
         <v>2022</v>
@@ -7782,13 +7791,13 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D11" s="32" t="n">
         <v>2021</v>
@@ -7803,13 +7812,13 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D12" s="32" t="n">
         <v>2022</v>
@@ -7824,7 +7833,7 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D13" s="28" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E13" s="28" t="n">
         <f aca="false">SUM(E2:E12)</f>
@@ -7833,7 +7842,7 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D14" s="28" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E14" s="28" t="n">
         <f aca="false">COUNTIF(F2:F12,"Yes")</f>
@@ -7842,12 +7851,12 @@
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
@@ -7877,19 +7886,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7897,13 +7906,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E2" s="33"/>
     </row>
@@ -7912,13 +7921,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E3" s="33"/>
     </row>
@@ -7927,13 +7936,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E4" s="33"/>
     </row>
@@ -7942,13 +7951,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C5" s="33" t="s">
+        <v>525</v>
+      </c>
+      <c r="D5" s="33" t="s">
         <v>522</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>519</v>
       </c>
       <c r="E5" s="33"/>
     </row>
@@ -7957,13 +7966,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C6" s="33" t="s">
+        <v>525</v>
+      </c>
+      <c r="D6" s="33" t="s">
         <v>522</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>519</v>
       </c>
       <c r="E6" s="33"/>
     </row>
@@ -7972,16 +7981,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7989,16 +7998,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8006,16 +8015,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="33" t="s">
+        <v>531</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>525</v>
+      </c>
+      <c r="D9" s="33" t="s">
         <v>528</v>
       </c>
-      <c r="C9" s="33" t="s">
-        <v>522</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>525</v>
-      </c>
       <c r="E9" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8023,16 +8032,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="33" t="s">
+        <v>532</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>525</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>528</v>
+      </c>
+      <c r="E10" s="33" t="s">
         <v>529</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>522</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>525</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8040,13 +8049,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C11" s="33" t="s">
+        <v>525</v>
+      </c>
+      <c r="D11" s="33" t="s">
         <v>522</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>519</v>
       </c>
       <c r="E11" s="33"/>
     </row>
@@ -8055,13 +8064,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E12" s="33"/>
     </row>
@@ -8070,13 +8079,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E13" s="33"/>
     </row>
@@ -8085,13 +8094,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E14" s="33"/>
     </row>
@@ -8100,13 +8109,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="33" t="s">
+        <v>538</v>
+      </c>
+      <c r="C15" s="33" t="s">
         <v>535</v>
       </c>
-      <c r="C15" s="33" t="s">
-        <v>532</v>
-      </c>
       <c r="D15" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E15" s="33"/>
     </row>
@@ -8115,16 +8124,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8132,16 +8141,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8149,16 +8158,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8166,16 +8175,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8183,16 +8192,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="33" t="s">
+        <v>542</v>
+      </c>
+      <c r="C20" s="33" t="s">
         <v>539</v>
       </c>
-      <c r="C20" s="33" t="s">
-        <v>536</v>
-      </c>
       <c r="D20" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8200,13 +8209,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E21" s="33"/>
     </row>
@@ -8215,16 +8224,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8232,16 +8241,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8249,16 +8258,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8266,13 +8275,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E25" s="33"/>
     </row>
@@ -8281,13 +8290,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="33" t="s">
+        <v>548</v>
+      </c>
+      <c r="C26" s="33" t="s">
         <v>545</v>
       </c>
-      <c r="C26" s="33" t="s">
-        <v>542</v>
-      </c>
       <c r="D26" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E26" s="33"/>
     </row>
@@ -8296,13 +8305,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E27" s="33"/>
     </row>
@@ -8311,13 +8320,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E28" s="33"/>
     </row>
@@ -8326,13 +8335,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E29" s="33"/>
     </row>
@@ -8341,13 +8350,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E30" s="33"/>
     </row>
@@ -8356,13 +8365,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E31" s="33"/>
     </row>
@@ -8371,13 +8380,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E32" s="33"/>
     </row>
@@ -8386,13 +8395,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E33" s="33"/>
     </row>
@@ -8401,13 +8410,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E34" s="33"/>
     </row>
@@ -8416,19 +8425,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E35" s="33"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="28" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C37" s="28" t="n">
         <f aca="false">COUNTA(B2:B35)</f>
@@ -8437,7 +8446,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C38" s="1" t="n">
         <f aca="false">COUNTIF(D2:D35,"Shaded")</f>
@@ -8446,7 +8455,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C39" s="1" t="n">
         <f aca="false">COUNTIF(D2:D35,"Dot")</f>
@@ -8455,7 +8464,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
   </sheetData>
@@ -8486,16 +8495,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E1" s="27" t="s">
         <v>46</v>
@@ -8503,98 +8512,98 @@
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>60</v>
@@ -8605,13 +8614,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>60</v>
@@ -8622,130 +8631,130 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D13" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>60</v>
@@ -8756,13 +8765,13 @@
     </row>
     <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>60</v>
@@ -8773,13 +8782,13 @@
     </row>
     <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>60</v>
@@ -8790,13 +8799,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>60</v>
@@ -8807,106 +8816,106 @@
     </row>
     <row r="20" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D22" s="21"/>
       <c r="E22" s="17" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="17" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="D24" s="21"/>
       <c r="E24" s="17" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="D25" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
     </row>
   </sheetData>
@@ -8936,16 +8945,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8953,10 +8962,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>60</v>
@@ -8967,13 +8976,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8981,13 +8990,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8995,13 +9004,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9009,13 +9018,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9023,13 +9032,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9037,13 +9046,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9051,13 +9060,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9065,13 +9074,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9079,13 +9088,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9093,13 +9102,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9107,13 +9116,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9121,13 +9130,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9135,13 +9144,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9149,13 +9158,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9163,13 +9172,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9177,13 +9186,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9191,13 +9200,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9205,13 +9214,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9219,13 +9228,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9233,13 +9242,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9247,10 +9256,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="D23" s="21"/>
     </row>

--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="683">
   <si>
     <t xml:space="preserve">Site artifacts: mapping workbook</t>
   </si>
@@ -395,6 +395,9 @@
   </si>
   <si>
     <t xml:space="preserve">Formula SAE electric powertrain (U1); biomechanical research (U2); SAE and Society of Biomedical Engineering.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KU School of Engineering logo (in repo)</t>
   </si>
   <si>
     <t xml:space="preserve">R7</t>
@@ -3487,7 +3490,7 @@
         <v>62</v>
       </c>
       <c r="U8" s="17" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="V8" s="21"/>
       <c r="W8" s="17" t="s">
@@ -3496,22 +3499,22 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E9" s="17"/>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
       <c r="H9" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
@@ -3528,7 +3531,7 @@
         <v>62</v>
       </c>
       <c r="S9" s="17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="T9" s="17" t="s">
         <v>62</v>
@@ -3537,7 +3540,7 @@
         <v>100</v>
       </c>
       <c r="V9" s="21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="W9" s="17" t="s">
         <v>65</v>
@@ -3545,22 +3548,22 @@
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E10" s="17"/>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
       <c r="H10" s="17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
@@ -3577,7 +3580,7 @@
         <v>62</v>
       </c>
       <c r="S10" s="17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="T10" s="17" t="s">
         <v>62</v>
@@ -3586,7 +3589,7 @@
         <v>100</v>
       </c>
       <c r="V10" s="21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="W10" s="17" t="s">
         <v>65</v>
@@ -3594,7 +3597,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
@@ -3621,13 +3624,13 @@
     </row>
     <row r="12" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>51</v>
@@ -3642,13 +3645,13 @@
         <v>54</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K12" s="17"/>
       <c r="L12" s="18" t="s">
@@ -3667,16 +3670,16 @@
         <v>60</v>
       </c>
       <c r="S12" s="17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U12" s="17" t="s">
         <v>63</v>
       </c>
       <c r="V12" s="21" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="W12" s="17" t="s">
         <v>65</v>
@@ -3684,13 +3687,13 @@
     </row>
     <row r="13" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D13" s="17" t="s">
         <v>51</v>
@@ -3705,13 +3708,13 @@
         <v>54</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K13" s="17"/>
       <c r="L13" s="20"/>
@@ -3728,16 +3731,16 @@
         <v>60</v>
       </c>
       <c r="S13" s="17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="U13" s="17" t="s">
         <v>63</v>
       </c>
       <c r="V13" s="21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="W13" s="17" t="s">
         <v>65</v>
@@ -3745,30 +3748,30 @@
     </row>
     <row r="14" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K14" s="17"/>
       <c r="L14" s="20"/>
@@ -3787,47 +3790,47 @@
         <v>60</v>
       </c>
       <c r="S14" s="17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="T14" s="17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="U14" s="17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="V14" s="21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="W14" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
       <c r="H15" s="17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I15" s="17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J15" s="17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="20"/>
@@ -3844,47 +3847,47 @@
         <v>60</v>
       </c>
       <c r="S15" s="17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="T15" s="17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="U15" s="17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="V15" s="21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="W15" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
       <c r="H16" s="17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K16" s="17"/>
       <c r="L16" s="20"/>
@@ -3901,49 +3904,49 @@
         <v>60</v>
       </c>
       <c r="S16" s="17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="V16" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="W16" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>80</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="20"/>
@@ -3962,47 +3965,47 @@
         <v>60</v>
       </c>
       <c r="S17" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="V17" s="21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="W17" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
       <c r="H18" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K18" s="17"/>
       <c r="L18" s="20"/>
@@ -4017,16 +4020,16 @@
         <v>60</v>
       </c>
       <c r="S18" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="T18" s="17" t="s">
         <v>92</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="V18" s="21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="W18" s="17" t="s">
         <v>65</v>
@@ -4034,7 +4037,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -4061,34 +4064,34 @@
     </row>
     <row r="20" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G20" s="15" t="s">
         <v>71</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K20" s="17"/>
       <c r="L20" s="18" t="s">
@@ -4111,16 +4114,16 @@
         <v>60</v>
       </c>
       <c r="S20" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="V20" s="21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="W20" s="17" t="s">
         <v>65</v>
@@ -4128,16 +4131,16 @@
     </row>
     <row r="21" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>69</v>
@@ -4145,10 +4148,10 @@
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
       <c r="H21" s="17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
@@ -4166,42 +4169,42 @@
         <v>92</v>
       </c>
       <c r="S21" s="17" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="T21" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U21" s="17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="V21" s="21"/>
       <c r="W21" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
       <c r="H22" s="17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J22" s="17"/>
       <c r="K22" s="17"/>
@@ -4219,42 +4222,42 @@
         <v>92</v>
       </c>
       <c r="S22" s="17" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="T22" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U22" s="17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="V22" s="21"/>
       <c r="W22" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
       <c r="H23" s="17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
@@ -4272,31 +4275,31 @@
         <v>92</v>
       </c>
       <c r="S23" s="17" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="T23" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U23" s="17" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="V23" s="21"/>
       <c r="W23" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>69</v>
@@ -4304,10 +4307,10 @@
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
       <c r="H24" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J24" s="17"/>
       <c r="K24" s="17"/>
@@ -4325,22 +4328,22 @@
         <v>92</v>
       </c>
       <c r="S24" s="17" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="T24" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U24" s="17" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="V24" s="21"/>
       <c r="W24" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -4367,13 +4370,13 @@
     </row>
     <row r="26" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>104</v>
@@ -4382,19 +4385,19 @@
         <v>105</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G26" s="15" t="s">
         <v>89</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K26" s="17"/>
       <c r="L26" s="18" t="s">
@@ -4413,33 +4416,33 @@
         <v>60</v>
       </c>
       <c r="S26" s="17" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="T26" s="17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="U26" s="17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="V26" s="21" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="W26" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>105</v>
@@ -4448,16 +4451,16 @@
         <v>96</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K27" s="17"/>
       <c r="L27" s="18" t="s">
@@ -4476,24 +4479,24 @@
         <v>60</v>
       </c>
       <c r="S27" s="17" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="T27" s="17" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="U27" s="17" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="V27" s="21" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="W27" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -4520,28 +4523,28 @@
     </row>
     <row r="29" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K29" s="17"/>
       <c r="L29" s="20"/>
@@ -4558,45 +4561,45 @@
         <v>60</v>
       </c>
       <c r="S29" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="T29" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="U29" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="V29" s="21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="W29" s="17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K30" s="17"/>
       <c r="L30" s="20"/>
@@ -4613,45 +4616,45 @@
         <v>60</v>
       </c>
       <c r="S30" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="T30" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="U30" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="V30" s="21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="W30" s="17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
       <c r="H31" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K31" s="17"/>
       <c r="L31" s="20"/>
@@ -4672,24 +4675,24 @@
         <v>60</v>
       </c>
       <c r="S31" s="17" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="T31" s="17" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="U31" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="V31" s="21" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="W31" s="17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -4716,35 +4719,35 @@
     </row>
     <row r="33" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E33" s="17"/>
       <c r="F33" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K33" s="26" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L33" s="20"/>
       <c r="M33" s="20"/>
@@ -4758,52 +4761,52 @@
         <v>60</v>
       </c>
       <c r="S33" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T33" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U33" s="17" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="V33" s="21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="W33" s="17" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E34" s="17"/>
       <c r="F34" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K34" s="26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L34" s="20"/>
       <c r="M34" s="19" t="s">
@@ -4819,52 +4822,52 @@
         <v>60</v>
       </c>
       <c r="S34" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T34" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U34" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="V34" s="21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="W34" s="17" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E35" s="17"/>
       <c r="F35" s="15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K35" s="26" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L35" s="20"/>
       <c r="M35" s="19" t="s">
@@ -4882,52 +4885,52 @@
         <v>60</v>
       </c>
       <c r="S35" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T35" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U35" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="V35" s="21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="W35" s="17" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E36" s="17"/>
       <c r="F36" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K36" s="26" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L36" s="18" t="s">
         <v>59</v>
@@ -4945,52 +4948,52 @@
         <v>62</v>
       </c>
       <c r="S36" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T36" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U36" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="V36" s="21" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="W36" s="17" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E37" s="17"/>
       <c r="F37" s="15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K37" s="26" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L37" s="20"/>
       <c r="M37" s="20"/>
@@ -5006,52 +5009,52 @@
         <v>60</v>
       </c>
       <c r="S37" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T37" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U37" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="V37" s="21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="W37" s="17" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E38" s="17"/>
       <c r="F38" s="15" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I38" s="17" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K38" s="26" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L38" s="20"/>
       <c r="M38" s="20"/>
@@ -5065,49 +5068,49 @@
         <v>62</v>
       </c>
       <c r="S38" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T38" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U38" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="V38" s="21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="W38" s="17" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E39" s="17"/>
       <c r="F39" s="15" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="20"/>
@@ -5122,49 +5125,49 @@
         <v>62</v>
       </c>
       <c r="S39" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T39" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U39" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="V39" s="21" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="W39" s="17" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E40" s="17"/>
       <c r="F40" s="15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K40" s="17"/>
       <c r="L40" s="20"/>
@@ -5181,49 +5184,49 @@
         <v>62</v>
       </c>
       <c r="S40" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T40" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U40" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="V40" s="21" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="W40" s="17" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E41" s="17"/>
       <c r="F41" s="15" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K41" s="17"/>
       <c r="L41" s="20"/>
@@ -5238,49 +5241,49 @@
         <v>62</v>
       </c>
       <c r="S41" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T41" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U41" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="V41" s="21" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="W41" s="17" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E42" s="17"/>
       <c r="F42" s="15" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K42" s="17"/>
       <c r="L42" s="20"/>
@@ -5297,52 +5300,52 @@
         <v>62</v>
       </c>
       <c r="S42" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T42" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U42" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="V42" s="21" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="W42" s="17" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="15" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K43" s="26" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L43" s="20"/>
       <c r="M43" s="19" t="s">
@@ -5358,52 +5361,52 @@
         <v>60</v>
       </c>
       <c r="S43" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T43" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U43" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="V43" s="21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="W43" s="17" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E44" s="17"/>
       <c r="F44" s="15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J44" s="17" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K44" s="26" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L44" s="20"/>
       <c r="M44" s="20"/>
@@ -5417,49 +5420,49 @@
         <v>62</v>
       </c>
       <c r="S44" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T44" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U44" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="V44" s="21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="W44" s="17" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I45" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K45" s="17"/>
       <c r="L45" s="20"/>
@@ -5476,39 +5479,39 @@
         <v>60</v>
       </c>
       <c r="S45" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T45" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U45" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="V45" s="21" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="W45" s="17" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E46" s="17"/>
       <c r="F46" s="15"/>
       <c r="G46" s="15"/>
       <c r="H46" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I46" s="17"/>
       <c r="J46" s="17"/>
@@ -5525,24 +5528,24 @@
         <v>60</v>
       </c>
       <c r="S46" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="T46" s="17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="U46" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="V46" s="21" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="W46" s="17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -5569,19 +5572,19 @@
     </row>
     <row r="48" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F48" s="15" t="n">
         <v>2026</v>
@@ -5590,11 +5593,11 @@
         <v>2026</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I48" s="17"/>
       <c r="J48" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K48" s="17"/>
       <c r="L48" s="20"/>
@@ -5611,36 +5614,36 @@
         <v>60</v>
       </c>
       <c r="S48" s="17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T48" s="17" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="U48" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="V48" s="21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="W48" s="17" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F49" s="15" t="n">
         <v>2026</v>
@@ -5649,11 +5652,11 @@
         <v>2026</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I49" s="17"/>
       <c r="J49" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K49" s="17"/>
       <c r="L49" s="20"/>
@@ -5670,36 +5673,36 @@
         <v>60</v>
       </c>
       <c r="S49" s="17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T49" s="17" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="U49" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="V49" s="21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="W49" s="17" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F50" s="15" t="s">
         <v>53</v>
@@ -5708,11 +5711,11 @@
         <v>53</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I50" s="17"/>
       <c r="J50" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K50" s="17"/>
       <c r="L50" s="20"/>
@@ -5729,36 +5732,36 @@
         <v>60</v>
       </c>
       <c r="S50" s="17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T50" s="17" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="U50" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="V50" s="21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="W50" s="17" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F51" s="15" t="s">
         <v>53</v>
@@ -5767,11 +5770,11 @@
         <v>53</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I51" s="17"/>
       <c r="J51" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="20"/>
@@ -5788,36 +5791,36 @@
         <v>60</v>
       </c>
       <c r="S51" s="17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T51" s="17" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="U51" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="V51" s="21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="W51" s="17" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F52" s="15" t="s">
         <v>53</v>
@@ -5826,11 +5829,11 @@
         <v>53</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I52" s="17"/>
       <c r="J52" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K52" s="17"/>
       <c r="L52" s="18" t="s">
@@ -5849,36 +5852,36 @@
         <v>60</v>
       </c>
       <c r="S52" s="17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T52" s="17" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="U52" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="V52" s="21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="W52" s="17" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F53" s="15" t="n">
         <v>2024</v>
@@ -5887,11 +5890,11 @@
         <v>2024</v>
       </c>
       <c r="H53" s="17" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I53" s="17"/>
       <c r="J53" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K53" s="17"/>
       <c r="L53" s="20"/>
@@ -5908,36 +5911,36 @@
         <v>60</v>
       </c>
       <c r="S53" s="17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T53" s="17" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="U53" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="V53" s="21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="W53" s="17" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F54" s="15" t="n">
         <v>2023</v>
@@ -5946,11 +5949,11 @@
         <v>2023</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="I54" s="17"/>
       <c r="J54" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K54" s="17"/>
       <c r="L54" s="20"/>
@@ -5967,36 +5970,36 @@
         <v>60</v>
       </c>
       <c r="S54" s="17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T54" s="17" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="U54" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="V54" s="21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="W54" s="17" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F55" s="15" t="n">
         <v>2023</v>
@@ -6005,11 +6008,11 @@
         <v>2023</v>
       </c>
       <c r="H55" s="17" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I55" s="17"/>
       <c r="J55" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K55" s="17"/>
       <c r="L55" s="20"/>
@@ -6026,36 +6029,36 @@
         <v>60</v>
       </c>
       <c r="S55" s="17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T55" s="17" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="U55" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="V55" s="21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="W55" s="17" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F56" s="15" t="n">
         <v>2022</v>
@@ -6064,11 +6067,11 @@
         <v>2022</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I56" s="17"/>
       <c r="J56" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K56" s="17"/>
       <c r="L56" s="20"/>
@@ -6085,36 +6088,36 @@
         <v>60</v>
       </c>
       <c r="S56" s="17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T56" s="17" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="U56" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="V56" s="21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="W56" s="17" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="15" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F57" s="15" t="n">
         <v>2021</v>
@@ -6123,11 +6126,11 @@
         <v>2021</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I57" s="17"/>
       <c r="J57" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K57" s="17"/>
       <c r="L57" s="20"/>
@@ -6144,36 +6147,36 @@
         <v>60</v>
       </c>
       <c r="S57" s="17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T57" s="17" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="U57" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="V57" s="21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="W57" s="17" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="15" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F58" s="15" t="n">
         <v>2022</v>
@@ -6182,11 +6185,11 @@
         <v>2022</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I58" s="17"/>
       <c r="J58" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K58" s="17"/>
       <c r="L58" s="20"/>
@@ -6203,22 +6206,22 @@
         <v>60</v>
       </c>
       <c r="S58" s="17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T58" s="17" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="U58" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="V58" s="21"/>
       <c r="W58" s="17" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -6245,24 +6248,24 @@
     </row>
     <row r="60" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C60" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="D60" s="17" t="s">
+        <v>421</v>
+      </c>
+      <c r="E60" s="17" t="s">
         <v>419</v>
-      </c>
-      <c r="D60" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="E60" s="17" t="s">
-        <v>418</v>
       </c>
       <c r="F60" s="15"/>
       <c r="G60" s="15"/>
       <c r="H60" s="17" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I60" s="17"/>
       <c r="J60" s="17"/>
@@ -6281,31 +6284,31 @@
         <v>60</v>
       </c>
       <c r="S60" s="17" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="T60" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U60" s="17"/>
       <c r="V60" s="21" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="W60" s="17" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="15" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B61" s="16" t="s">
         <v>105</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E61" s="17" t="s">
         <v>105</v>
@@ -6317,7 +6320,7 @@
         <v>89</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I61" s="17"/>
       <c r="J61" s="17"/>
@@ -6336,31 +6339,31 @@
         <v>60</v>
       </c>
       <c r="S61" s="17" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="T61" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U61" s="17"/>
       <c r="V61" s="21" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="W61" s="17" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="15" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B62" s="16" t="s">
         <v>88</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E62" s="17" t="s">
         <v>88</v>
@@ -6372,7 +6375,7 @@
         <v>80</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I62" s="17"/>
       <c r="J62" s="17"/>
@@ -6391,31 +6394,31 @@
         <v>60</v>
       </c>
       <c r="S62" s="17" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="T62" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U62" s="17"/>
       <c r="V62" s="21" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="W62" s="17" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B63" s="16" t="s">
         <v>79</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E63" s="17" t="s">
         <v>79</v>
@@ -6427,7 +6430,7 @@
         <v>70</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I63" s="17"/>
       <c r="J63" s="17"/>
@@ -6446,31 +6449,31 @@
         <v>60</v>
       </c>
       <c r="S63" s="17" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="T63" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U63" s="17"/>
       <c r="V63" s="21" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="W63" s="17" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B64" s="16" t="s">
         <v>69</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E64" s="17" t="s">
         <v>69</v>
@@ -6482,7 +6485,7 @@
         <v>71</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="I64" s="17"/>
       <c r="J64" s="17"/>
@@ -6501,31 +6504,31 @@
         <v>60</v>
       </c>
       <c r="S64" s="17" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="T64" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U64" s="17"/>
       <c r="V64" s="21" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="W64" s="17" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="15" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B65" s="16" t="s">
         <v>52</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E65" s="17" t="s">
         <v>52</v>
@@ -6537,7 +6540,7 @@
         <v>54</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I65" s="17"/>
       <c r="J65" s="17"/>
@@ -6556,17 +6559,17 @@
         <v>60</v>
       </c>
       <c r="S65" s="17" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="T65" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U65" s="17"/>
       <c r="V65" s="21" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="W65" s="17" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -6622,28 +6625,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6673,7 +6676,7 @@
         <v>Add</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6703,7 +6706,7 @@
         <v>OK</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6733,7 +6736,7 @@
         <v>OK</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6763,7 +6766,7 @@
         <v>OK</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6793,7 +6796,7 @@
         <v>OK</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6823,7 +6826,7 @@
         <v>Trim</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6838,7 +6841,7 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">COUNTA(Artifacts!$C$2:$C$124)</f>
@@ -6853,7 +6856,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -6889,52 +6892,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J1" s="27" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D2" s="17"/>
       <c r="E2" s="17" t="s">
         <v>106</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G2" s="17" t="n">
         <v>42.08</v>
@@ -6946,7 +6949,7 @@
         <v>60</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6954,10 +6957,10 @@
         <v>105</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>106</v>
@@ -6978,7 +6981,7 @@
         <v>60</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6986,10 +6989,10 @@
         <v>88</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D4" s="17" t="s">
         <v>89</v>
@@ -6998,7 +7001,7 @@
         <v>80</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G4" s="17" t="n">
         <v>41.88</v>
@@ -7010,18 +7013,18 @@
         <v>60</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>80</v>
@@ -7030,7 +7033,7 @@
         <v>70</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>45.46</v>
@@ -7042,7 +7045,7 @@
         <v>60</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7050,10 +7053,10 @@
         <v>69</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>70</v>
@@ -7062,7 +7065,7 @@
         <v>53</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G6" s="17" t="n">
         <v>32.78</v>
@@ -7074,7 +7077,7 @@
         <v>60</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7082,10 +7085,10 @@
         <v>52</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>53</v>
@@ -7094,7 +7097,7 @@
         <v>54</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>30.27</v>
@@ -7106,23 +7109,23 @@
         <v>60</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="17" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>29.76</v>
@@ -7137,18 +7140,18 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="17" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>33.43</v>
@@ -7163,18 +7166,18 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="17" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G10" s="17" t="n">
         <v>32.76</v>
@@ -7189,13 +7192,13 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>89</v>
@@ -7204,7 +7207,7 @@
         <v>89</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>40.81</v>
@@ -7219,22 +7222,22 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G12" s="17" t="n">
         <v>39.57</v>
@@ -7249,22 +7252,22 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>38.72</v>
@@ -7279,13 +7282,13 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>53</v>
@@ -7294,7 +7297,7 @@
         <v>53</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
@@ -7302,18 +7305,18 @@
         <v>60</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>53</v>
@@ -7322,7 +7325,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G15" s="17"/>
       <c r="H15" s="17"/>
@@ -7330,18 +7333,18 @@
         <v>60</v>
       </c>
       <c r="J15" s="21" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>53</v>
@@ -7350,7 +7353,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
@@ -7358,18 +7361,18 @@
         <v>60</v>
       </c>
       <c r="J16" s="21" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>71</v>
@@ -7378,7 +7381,7 @@
         <v>71</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>-22.97</v>
@@ -7390,27 +7393,27 @@
         <v>60</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
@@ -7418,27 +7421,27 @@
         <v>60</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>26.71</v>
@@ -7453,22 +7456,22 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G20" s="17" t="n">
         <v>19.43</v>
@@ -7483,13 +7486,13 @@
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D21" s="17" t="s">
         <v>70</v>
@@ -7498,7 +7501,7 @@
         <v>70</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>41.89</v>
@@ -7510,27 +7513,27 @@
         <v>60</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
@@ -7541,12 +7544,12 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>
@@ -7582,33 +7585,33 @@
         <v>24</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F1" s="27" t="s">
         <v>41</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D2" s="32" t="n">
         <v>2026</v>
@@ -7623,13 +7626,13 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="32" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D3" s="32" t="n">
         <v>2026</v>
@@ -7644,13 +7647,13 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>53</v>
@@ -7665,13 +7668,13 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>53</v>
@@ -7686,13 +7689,13 @@
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D6" s="32" t="s">
         <v>53</v>
@@ -7707,13 +7710,13 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>2024</v>
@@ -7728,13 +7731,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>2023</v>
@@ -7749,13 +7752,13 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>2023</v>
@@ -7770,13 +7773,13 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D10" s="32" t="n">
         <v>2022</v>
@@ -7791,13 +7794,13 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D11" s="32" t="n">
         <v>2021</v>
@@ -7812,13 +7815,13 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D12" s="32" t="n">
         <v>2022</v>
@@ -7833,7 +7836,7 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D13" s="28" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E13" s="28" t="n">
         <f aca="false">SUM(E2:E12)</f>
@@ -7842,7 +7845,7 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D14" s="28" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E14" s="28" t="n">
         <f aca="false">COUNTIF(F2:F12,"Yes")</f>
@@ -7851,12 +7854,12 @@
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
@@ -7886,19 +7889,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7906,13 +7909,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E2" s="33"/>
     </row>
@@ -7921,13 +7924,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="33" t="s">
+        <v>524</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>522</v>
+      </c>
+      <c r="D3" s="33" t="s">
         <v>523</v>
-      </c>
-      <c r="C3" s="33" t="s">
-        <v>521</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>522</v>
       </c>
       <c r="E3" s="33"/>
     </row>
@@ -7936,13 +7939,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E4" s="33"/>
     </row>
@@ -7951,13 +7954,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E5" s="33"/>
     </row>
@@ -7966,13 +7969,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="33" t="s">
+        <v>527</v>
+      </c>
+      <c r="C6" s="33" t="s">
         <v>526</v>
       </c>
-      <c r="C6" s="33" t="s">
-        <v>525</v>
-      </c>
       <c r="D6" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E6" s="33"/>
     </row>
@@ -7981,16 +7984,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7998,16 +8001,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="33" t="s">
+        <v>531</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>529</v>
+      </c>
+      <c r="E8" s="33" t="s">
         <v>530</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>525</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>528</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8015,16 +8018,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8032,16 +8035,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8049,13 +8052,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E11" s="33"/>
     </row>
@@ -8064,13 +8067,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E12" s="33"/>
     </row>
@@ -8079,13 +8082,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="33" t="s">
+        <v>537</v>
+      </c>
+      <c r="C13" s="33" t="s">
         <v>536</v>
       </c>
-      <c r="C13" s="33" t="s">
-        <v>535</v>
-      </c>
       <c r="D13" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E13" s="33"/>
     </row>
@@ -8094,13 +8097,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E14" s="33"/>
     </row>
@@ -8109,13 +8112,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E15" s="33"/>
     </row>
@@ -8124,16 +8127,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8141,16 +8144,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8158,16 +8161,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8175,16 +8178,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8192,16 +8195,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8209,13 +8212,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E21" s="33"/>
     </row>
@@ -8224,16 +8227,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8241,16 +8244,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8258,16 +8261,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8275,13 +8278,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E25" s="33"/>
     </row>
@@ -8290,13 +8293,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E26" s="33"/>
     </row>
@@ -8305,13 +8308,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E27" s="33"/>
     </row>
@@ -8320,13 +8323,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E28" s="33"/>
     </row>
@@ -8335,13 +8338,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E29" s="33"/>
     </row>
@@ -8350,13 +8353,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E30" s="33"/>
     </row>
@@ -8365,13 +8368,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E31" s="33"/>
     </row>
@@ -8380,13 +8383,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E32" s="33"/>
     </row>
@@ -8395,13 +8398,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E33" s="33"/>
     </row>
@@ -8410,13 +8413,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E34" s="33"/>
     </row>
@@ -8425,19 +8428,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E35" s="33"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="28" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C37" s="28" t="n">
         <f aca="false">COUNTA(B2:B35)</f>
@@ -8446,7 +8449,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C38" s="1" t="n">
         <f aca="false">COUNTIF(D2:D35,"Shaded")</f>
@@ -8455,7 +8458,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C39" s="1" t="n">
         <f aca="false">COUNTIF(D2:D35,"Dot")</f>
@@ -8464,7 +8467,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>
@@ -8495,16 +8498,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E1" s="27" t="s">
         <v>46</v>
@@ -8512,98 +8515,98 @@
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>60</v>
@@ -8614,13 +8617,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>60</v>
@@ -8631,130 +8634,130 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D13" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>60</v>
@@ -8765,13 +8768,13 @@
     </row>
     <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>60</v>
@@ -8782,13 +8785,13 @@
     </row>
     <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>60</v>
@@ -8799,13 +8802,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>60</v>
@@ -8816,106 +8819,106 @@
     </row>
     <row r="20" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D22" s="21"/>
       <c r="E22" s="17" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="17" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D24" s="21"/>
       <c r="E24" s="17" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D25" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
   </sheetData>
@@ -8945,16 +8948,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8962,10 +8965,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>60</v>
@@ -8976,13 +8979,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8990,13 +8993,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9004,13 +9007,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9018,13 +9021,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9032,13 +9035,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9046,13 +9049,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9060,13 +9063,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9074,13 +9077,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9088,13 +9091,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9102,13 +9105,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9116,13 +9119,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9130,13 +9133,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9144,13 +9147,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9158,13 +9161,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9172,13 +9175,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9186,13 +9189,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9200,13 +9203,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9214,13 +9217,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9228,13 +9231,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9242,13 +9245,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9256,10 +9259,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D23" s="21"/>
     </row>

--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="694">
   <si>
     <t xml:space="preserve">Site artifacts: mapping workbook</t>
   </si>
@@ -133,7 +133,7 @@
     <t xml:space="preserve">Sections</t>
   </si>
   <si>
-    <t xml:space="preserve">About · Engineering · Projects · Art · Travel · Apps (the six tabs in the mocks).</t>
+    <t xml:space="preserve">About · Engineering · Projects · Art · Travel · Digital (was Apps) (the six tabs in the mocks).</t>
   </si>
   <si>
     <t xml:space="preserve">Sources</t>
@@ -190,7 +190,7 @@
     <t xml:space="preserve">Travel</t>
   </si>
   <si>
-    <t xml:space="preserve">Apps</t>
+    <t xml:space="preserve">Digital</t>
   </si>
   <si>
     <t xml:space="preserve">Featured?</t>
@@ -298,6 +298,9 @@
     <t xml:space="preserve">Portfolio pages 4–5; MAPEI logo (in repo)</t>
   </si>
   <si>
+    <t xml:space="preserve">Card shows both stints: Chicago 2018–19, Dallas 2021–24.</t>
+  </si>
+  <si>
     <t xml:space="preserve">R3</t>
   </si>
   <si>
@@ -346,288 +349,294 @@
     <t xml:space="preserve">Process improvement and infrastructure upgrades.</t>
   </si>
   <si>
+    <t xml:space="preserve">Shown on the MAPEI Corp card (R2) as its 2018–19 Chicago stint; still marks Chicago as "worked" on the map.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWC Industries: Mechanical Engineering Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWC Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer internship designing components and assemblies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cut raw-material waste with design-for-manufacture parts; designed replacement parts to prevent downtime.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolidWorks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Removed from the site (your call).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B.S. Mechanical Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Kansas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lawrence, KS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSME.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula SAE electric powertrain (U1); biomechanical research (U2); SAE and Society of Biomedical Engineering.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KU School of Engineering logo (in repo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMP certification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Management Professional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Badge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not on the site (this is not a resume).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOA Board Director</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leadership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercer Square Condominium Association</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Board director for a condominium association.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line in About</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional engineering projects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations facility build-out (200K sq ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End-to-end design and construction of a facility combining office, automated distribution, clean pack, sterilization and additive manufacturing, as owner rep.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200K sq ft; budget &gt;$10M; major utilities, equipment integration, controls, life safety; next-phase expansion and capacity planning; lean / continuous improvement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design-build delivery, commissioning, validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miniature diorama of the building</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate (simple diorama)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public-safe photos or layouts? NDA limits?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Industrial additive manufacturing center (EBM + SLS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built out an AM center with EBM and SLS systems for patient-specific implants.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilities, equipment siting, install sequencing, material-flow layout, production validation; scalable workflows aligned with regulatory, quality and environmental standards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBM, SLS, process validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printer / lattice part</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate (generic lattice, no real implant)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What can be shown (medical device confidentiality).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated dry mix production plant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPEI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houston, TX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ground-up automated dry mix production and packaging plant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">European / North American vendors; Italian electrical contractors for power and automation; air permitting and FAA approval; delivered on budget and schedule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolidWorks, AutoCAD, P&amp;IDs, commissioning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silo tower (strong hero)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Have CAD (render in portfolio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.4: elevation, P&amp;ID, 3D render, tower photo, interior photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dates: placeholder for now.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robotic palletizer and bag applicator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tempe, AZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added automated robotic palletizing and bag application to an existing dry mix plant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doubled the plant's total output capacity; removed two manual operations; prefab kept downtime minimal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolidWorks, AutoCAD, MS Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robot cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Have vendor render (portfolio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.4: render + photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site development: 315K sq ft brownfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houston, TX (from Dallas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turned a speculative brownfield building into a full production and distribution facility.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315K sq ft; design-build; vendor selection and contracts; multiple concurrent projects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS Project, design-build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building / diorama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.5: building photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lived in Dallas, travelled to Houston for this project. Dates: placeholder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-line static mixing process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milan → Dallas, TX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First production version of a new static mixing technology, prototyped in Milan and built in Dallas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production time −35%; manual operations removed; enabled bulk material purchasing; equipment procured from Europe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">European vendors, electromechanical contractors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixing skid (prototype → production story)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.5: drawing, 3D render, photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquid admixtures plant expansion ($5M)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX (verify)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plant expansion introducing automated blending and bulk transfer systems to the Southern U.S.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$5M; design, construction, commissioning and lifecycle management.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Process automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Process skid</t>
+  </si>
+  <si>
     <t xml:space="preserve">Maybe</t>
   </si>
   <si>
-    <t xml:space="preserve">R5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWC Industries: Mechanical Engineering Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWC Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summer internship designing components and assemblies.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cut raw-material waste with design-for-manufacture parts; designed replacement parts to prevent downtime.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolidWorks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B.S. Mechanical Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Education</t>
-  </si>
-  <si>
-    <t xml:space="preserve">University of Kansas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lawrence, KS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSME.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formula SAE electric powertrain (U1); biomechanical research (U2); SAE and Society of Biomedical Engineering.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KU School of Engineering logo (in repo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PMP certification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project Management Professional.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Badge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not on the site (this is not a resume).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOA Board Director</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leadership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mercer Square Condominium Association</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Board director for a condominium association.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Line in About</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Professional engineering projects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations facility build-out (200K sq ft)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End-to-end design and construction of a facility combining office, automated distribution, clean pack, sterilization and additive manufacturing, as owner rep.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200K sq ft; budget &gt;$10M; major utilities, equipment integration, controls, life safety; next-phase expansion and capacity planning; lean / continuous improvement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design-build delivery, commissioning, validation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miniature diorama of the building</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate (simple diorama)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public-safe photos or layouts? NDA limits?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Industrial additive manufacturing center (EBM + SLS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built out an AM center with EBM and SLS systems for patient-specific implants.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utilities, equipment siting, install sequencing, material-flow layout, production validation; scalable workflows aligned with regulatory, quality and environmental standards.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EBM, SLS, process validation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printer / lattice part</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate (generic lattice, no real implant)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What can be shown (medical device confidentiality).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automated dry mix production plant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPEI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Houston, TX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ground-up automated dry mix production and packaging plant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">European / North American vendors; Italian electrical contractors for power and automation; air permitting and FAA approval; delivered on budget and schedule.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolidWorks, AutoCAD, P&amp;IDs, commissioning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silo tower (strong hero)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Have CAD (render in portfolio)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.4: elevation, P&amp;ID, 3D render, tower photo, interior photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dates: placeholder for now.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robotic palletizer and bag applicator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tempe, AZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added automated robotic palletizing and bag application to an existing dry mix plant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doubled the plant's total output capacity; removed two manual operations; prefab kept downtime minimal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolidWorks, AutoCAD, MS Project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robot cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Have vendor render (portfolio)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.4: render + photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site development: 315K sq ft brownfield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Houston, TX (from Dallas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turned a speculative brownfield building into a full production and distribution facility.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315K sq ft; design-build; vendor selection and contracts; multiple concurrent projects.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS Project, design-build</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Building / diorama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.5: building photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lived in Dallas, travelled to Houston for this project. Dates: placeholder.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-line static mixing process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milan → Dallas, TX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First production version of a new static mixing technology, prototyped in Milan and built in Dallas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production time −35%; manual operations removed; enabled bulk material purchasing; equipment procured from Europe.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">European vendors, electromechanical contractors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mixing skid (prototype → production story)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.5: drawing, 3D render, photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liquid admixtures plant expansion ($5M)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TX (verify)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plant expansion introducing automated blending and bulk transfer systems to the Southern U.S.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$5M; design, construction, commissioning and lifecycle management.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Process automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Process skid</t>
-  </si>
-  <si>
     <t xml:space="preserve">You have photos (to send)</t>
   </si>
   <si>
@@ -1939,6 +1948,24 @@
     <t xml:space="preserve">→ Decided: the one quiet line and the dogs (rows 24–25). Everything else here is shown by the work itself, not listed.</t>
   </si>
   <si>
+    <t xml:space="preserve">Race</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austin Marathon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">February 2024. Its logo, small, on the 2024 ring in About (name on hover).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRONMAN 70.3 Texas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spring 2026 (April as a placeholder). Its logo, small, on the 2026 ring in About.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Question</t>
   </si>
   <si>
@@ -2117,6 +2144,12 @@
   </si>
   <si>
     <t xml:space="preserve">A14, Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About is now a calendar wheel (rings = year, angle = month). Start months for: KU, piano-pedal device, Formula SAE, MAPEI SpA, MAPEI Corp (Chicago and Dallas), OnlyChargeEV, the facility build-out. Only Enovis (April 2025) is known; the rest are placeholders.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Races: was the Austin Marathon the full 26.2 or the half? Which month was IRONMAN 70.3 Texas (April is the placeholder)?</t>
   </si>
 </sst>
 </file>
@@ -3262,38 +3295,40 @@
       <c r="U4" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="V4" s="21"/>
+      <c r="V4" s="21" t="s">
+        <v>76</v>
+      </c>
       <c r="W4" s="17" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>50</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G5" s="15" t="s">
         <v>70</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
@@ -3313,16 +3348,16 @@
         <v>60</v>
       </c>
       <c r="S5" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T5" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U5" s="17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V5" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="W5" s="17" t="s">
         <v>65</v>
@@ -3330,10 +3365,10 @@
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>50</v>
@@ -3342,19 +3377,19 @@
         <v>68</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
@@ -3367,7 +3402,7 @@
       <c r="P6" s="20"/>
       <c r="Q6" s="20"/>
       <c r="R6" s="20" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="S6" s="17" t="s">
         <v>61</v>
@@ -3376,43 +3411,45 @@
         <v>62</v>
       </c>
       <c r="U6" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="V6" s="21"/>
+        <v>85</v>
+      </c>
+      <c r="V6" s="21" t="s">
+        <v>93</v>
+      </c>
       <c r="W6" s="17" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>50</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K7" s="17"/>
       <c r="L7" s="18" t="s">
@@ -3424,7 +3461,7 @@
       <c r="P7" s="20"/>
       <c r="Q7" s="20"/>
       <c r="R7" s="20" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="S7" s="17" t="s">
         <v>61</v>
@@ -3433,40 +3470,42 @@
         <v>62</v>
       </c>
       <c r="U7" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="V7" s="21"/>
+        <v>101</v>
+      </c>
+      <c r="V7" s="21" t="s">
+        <v>102</v>
+      </c>
       <c r="W7" s="17" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
@@ -3490,7 +3529,7 @@
         <v>62</v>
       </c>
       <c r="U8" s="17" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="V8" s="21"/>
       <c r="W8" s="17" t="s">
@@ -3499,22 +3538,22 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E9" s="17"/>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
       <c r="H9" s="17" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
@@ -3531,16 +3570,16 @@
         <v>62</v>
       </c>
       <c r="S9" s="17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="T9" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="V9" s="21" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="W9" s="17" t="s">
         <v>65</v>
@@ -3548,22 +3587,22 @@
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E10" s="17"/>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
       <c r="H10" s="17" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
@@ -3580,16 +3619,16 @@
         <v>62</v>
       </c>
       <c r="S10" s="17" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="T10" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="V10" s="21" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="W10" s="17" t="s">
         <v>65</v>
@@ -3597,7 +3636,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
@@ -3624,13 +3663,13 @@
     </row>
     <row r="12" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>51</v>
@@ -3645,13 +3684,13 @@
         <v>54</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K12" s="17"/>
       <c r="L12" s="18" t="s">
@@ -3670,16 +3709,16 @@
         <v>60</v>
       </c>
       <c r="S12" s="17" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="U12" s="17" t="s">
         <v>63</v>
       </c>
       <c r="V12" s="21" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="W12" s="17" t="s">
         <v>65</v>
@@ -3687,13 +3726,13 @@
     </row>
     <row r="13" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" s="17" t="s">
         <v>51</v>
@@ -3708,13 +3747,13 @@
         <v>54</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K13" s="17"/>
       <c r="L13" s="20"/>
@@ -3731,16 +3770,16 @@
         <v>60</v>
       </c>
       <c r="S13" s="17" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="U13" s="17" t="s">
         <v>63</v>
       </c>
       <c r="V13" s="21" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="W13" s="17" t="s">
         <v>65</v>
@@ -3748,30 +3787,30 @@
     </row>
     <row r="14" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K14" s="17"/>
       <c r="L14" s="20"/>
@@ -3790,47 +3829,47 @@
         <v>60</v>
       </c>
       <c r="S14" s="17" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="T14" s="17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="U14" s="17" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="V14" s="21" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="W14" s="17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
       <c r="H15" s="17" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I15" s="17" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J15" s="17" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="20"/>
@@ -3847,47 +3886,47 @@
         <v>60</v>
       </c>
       <c r="S15" s="17" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="T15" s="17" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="U15" s="17" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="V15" s="21" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="W15" s="17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
       <c r="H16" s="17" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K16" s="17"/>
       <c r="L16" s="20"/>
@@ -3904,49 +3943,49 @@
         <v>60</v>
       </c>
       <c r="S16" s="17" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="V16" s="21" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W16" s="17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="17" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="20"/>
@@ -3965,47 +4004,47 @@
         <v>60</v>
       </c>
       <c r="S17" s="17" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="V17" s="21" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="W17" s="17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
       <c r="H18" s="17" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K18" s="17"/>
       <c r="L18" s="20"/>
@@ -4020,16 +4059,16 @@
         <v>60</v>
       </c>
       <c r="S18" s="17" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="V18" s="21" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="W18" s="17" t="s">
         <v>65</v>
@@ -4037,7 +4076,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -4064,34 +4103,34 @@
     </row>
     <row r="20" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G20" s="15" t="s">
         <v>71</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K20" s="17"/>
       <c r="L20" s="18" t="s">
@@ -4114,16 +4153,16 @@
         <v>60</v>
       </c>
       <c r="S20" s="17" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="V20" s="21" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="W20" s="17" t="s">
         <v>65</v>
@@ -4131,16 +4170,16 @@
     </row>
     <row r="21" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>69</v>
@@ -4148,10 +4187,10 @@
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
       <c r="H21" s="17" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
@@ -4166,45 +4205,45 @@
       <c r="P21" s="20"/>
       <c r="Q21" s="20"/>
       <c r="R21" s="20" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="S21" s="17" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="T21" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U21" s="17" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="V21" s="21"/>
       <c r="W21" s="17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
       <c r="H22" s="17" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J22" s="17"/>
       <c r="K22" s="17"/>
@@ -4219,45 +4258,45 @@
       <c r="P22" s="20"/>
       <c r="Q22" s="20"/>
       <c r="R22" s="20" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="S22" s="17" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="T22" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U22" s="17" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="V22" s="21"/>
       <c r="W22" s="17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
       <c r="H23" s="17" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
@@ -4272,34 +4311,34 @@
       <c r="P23" s="20"/>
       <c r="Q23" s="20"/>
       <c r="R23" s="20" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="S23" s="17" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="T23" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U23" s="17" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="V23" s="21"/>
       <c r="W23" s="17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>69</v>
@@ -4307,10 +4346,10 @@
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
       <c r="H24" s="17" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="J24" s="17"/>
       <c r="K24" s="17"/>
@@ -4325,25 +4364,25 @@
       <c r="P24" s="20"/>
       <c r="Q24" s="20"/>
       <c r="R24" s="20" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="S24" s="17" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="T24" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U24" s="17" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="V24" s="21"/>
       <c r="W24" s="17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -4370,34 +4409,34 @@
     </row>
     <row r="26" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="K26" s="17"/>
       <c r="L26" s="18" t="s">
@@ -4416,51 +4455,51 @@
         <v>60</v>
       </c>
       <c r="S26" s="17" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="T26" s="17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="U26" s="17" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="V26" s="21" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="W26" s="17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="K27" s="17"/>
       <c r="L27" s="18" t="s">
@@ -4479,24 +4518,24 @@
         <v>60</v>
       </c>
       <c r="S27" s="17" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="T27" s="17" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="U27" s="17" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="V27" s="21" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="W27" s="17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -4523,28 +4562,28 @@
     </row>
     <row r="29" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="17" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="K29" s="17"/>
       <c r="L29" s="20"/>
@@ -4561,45 +4600,45 @@
         <v>60</v>
       </c>
       <c r="S29" s="17" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="T29" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="U29" s="17" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="V29" s="21" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="W29" s="17" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="K30" s="17"/>
       <c r="L30" s="20"/>
@@ -4616,45 +4655,45 @@
         <v>60</v>
       </c>
       <c r="S30" s="17" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="T30" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="U30" s="17" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="V30" s="21" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="W30" s="17" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
       <c r="H31" s="17" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K31" s="17"/>
       <c r="L31" s="20"/>
@@ -4675,24 +4714,24 @@
         <v>60</v>
       </c>
       <c r="S31" s="17" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="T31" s="17" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="U31" s="17" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="V31" s="21" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="W31" s="17" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -4719,35 +4758,35 @@
     </row>
     <row r="33" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E33" s="17"/>
       <c r="F33" s="15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K33" s="26" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L33" s="20"/>
       <c r="M33" s="20"/>
@@ -4761,52 +4800,52 @@
         <v>60</v>
       </c>
       <c r="S33" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="T33" s="17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="U33" s="17" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="V33" s="21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="W33" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E34" s="17"/>
       <c r="F34" s="15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K34" s="26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="L34" s="20"/>
       <c r="M34" s="19" t="s">
@@ -4822,52 +4861,52 @@
         <v>60</v>
       </c>
       <c r="S34" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="T34" s="17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="U34" s="17" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="V34" s="21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="W34" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E35" s="17"/>
       <c r="F35" s="15" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="K35" s="26" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="L35" s="20"/>
       <c r="M35" s="19" t="s">
@@ -4885,52 +4924,52 @@
         <v>60</v>
       </c>
       <c r="S35" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="T35" s="17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="U35" s="17" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="V35" s="21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="W35" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E36" s="17"/>
       <c r="F36" s="15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K36" s="26" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L36" s="18" t="s">
         <v>59</v>
@@ -4948,52 +4987,52 @@
         <v>62</v>
       </c>
       <c r="S36" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="T36" s="17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="U36" s="17" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="V36" s="21" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="W36" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E37" s="17"/>
       <c r="F37" s="15" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K37" s="26" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="L37" s="20"/>
       <c r="M37" s="20"/>
@@ -5009,52 +5048,52 @@
         <v>60</v>
       </c>
       <c r="S37" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="T37" s="17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="U37" s="17" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="V37" s="21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="W37" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E38" s="17"/>
       <c r="F38" s="15" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I38" s="17" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K38" s="26" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="L38" s="20"/>
       <c r="M38" s="20"/>
@@ -5068,49 +5107,49 @@
         <v>62</v>
       </c>
       <c r="S38" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="T38" s="17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="U38" s="17" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="V38" s="21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="W38" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E39" s="17"/>
       <c r="F39" s="15" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="20"/>
@@ -5125,49 +5164,49 @@
         <v>62</v>
       </c>
       <c r="S39" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="T39" s="17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="U39" s="17" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="V39" s="21" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="W39" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E40" s="17"/>
       <c r="F40" s="15" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="K40" s="17"/>
       <c r="L40" s="20"/>
@@ -5184,49 +5223,49 @@
         <v>62</v>
       </c>
       <c r="S40" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="T40" s="17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="U40" s="17" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="V40" s="21" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="W40" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E41" s="17"/>
       <c r="F41" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="K41" s="17"/>
       <c r="L41" s="20"/>
@@ -5241,49 +5280,49 @@
         <v>62</v>
       </c>
       <c r="S41" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="T41" s="17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="U41" s="17" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="V41" s="21" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="W41" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E42" s="17"/>
       <c r="F42" s="15" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="K42" s="17"/>
       <c r="L42" s="20"/>
@@ -5300,52 +5339,52 @@
         <v>62</v>
       </c>
       <c r="S42" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="T42" s="17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="U42" s="17" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="V42" s="21" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="W42" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="15" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K43" s="26" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L43" s="20"/>
       <c r="M43" s="19" t="s">
@@ -5361,52 +5400,52 @@
         <v>60</v>
       </c>
       <c r="S43" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="T43" s="17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="U43" s="17" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="V43" s="21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="W43" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E44" s="17"/>
       <c r="F44" s="15" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J44" s="17" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K44" s="26" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L44" s="20"/>
       <c r="M44" s="20"/>
@@ -5420,49 +5459,49 @@
         <v>62</v>
       </c>
       <c r="S44" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="T44" s="17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="U44" s="17" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="V44" s="21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="W44" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="15" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I45" s="17" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K45" s="17"/>
       <c r="L45" s="20"/>
@@ -5479,39 +5518,39 @@
         <v>60</v>
       </c>
       <c r="S45" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="T45" s="17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="U45" s="17" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="V45" s="21" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="W45" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E46" s="17"/>
       <c r="F46" s="15"/>
       <c r="G46" s="15"/>
       <c r="H46" s="17" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="I46" s="17"/>
       <c r="J46" s="17"/>
@@ -5528,24 +5567,24 @@
         <v>60</v>
       </c>
       <c r="S46" s="17" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="T46" s="17" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="U46" s="17" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="V46" s="21" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="W46" s="17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -5572,19 +5611,19 @@
     </row>
     <row r="48" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F48" s="15" t="n">
         <v>2026</v>
@@ -5593,11 +5632,11 @@
         <v>2026</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="I48" s="17"/>
       <c r="J48" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K48" s="17"/>
       <c r="L48" s="20"/>
@@ -5614,36 +5653,36 @@
         <v>60</v>
       </c>
       <c r="S48" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="T48" s="17" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="U48" s="17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="V48" s="21" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="W48" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F49" s="15" t="n">
         <v>2026</v>
@@ -5652,11 +5691,11 @@
         <v>2026</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="I49" s="17"/>
       <c r="J49" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K49" s="17"/>
       <c r="L49" s="20"/>
@@ -5673,36 +5712,36 @@
         <v>60</v>
       </c>
       <c r="S49" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="T49" s="17" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="U49" s="17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="V49" s="21" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="W49" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F50" s="15" t="s">
         <v>53</v>
@@ -5711,11 +5750,11 @@
         <v>53</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I50" s="17"/>
       <c r="J50" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K50" s="17"/>
       <c r="L50" s="20"/>
@@ -5732,36 +5771,36 @@
         <v>60</v>
       </c>
       <c r="S50" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="T50" s="17" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="U50" s="17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="V50" s="21" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="W50" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F51" s="15" t="s">
         <v>53</v>
@@ -5770,11 +5809,11 @@
         <v>53</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="I51" s="17"/>
       <c r="J51" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="20"/>
@@ -5791,36 +5830,36 @@
         <v>60</v>
       </c>
       <c r="S51" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="T51" s="17" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="U51" s="17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="V51" s="21" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="W51" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F52" s="15" t="s">
         <v>53</v>
@@ -5829,16 +5868,14 @@
         <v>53</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="I52" s="17"/>
       <c r="J52" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K52" s="17"/>
-      <c r="L52" s="18" t="s">
-        <v>59</v>
-      </c>
+      <c r="L52" s="18"/>
       <c r="M52" s="20"/>
       <c r="N52" s="20"/>
       <c r="O52" s="25" t="s">
@@ -5852,36 +5889,36 @@
         <v>60</v>
       </c>
       <c r="S52" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="T52" s="17" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="U52" s="17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="V52" s="21" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="W52" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F53" s="15" t="n">
         <v>2024</v>
@@ -5890,11 +5927,11 @@
         <v>2024</v>
       </c>
       <c r="H53" s="17" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="I53" s="17"/>
       <c r="J53" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K53" s="17"/>
       <c r="L53" s="20"/>
@@ -5911,36 +5948,36 @@
         <v>60</v>
       </c>
       <c r="S53" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="T53" s="17" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="U53" s="17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="V53" s="21" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="W53" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F54" s="15" t="n">
         <v>2023</v>
@@ -5949,11 +5986,11 @@
         <v>2023</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="I54" s="17"/>
       <c r="J54" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K54" s="17"/>
       <c r="L54" s="20"/>
@@ -5970,36 +6007,36 @@
         <v>60</v>
       </c>
       <c r="S54" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="T54" s="17" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="U54" s="17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="V54" s="21" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="W54" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F55" s="15" t="n">
         <v>2023</v>
@@ -6008,11 +6045,11 @@
         <v>2023</v>
       </c>
       <c r="H55" s="17" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="I55" s="17"/>
       <c r="J55" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K55" s="17"/>
       <c r="L55" s="20"/>
@@ -6029,36 +6066,36 @@
         <v>60</v>
       </c>
       <c r="S55" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="T55" s="17" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="U55" s="17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="V55" s="21" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="W55" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F56" s="15" t="n">
         <v>2022</v>
@@ -6067,11 +6104,11 @@
         <v>2022</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="I56" s="17"/>
       <c r="J56" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K56" s="17"/>
       <c r="L56" s="20"/>
@@ -6088,36 +6125,36 @@
         <v>60</v>
       </c>
       <c r="S56" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="T56" s="17" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="U56" s="17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="V56" s="21" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="W56" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="15" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F57" s="15" t="n">
         <v>2021</v>
@@ -6126,11 +6163,11 @@
         <v>2021</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="I57" s="17"/>
       <c r="J57" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K57" s="17"/>
       <c r="L57" s="20"/>
@@ -6147,36 +6184,36 @@
         <v>60</v>
       </c>
       <c r="S57" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="T57" s="17" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="U57" s="17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="V57" s="21" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="W57" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="15" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F58" s="15" t="n">
         <v>2022</v>
@@ -6185,11 +6222,11 @@
         <v>2022</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="I58" s="17"/>
       <c r="J58" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K58" s="17"/>
       <c r="L58" s="20"/>
@@ -6206,22 +6243,22 @@
         <v>60</v>
       </c>
       <c r="S58" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="T58" s="17" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="U58" s="17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="V58" s="21"/>
       <c r="W58" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -6248,24 +6285,24 @@
     </row>
     <row r="60" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F60" s="15"/>
       <c r="G60" s="15"/>
       <c r="H60" s="17" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="I60" s="17"/>
       <c r="J60" s="17"/>
@@ -6284,43 +6321,43 @@
         <v>60</v>
       </c>
       <c r="S60" s="17" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="T60" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U60" s="17"/>
       <c r="V60" s="21" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="W60" s="17" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="15" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G61" s="15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="I61" s="17"/>
       <c r="J61" s="17"/>
@@ -6339,43 +6376,43 @@
         <v>60</v>
       </c>
       <c r="S61" s="17" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="T61" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U61" s="17"/>
       <c r="V61" s="21" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="W61" s="17" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="15" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G62" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="I62" s="17"/>
       <c r="J62" s="17"/>
@@ -6394,43 +6431,43 @@
         <v>60</v>
       </c>
       <c r="S62" s="17" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="T62" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U62" s="17"/>
       <c r="V62" s="21" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="W62" s="17" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G63" s="15" t="s">
         <v>70</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="I63" s="17"/>
       <c r="J63" s="17"/>
@@ -6449,31 +6486,31 @@
         <v>60</v>
       </c>
       <c r="S63" s="17" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="T63" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U63" s="17"/>
       <c r="V63" s="21" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="W63" s="17" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B64" s="16" t="s">
         <v>69</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E64" s="17" t="s">
         <v>69</v>
@@ -6485,7 +6522,7 @@
         <v>71</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="I64" s="17"/>
       <c r="J64" s="17"/>
@@ -6504,31 +6541,31 @@
         <v>60</v>
       </c>
       <c r="S64" s="17" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="T64" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U64" s="17"/>
       <c r="V64" s="21" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="W64" s="17" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="15" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B65" s="16" t="s">
         <v>52</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E65" s="17" t="s">
         <v>52</v>
@@ -6540,7 +6577,7 @@
         <v>54</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="I65" s="17"/>
       <c r="J65" s="17"/>
@@ -6559,17 +6596,17 @@
         <v>60</v>
       </c>
       <c r="S65" s="17" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="T65" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U65" s="17"/>
       <c r="V65" s="21" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="W65" s="17" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -6625,28 +6662,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6659,7 +6696,7 @@
       </c>
       <c r="C2" s="29" t="n">
         <f aca="false">COUNTIF(Artifacts!$L$2:$L$124,"●")+COUNTIF(Artifacts!$L$2:$L$124,"○")</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" s="29" t="n">
         <f aca="false">COUNTIFS(Artifacts!$L$2:$L$124,"●",Artifacts!$R$2:$R$124,"Yes")</f>
@@ -6676,7 +6713,7 @@
         <v>Add</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6706,7 +6743,7 @@
         <v>OK</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6736,7 +6773,7 @@
         <v>OK</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6766,7 +6803,7 @@
         <v>OK</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6796,7 +6833,7 @@
         <v>OK</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6826,7 +6863,7 @@
         <v>Trim</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6841,7 +6878,7 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">COUNTA(Artifacts!$C$2:$C$124)</f>
@@ -6856,7 +6893,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
   </sheetData>
@@ -6892,52 +6929,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="J1" s="27" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D2" s="17"/>
       <c r="E2" s="17" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="G2" s="17" t="n">
         <v>42.08</v>
@@ -6949,27 +6986,27 @@
         <v>60</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D3" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="17" t="s">
         <v>106</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>104</v>
       </c>
       <c r="G3" s="17" t="n">
         <v>38.97</v>
@@ -6981,27 +7018,27 @@
         <v>60</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="G4" s="17" t="n">
         <v>41.88</v>
@@ -7013,27 +7050,27 @@
         <v>60</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>70</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>45.46</v>
@@ -7045,7 +7082,7 @@
         <v>60</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7053,10 +7090,10 @@
         <v>69</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>70</v>
@@ -7065,7 +7102,7 @@
         <v>53</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="G6" s="17" t="n">
         <v>32.78</v>
@@ -7077,7 +7114,7 @@
         <v>60</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7085,10 +7122,10 @@
         <v>52</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>53</v>
@@ -7097,7 +7134,7 @@
         <v>54</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>30.27</v>
@@ -7109,23 +7146,23 @@
         <v>60</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="17" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>29.76</v>
@@ -7134,24 +7171,24 @@
         <v>-95.37</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="J8" s="21"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="17" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>33.43</v>
@@ -7160,24 +7197,24 @@
         <v>-111.94</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="J9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="17" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="G10" s="17" t="n">
         <v>32.76</v>
@@ -7192,22 +7229,22 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>40.81</v>
@@ -7222,22 +7259,22 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="G12" s="17" t="n">
         <v>39.57</v>
@@ -7252,22 +7289,22 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
+        <v>495</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="C13" s="17" t="s">
         <v>492</v>
       </c>
-      <c r="B13" s="17" t="s">
-        <v>382</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>489</v>
-      </c>
       <c r="D13" s="17" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>38.72</v>
@@ -7282,13 +7319,13 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>53</v>
@@ -7297,7 +7334,7 @@
         <v>53</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
@@ -7305,18 +7342,18 @@
         <v>60</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>53</v>
@@ -7325,7 +7362,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="G15" s="17"/>
       <c r="H15" s="17"/>
@@ -7333,18 +7370,18 @@
         <v>60</v>
       </c>
       <c r="J15" s="21" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>53</v>
@@ -7353,7 +7390,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
@@ -7361,18 +7398,18 @@
         <v>60</v>
       </c>
       <c r="J16" s="21" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>71</v>
@@ -7381,7 +7418,7 @@
         <v>71</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>-22.97</v>
@@ -7393,27 +7430,27 @@
         <v>60</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
@@ -7421,27 +7458,27 @@
         <v>60</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>26.71</v>
@@ -7450,28 +7487,28 @@
         <v>-80.04</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="J19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="G20" s="17" t="n">
         <v>19.43</v>
@@ -7486,13 +7523,13 @@
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D21" s="17" t="s">
         <v>70</v>
@@ -7501,7 +7538,7 @@
         <v>70</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>41.89</v>
@@ -7513,27 +7550,27 @@
         <v>60</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
@@ -7544,12 +7581,12 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -7585,33 +7622,33 @@
         <v>24</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F1" s="27" t="s">
         <v>41</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D2" s="32" t="n">
         <v>2026</v>
@@ -7626,13 +7663,13 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="32" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D3" s="32" t="n">
         <v>2026</v>
@@ -7647,13 +7684,13 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>53</v>
@@ -7668,13 +7705,13 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>53</v>
@@ -7689,13 +7726,13 @@
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D6" s="32" t="s">
         <v>53</v>
@@ -7710,13 +7747,13 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>2024</v>
@@ -7731,13 +7768,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>2023</v>
@@ -7752,13 +7789,13 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>2023</v>
@@ -7773,13 +7810,13 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D10" s="32" t="n">
         <v>2022</v>
@@ -7794,13 +7831,13 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D11" s="32" t="n">
         <v>2021</v>
@@ -7815,13 +7852,13 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D12" s="32" t="n">
         <v>2022</v>
@@ -7836,7 +7873,7 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D13" s="28" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E13" s="28" t="n">
         <f aca="false">SUM(E2:E12)</f>
@@ -7845,7 +7882,7 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D14" s="28" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E14" s="28" t="n">
         <f aca="false">COUNTIF(F2:F12,"Yes")</f>
@@ -7854,12 +7891,12 @@
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
@@ -7889,19 +7926,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7909,13 +7946,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E2" s="33"/>
     </row>
@@ -7924,13 +7961,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E3" s="33"/>
     </row>
@@ -7939,13 +7976,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E4" s="33"/>
     </row>
@@ -7954,13 +7991,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C5" s="33" t="s">
+        <v>529</v>
+      </c>
+      <c r="D5" s="33" t="s">
         <v>526</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>523</v>
       </c>
       <c r="E5" s="33"/>
     </row>
@@ -7969,13 +8006,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C6" s="33" t="s">
+        <v>529</v>
+      </c>
+      <c r="D6" s="33" t="s">
         <v>526</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>523</v>
       </c>
       <c r="E6" s="33"/>
     </row>
@@ -7984,16 +8021,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8001,16 +8038,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8018,16 +8055,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="33" t="s">
+        <v>535</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>529</v>
+      </c>
+      <c r="D9" s="33" t="s">
         <v>532</v>
       </c>
-      <c r="C9" s="33" t="s">
-        <v>526</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>529</v>
-      </c>
       <c r="E9" s="33" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8035,16 +8072,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>529</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>532</v>
+      </c>
+      <c r="E10" s="33" t="s">
         <v>533</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>526</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>529</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8052,13 +8089,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C11" s="33" t="s">
+        <v>529</v>
+      </c>
+      <c r="D11" s="33" t="s">
         <v>526</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>523</v>
       </c>
       <c r="E11" s="33"/>
     </row>
@@ -8067,13 +8104,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E12" s="33"/>
     </row>
@@ -8082,13 +8119,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E13" s="33"/>
     </row>
@@ -8097,13 +8134,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E14" s="33"/>
     </row>
@@ -8112,13 +8149,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="33" t="s">
+        <v>542</v>
+      </c>
+      <c r="C15" s="33" t="s">
         <v>539</v>
       </c>
-      <c r="C15" s="33" t="s">
-        <v>536</v>
-      </c>
       <c r="D15" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E15" s="33"/>
     </row>
@@ -8127,16 +8164,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8144,16 +8181,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8161,16 +8198,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8178,16 +8215,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8195,16 +8232,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="33" t="s">
+        <v>546</v>
+      </c>
+      <c r="C20" s="33" t="s">
         <v>543</v>
       </c>
-      <c r="C20" s="33" t="s">
-        <v>540</v>
-      </c>
       <c r="D20" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8212,13 +8249,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E21" s="33"/>
     </row>
@@ -8227,16 +8264,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8244,16 +8281,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8261,16 +8298,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8278,13 +8315,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E25" s="33"/>
     </row>
@@ -8293,13 +8330,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="33" t="s">
+        <v>552</v>
+      </c>
+      <c r="C26" s="33" t="s">
         <v>549</v>
       </c>
-      <c r="C26" s="33" t="s">
-        <v>546</v>
-      </c>
       <c r="D26" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E26" s="33"/>
     </row>
@@ -8308,13 +8345,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E27" s="33"/>
     </row>
@@ -8323,13 +8360,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E28" s="33"/>
     </row>
@@ -8338,13 +8375,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E29" s="33"/>
     </row>
@@ -8353,13 +8390,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E30" s="33"/>
     </row>
@@ -8368,13 +8405,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E31" s="33"/>
     </row>
@@ -8383,13 +8420,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E32" s="33"/>
     </row>
@@ -8398,13 +8435,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E33" s="33"/>
     </row>
@@ -8413,13 +8450,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E34" s="33"/>
     </row>
@@ -8428,19 +8465,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E35" s="33"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="28" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C37" s="28" t="n">
         <f aca="false">COUNTA(B2:B35)</f>
@@ -8449,7 +8486,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C38" s="1" t="n">
         <f aca="false">COUNTIF(D2:D35,"Shaded")</f>
@@ -8458,7 +8495,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C39" s="1" t="n">
         <f aca="false">COUNTIF(D2:D35,"Dot")</f>
@@ -8467,7 +8504,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
   </sheetData>
@@ -8486,7 +8523,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -8498,16 +8535,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E1" s="27" t="s">
         <v>46</v>
@@ -8515,98 +8552,98 @@
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>60</v>
@@ -8617,13 +8654,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>60</v>
@@ -8634,130 +8671,130 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D13" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>60</v>
@@ -8768,13 +8805,13 @@
     </row>
     <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>60</v>
@@ -8785,13 +8822,13 @@
     </row>
     <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>60</v>
@@ -8802,13 +8839,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>60</v>
@@ -8819,106 +8856,140 @@
     </row>
     <row r="20" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="D22" s="21"/>
       <c r="E22" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="D24" s="21"/>
       <c r="E24" s="17" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="D25" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>622</v>
+        <v>625</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="17" t="s">
+        <v>626</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>627</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="17" t="s">
+        <v>626</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>630</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>631</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>629</v>
       </c>
     </row>
   </sheetData>
@@ -8937,7 +9008,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
@@ -8948,16 +9019,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8965,10 +9036,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>625</v>
+        <v>634</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>60</v>
@@ -8979,13 +9050,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>627</v>
+        <v>636</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>628</v>
+        <v>637</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8993,13 +9064,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>631</v>
+        <v>640</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>632</v>
+        <v>641</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9007,13 +9078,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>633</v>
+        <v>642</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>635</v>
+        <v>644</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9021,13 +9092,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>636</v>
+        <v>645</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>638</v>
+        <v>647</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9035,13 +9106,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>640</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9049,13 +9120,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9063,13 +9134,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>645</v>
+        <v>654</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9077,13 +9148,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>648</v>
+        <v>657</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9091,13 +9162,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>651</v>
+        <v>660</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9105,13 +9176,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9119,13 +9190,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>654</v>
+        <v>663</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9133,13 +9204,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>659</v>
+        <v>668</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9147,13 +9218,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9161,13 +9232,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>664</v>
+        <v>673</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9175,13 +9246,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9189,13 +9260,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9203,13 +9274,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>670</v>
+        <v>679</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>672</v>
+        <v>681</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9217,13 +9288,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>673</v>
+        <v>682</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>631</v>
+        <v>640</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>674</v>
+        <v>683</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9231,13 +9302,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>677</v>
+        <v>686</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9245,13 +9316,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>678</v>
+        <v>687</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>679</v>
+        <v>688</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>680</v>
+        <v>689</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9259,12 +9330,36 @@
         <v>22</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>682</v>
+        <v>691</v>
       </c>
       <c r="D23" s="21"/>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>692</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="21"/>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>693</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="21"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -403,7 +403,7 @@
     <t xml:space="preserve">Formula SAE electric powertrain (U1); biomechanical research (U2); SAE and Society of Biomedical Engineering.</t>
   </si>
   <si>
-    <t xml:space="preserve">KU School of Engineering logo (in repo)</t>
+    <t xml:space="preserve">KU School of Engineering image (used as the KU tile picture); small KU logo (in repo, not shown under the tile)</t>
   </si>
   <si>
     <t xml:space="preserve">R7</t>

--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="697">
   <si>
     <t xml:space="preserve">Site artifacts: mapping workbook</t>
   </si>
@@ -1954,7 +1954,7 @@
     <t xml:space="preserve">Austin Marathon</t>
   </si>
   <si>
-    <t xml:space="preserve">February 2024. Its logo, small, on the 2024 ring in About (name on hover).</t>
+    <t xml:space="preserve">Full marathon (26.2 mi), February 2024. Its logo, small, on the 2024 ring in About (name on hover).</t>
   </si>
   <si>
     <t xml:space="preserve">Your note</t>
@@ -2150,6 +2150,15 @@
   </si>
   <si>
     <t xml:space="preserve">Races: was the Austin Marathon the full 26.2 or the half? Which month was IRONMAN 70.3 Texas (April is the placeholder)?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austin Marathon: the full 26.2. IRONMAN month still open (April placeholder).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Origin card (click "Grant" in About): which email should it show? (The repo is public, so the address will be visible to scrapers; a forwarding address is an option.) Also: send the headshot, and edit the two draft sentences if you like.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About, contact</t>
   </si>
 </sst>
 </file>
@@ -9008,7 +9017,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
@@ -9359,7 +9368,21 @@
       <c r="C25" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="21"/>
+      <c r="D25" s="21" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>695</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>696</v>
+      </c>
+      <c r="D26" s="21"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="700">
   <si>
     <t xml:space="preserve">Site artifacts: mapping workbook</t>
   </si>
@@ -469,118 +469,127 @@
     <t xml:space="preserve">Miniature diorama of the building</t>
   </si>
   <si>
+    <t xml:space="preserve">Yes (generic massing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enovis logo (in repo); 3D model of the MPOC (generic massing, six zones) + tile still, in Lens v2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public-safe photos or layouts? NDA limits?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Industrial additive manufacturing center (EBM + SLS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built out an AM center with EBM and SLS systems for patient-specific implants.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilities, equipment siting, install sequencing, material-flow layout, production validation; scalable workflows aligned with regulatory, quality and environmental standards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBM, SLS, process validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printer / lattice part</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes (shares the MPOC model)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shares the MPOC 3D model, opening with the additive &amp; subtractive manufacturing lab highlighted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What can be shown (medical device confidentiality).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated dry mix production plant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPEI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houston, TX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ground-up automated dry mix production and packaging plant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">European / North American vendors; Italian electrical contractors for power and automation; air permitting and FAA approval; delivered on budget and schedule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolidWorks, AutoCAD, P&amp;IDs, commissioning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silo tower (strong hero)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Have CAD (render in portfolio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.4: elevation, P&amp;ID, 3D render, tower photo, interior photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dates: placeholder for now.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robotic palletizer and bag applicator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tempe, AZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added automated robotic palletizing and bag application to an existing dry mix plant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doubled the plant's total output capacity; removed two manual operations; prefab kept downtime minimal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolidWorks, AutoCAD, MS Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robot cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Have vendor render (portfolio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.4: render + photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site development: 315K sq ft brownfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houston, TX (from Dallas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turned a speculative brownfield building into a full production and distribution facility.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315K sq ft; design-build; vendor selection and contracts; multiple concurrent projects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS Project, design-build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building / diorama</t>
+  </si>
+  <si>
     <t xml:space="preserve">Generate (simple diorama)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public-safe photos or layouts? NDA limits?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Industrial additive manufacturing center (EBM + SLS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built out an AM center with EBM and SLS systems for patient-specific implants.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utilities, equipment siting, install sequencing, material-flow layout, production validation; scalable workflows aligned with regulatory, quality and environmental standards.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EBM, SLS, process validation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printer / lattice part</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate (generic lattice, no real implant)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What can be shown (medical device confidentiality).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automated dry mix production plant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPEI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Houston, TX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ground-up automated dry mix production and packaging plant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">European / North American vendors; Italian electrical contractors for power and automation; air permitting and FAA approval; delivered on budget and schedule.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolidWorks, AutoCAD, P&amp;IDs, commissioning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silo tower (strong hero)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Have CAD (render in portfolio)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.4: elevation, P&amp;ID, 3D render, tower photo, interior photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dates: placeholder for now.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robotic palletizer and bag applicator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tempe, AZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added automated robotic palletizing and bag application to an existing dry mix plant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doubled the plant's total output capacity; removed two manual operations; prefab kept downtime minimal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolidWorks, AutoCAD, MS Project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robot cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Have vendor render (portfolio)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.4: render + photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site development: 315K sq ft brownfield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Houston, TX (from Dallas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turned a speculative brownfield building into a full production and distribution facility.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315K sq ft; design-build; vendor selection and contracts; multiple concurrent projects.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS Project, design-build</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Building / diorama</t>
   </si>
   <si>
     <t xml:space="preserve">Portfolio p.5: building photo</t>
@@ -3724,10 +3733,10 @@
         <v>133</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="V12" s="21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="W12" s="17" t="s">
         <v>65</v>
@@ -3735,10 +3744,10 @@
     </row>
     <row r="13" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>128</v>
@@ -3756,13 +3765,13 @@
         <v>54</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K13" s="17"/>
       <c r="L13" s="20"/>
@@ -3779,16 +3788,16 @@
         <v>60</v>
       </c>
       <c r="S13" s="17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="V13" s="21" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="W13" s="17" t="s">
         <v>65</v>
@@ -3796,30 +3805,30 @@
     </row>
     <row r="14" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>128</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K14" s="17"/>
       <c r="L14" s="20"/>
@@ -3838,47 +3847,47 @@
         <v>60</v>
       </c>
       <c r="S14" s="17" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="T14" s="17" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U14" s="17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="V14" s="21" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="W14" s="17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>128</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
       <c r="H15" s="17" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I15" s="17" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J15" s="17" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="20"/>
@@ -3895,47 +3904,47 @@
         <v>60</v>
       </c>
       <c r="S15" s="17" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="T15" s="17" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="U15" s="17" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="V15" s="21" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="W15" s="17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>128</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
       <c r="H16" s="17" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K16" s="17"/>
       <c r="L16" s="20"/>
@@ -3952,49 +3961,49 @@
         <v>60</v>
       </c>
       <c r="S16" s="17" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="V16" s="21" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="W16" s="17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>128</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>81</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="17" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="20"/>
@@ -4013,47 +4022,47 @@
         <v>60</v>
       </c>
       <c r="S17" s="17" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="V17" s="21" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="W17" s="17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>128</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
       <c r="H18" s="17" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K18" s="17"/>
       <c r="L18" s="20"/>
@@ -4068,16 +4077,16 @@
         <v>60</v>
       </c>
       <c r="S18" s="17" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="V18" s="21" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="W18" s="17" t="s">
         <v>65</v>
@@ -4085,7 +4094,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -4112,34 +4121,34 @@
     </row>
     <row r="20" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G20" s="15" t="s">
         <v>71</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K20" s="17"/>
       <c r="L20" s="18" t="s">
@@ -4162,16 +4171,16 @@
         <v>60</v>
       </c>
       <c r="S20" s="17" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="V20" s="21" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="W20" s="17" t="s">
         <v>65</v>
@@ -4179,16 +4188,16 @@
     </row>
     <row r="21" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>69</v>
@@ -4196,10 +4205,10 @@
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
       <c r="H21" s="17" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
@@ -4214,45 +4223,45 @@
       <c r="P21" s="20"/>
       <c r="Q21" s="20"/>
       <c r="R21" s="20" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="S21" s="17" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="T21" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U21" s="17" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="V21" s="21"/>
       <c r="W21" s="17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
       <c r="H22" s="17" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="J22" s="17"/>
       <c r="K22" s="17"/>
@@ -4267,45 +4276,45 @@
       <c r="P22" s="20"/>
       <c r="Q22" s="20"/>
       <c r="R22" s="20" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="S22" s="17" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="T22" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U22" s="17" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="V22" s="21"/>
       <c r="W22" s="17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
       <c r="H23" s="17" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
@@ -4320,34 +4329,34 @@
       <c r="P23" s="20"/>
       <c r="Q23" s="20"/>
       <c r="R23" s="20" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="S23" s="17" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="T23" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U23" s="17" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="V23" s="21"/>
       <c r="W23" s="17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>69</v>
@@ -4355,10 +4364,10 @@
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
       <c r="H24" s="17" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J24" s="17"/>
       <c r="K24" s="17"/>
@@ -4373,25 +4382,25 @@
       <c r="P24" s="20"/>
       <c r="Q24" s="20"/>
       <c r="R24" s="20" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="S24" s="17" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="T24" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U24" s="17" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="V24" s="21"/>
       <c r="W24" s="17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -4418,13 +4427,13 @@
     </row>
     <row r="26" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>106</v>
@@ -4433,19 +4442,19 @@
         <v>107</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G26" s="15" t="s">
         <v>90</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="K26" s="17"/>
       <c r="L26" s="18" t="s">
@@ -4464,33 +4473,33 @@
         <v>60</v>
       </c>
       <c r="S26" s="17" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="T26" s="17" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U26" s="17" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="V26" s="21" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="W26" s="17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>107</v>
@@ -4499,16 +4508,16 @@
         <v>97</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="K27" s="17"/>
       <c r="L27" s="18" t="s">
@@ -4527,24 +4536,24 @@
         <v>60</v>
       </c>
       <c r="S27" s="17" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="T27" s="17" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="U27" s="17" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="V27" s="21" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="W27" s="17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -4571,28 +4580,28 @@
     </row>
     <row r="29" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="17" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="K29" s="17"/>
       <c r="L29" s="20"/>
@@ -4609,45 +4618,45 @@
         <v>60</v>
       </c>
       <c r="S29" s="17" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="T29" s="17" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="U29" s="17" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="V29" s="21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="W29" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="17" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K30" s="17"/>
       <c r="L30" s="20"/>
@@ -4664,45 +4673,45 @@
         <v>60</v>
       </c>
       <c r="S30" s="17" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="T30" s="17" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="U30" s="17" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="V30" s="21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="W30" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
       <c r="H31" s="17" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K31" s="17"/>
       <c r="L31" s="20"/>
@@ -4723,24 +4732,24 @@
         <v>60</v>
       </c>
       <c r="S31" s="17" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="T31" s="17" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="U31" s="17" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="V31" s="21" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="W31" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -4767,35 +4776,35 @@
     </row>
     <row r="33" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E33" s="17"/>
       <c r="F33" s="15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="K33" s="26" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L33" s="20"/>
       <c r="M33" s="20"/>
@@ -4809,52 +4818,52 @@
         <v>60</v>
       </c>
       <c r="S33" s="17" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="T33" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="U33" s="17" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="V33" s="21" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="W33" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E34" s="17"/>
       <c r="F34" s="15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K34" s="26" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="L34" s="20"/>
       <c r="M34" s="19" t="s">
@@ -4870,52 +4879,52 @@
         <v>60</v>
       </c>
       <c r="S34" s="17" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="T34" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="U34" s="17" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="V34" s="21" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="W34" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E35" s="17"/>
       <c r="F35" s="15" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="K35" s="26" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L35" s="20"/>
       <c r="M35" s="19" t="s">
@@ -4933,52 +4942,52 @@
         <v>60</v>
       </c>
       <c r="S35" s="17" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="T35" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="U35" s="17" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="V35" s="21" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="W35" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E36" s="17"/>
       <c r="F36" s="15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="K36" s="26" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L36" s="18" t="s">
         <v>59</v>
@@ -4996,52 +5005,52 @@
         <v>62</v>
       </c>
       <c r="S36" s="17" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="T36" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="U36" s="17" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="V36" s="21" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="W36" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E37" s="17"/>
       <c r="F37" s="15" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="K37" s="26" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="L37" s="20"/>
       <c r="M37" s="20"/>
@@ -5057,52 +5066,52 @@
         <v>60</v>
       </c>
       <c r="S37" s="17" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="T37" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="U37" s="17" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="V37" s="21" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="W37" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E38" s="17"/>
       <c r="F38" s="15" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I38" s="17" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="K38" s="26" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="L38" s="20"/>
       <c r="M38" s="20"/>
@@ -5116,49 +5125,49 @@
         <v>62</v>
       </c>
       <c r="S38" s="17" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="T38" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="U38" s="17" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="V38" s="21" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="W38" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E39" s="17"/>
       <c r="F39" s="15" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="20"/>
@@ -5173,49 +5182,49 @@
         <v>62</v>
       </c>
       <c r="S39" s="17" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="T39" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="U39" s="17" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="V39" s="21" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="W39" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E40" s="17"/>
       <c r="F40" s="15" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="K40" s="17"/>
       <c r="L40" s="20"/>
@@ -5232,49 +5241,49 @@
         <v>62</v>
       </c>
       <c r="S40" s="17" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="T40" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="U40" s="17" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="V40" s="21" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="W40" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E41" s="17"/>
       <c r="F41" s="15" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K41" s="17"/>
       <c r="L41" s="20"/>
@@ -5289,49 +5298,49 @@
         <v>62</v>
       </c>
       <c r="S41" s="17" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="T41" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="U41" s="17" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="V41" s="21" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="W41" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E42" s="17"/>
       <c r="F42" s="15" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="K42" s="17"/>
       <c r="L42" s="20"/>
@@ -5348,52 +5357,52 @@
         <v>62</v>
       </c>
       <c r="S42" s="17" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="T42" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="U42" s="17" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="V42" s="21" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="W42" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="15" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K43" s="26" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="L43" s="20"/>
       <c r="M43" s="19" t="s">
@@ -5409,52 +5418,52 @@
         <v>60</v>
       </c>
       <c r="S43" s="17" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="T43" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="U43" s="17" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="V43" s="21" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="W43" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E44" s="17"/>
       <c r="F44" s="15" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J44" s="17" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K44" s="26" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="L44" s="20"/>
       <c r="M44" s="20"/>
@@ -5468,49 +5477,49 @@
         <v>62</v>
       </c>
       <c r="S44" s="17" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="T44" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="U44" s="17" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="V44" s="21" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="W44" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="15" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="I45" s="17" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K45" s="17"/>
       <c r="L45" s="20"/>
@@ -5527,39 +5536,39 @@
         <v>60</v>
       </c>
       <c r="S45" s="17" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="T45" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="U45" s="17" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="V45" s="21" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="W45" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E46" s="17"/>
       <c r="F46" s="15"/>
       <c r="G46" s="15"/>
       <c r="H46" s="17" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="I46" s="17"/>
       <c r="J46" s="17"/>
@@ -5576,24 +5585,24 @@
         <v>60</v>
       </c>
       <c r="S46" s="17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="T46" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="U46" s="17" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="V46" s="21" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="W46" s="17" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -5620,19 +5629,19 @@
     </row>
     <row r="48" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F48" s="15" t="n">
         <v>2026</v>
@@ -5641,11 +5650,11 @@
         <v>2026</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="I48" s="17"/>
       <c r="J48" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K48" s="17"/>
       <c r="L48" s="20"/>
@@ -5662,36 +5671,36 @@
         <v>60</v>
       </c>
       <c r="S48" s="17" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="T48" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="U48" s="17" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="V48" s="21" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="W48" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F49" s="15" t="n">
         <v>2026</v>
@@ -5700,11 +5709,11 @@
         <v>2026</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="I49" s="17"/>
       <c r="J49" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K49" s="17"/>
       <c r="L49" s="20"/>
@@ -5721,36 +5730,36 @@
         <v>60</v>
       </c>
       <c r="S49" s="17" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="T49" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="U49" s="17" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="V49" s="21" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="W49" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F50" s="15" t="s">
         <v>53</v>
@@ -5759,11 +5768,11 @@
         <v>53</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="I50" s="17"/>
       <c r="J50" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K50" s="17"/>
       <c r="L50" s="20"/>
@@ -5780,36 +5789,36 @@
         <v>60</v>
       </c>
       <c r="S50" s="17" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="T50" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="U50" s="17" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="V50" s="21" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="W50" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F51" s="15" t="s">
         <v>53</v>
@@ -5818,11 +5827,11 @@
         <v>53</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I51" s="17"/>
       <c r="J51" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="20"/>
@@ -5839,36 +5848,36 @@
         <v>60</v>
       </c>
       <c r="S51" s="17" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="T51" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="U51" s="17" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="V51" s="21" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="W51" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F52" s="15" t="s">
         <v>53</v>
@@ -5877,11 +5886,11 @@
         <v>53</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I52" s="17"/>
       <c r="J52" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K52" s="17"/>
       <c r="L52" s="18"/>
@@ -5898,36 +5907,36 @@
         <v>60</v>
       </c>
       <c r="S52" s="17" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="T52" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="U52" s="17" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="V52" s="21" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="W52" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F53" s="15" t="n">
         <v>2024</v>
@@ -5936,11 +5945,11 @@
         <v>2024</v>
       </c>
       <c r="H53" s="17" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I53" s="17"/>
       <c r="J53" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K53" s="17"/>
       <c r="L53" s="20"/>
@@ -5957,36 +5966,36 @@
         <v>60</v>
       </c>
       <c r="S53" s="17" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="T53" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="U53" s="17" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="V53" s="21" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="W53" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F54" s="15" t="n">
         <v>2023</v>
@@ -5995,11 +6004,11 @@
         <v>2023</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="I54" s="17"/>
       <c r="J54" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K54" s="17"/>
       <c r="L54" s="20"/>
@@ -6016,36 +6025,36 @@
         <v>60</v>
       </c>
       <c r="S54" s="17" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="T54" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="U54" s="17" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="V54" s="21" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="W54" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F55" s="15" t="n">
         <v>2023</v>
@@ -6054,11 +6063,11 @@
         <v>2023</v>
       </c>
       <c r="H55" s="17" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I55" s="17"/>
       <c r="J55" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K55" s="17"/>
       <c r="L55" s="20"/>
@@ -6075,36 +6084,36 @@
         <v>60</v>
       </c>
       <c r="S55" s="17" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="T55" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="U55" s="17" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="V55" s="21" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="W55" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F56" s="15" t="n">
         <v>2022</v>
@@ -6113,11 +6122,11 @@
         <v>2022</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="I56" s="17"/>
       <c r="J56" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K56" s="17"/>
       <c r="L56" s="20"/>
@@ -6134,36 +6143,36 @@
         <v>60</v>
       </c>
       <c r="S56" s="17" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="T56" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="U56" s="17" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="V56" s="21" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="W56" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="15" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F57" s="15" t="n">
         <v>2021</v>
@@ -6172,11 +6181,11 @@
         <v>2021</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="I57" s="17"/>
       <c r="J57" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K57" s="17"/>
       <c r="L57" s="20"/>
@@ -6193,36 +6202,36 @@
         <v>60</v>
       </c>
       <c r="S57" s="17" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="T57" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="U57" s="17" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="V57" s="21" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="W57" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="15" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F58" s="15" t="n">
         <v>2022</v>
@@ -6231,11 +6240,11 @@
         <v>2022</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="I58" s="17"/>
       <c r="J58" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K58" s="17"/>
       <c r="L58" s="20"/>
@@ -6252,22 +6261,22 @@
         <v>60</v>
       </c>
       <c r="S58" s="17" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="T58" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="U58" s="17" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="V58" s="21"/>
       <c r="W58" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -6294,24 +6303,24 @@
     </row>
     <row r="60" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F60" s="15"/>
       <c r="G60" s="15"/>
       <c r="H60" s="17" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I60" s="17"/>
       <c r="J60" s="17"/>
@@ -6330,31 +6339,31 @@
         <v>60</v>
       </c>
       <c r="S60" s="17" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="T60" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U60" s="17"/>
       <c r="V60" s="21" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="W60" s="17" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="15" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B61" s="16" t="s">
         <v>107</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E61" s="17" t="s">
         <v>107</v>
@@ -6366,7 +6375,7 @@
         <v>90</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="I61" s="17"/>
       <c r="J61" s="17"/>
@@ -6385,31 +6394,31 @@
         <v>60</v>
       </c>
       <c r="S61" s="17" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="T61" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U61" s="17"/>
       <c r="V61" s="21" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="W61" s="17" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="15" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B62" s="16" t="s">
         <v>89</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E62" s="17" t="s">
         <v>89</v>
@@ -6421,7 +6430,7 @@
         <v>81</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="I62" s="17"/>
       <c r="J62" s="17"/>
@@ -6440,31 +6449,31 @@
         <v>60</v>
       </c>
       <c r="S62" s="17" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="T62" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U62" s="17"/>
       <c r="V62" s="21" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="W62" s="17" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B63" s="16" t="s">
         <v>80</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E63" s="17" t="s">
         <v>80</v>
@@ -6476,7 +6485,7 @@
         <v>70</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="I63" s="17"/>
       <c r="J63" s="17"/>
@@ -6495,31 +6504,31 @@
         <v>60</v>
       </c>
       <c r="S63" s="17" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="T63" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U63" s="17"/>
       <c r="V63" s="21" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="W63" s="17" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B64" s="16" t="s">
         <v>69</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E64" s="17" t="s">
         <v>69</v>
@@ -6531,7 +6540,7 @@
         <v>71</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="I64" s="17"/>
       <c r="J64" s="17"/>
@@ -6550,31 +6559,31 @@
         <v>60</v>
       </c>
       <c r="S64" s="17" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="T64" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U64" s="17"/>
       <c r="V64" s="21" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="W64" s="17" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="15" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B65" s="16" t="s">
         <v>52</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E65" s="17" t="s">
         <v>52</v>
@@ -6586,7 +6595,7 @@
         <v>54</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="I65" s="17"/>
       <c r="J65" s="17"/>
@@ -6605,17 +6614,17 @@
         <v>60</v>
       </c>
       <c r="S65" s="17" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="T65" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U65" s="17"/>
       <c r="V65" s="21" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="W65" s="17" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -6671,28 +6680,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6722,7 +6731,7 @@
         <v>Add</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6752,7 +6761,7 @@
         <v>OK</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6782,7 +6791,7 @@
         <v>OK</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6812,7 +6821,7 @@
         <v>OK</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6842,7 +6851,7 @@
         <v>OK</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6872,7 +6881,7 @@
         <v>Trim</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6887,7 +6896,7 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">COUNTA(Artifacts!$C$2:$C$124)</f>
@@ -6902,7 +6911,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -6938,52 +6947,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="J1" s="27" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D2" s="17"/>
       <c r="E2" s="17" t="s">
         <v>108</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="G2" s="17" t="n">
         <v>42.08</v>
@@ -6995,7 +7004,7 @@
         <v>60</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7003,10 +7012,10 @@
         <v>107</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>108</v>
@@ -7027,7 +7036,7 @@
         <v>60</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7035,10 +7044,10 @@
         <v>89</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D4" s="17" t="s">
         <v>90</v>
@@ -7047,7 +7056,7 @@
         <v>81</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="G4" s="17" t="n">
         <v>41.88</v>
@@ -7059,18 +7068,18 @@
         <v>60</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>81</v>
@@ -7079,7 +7088,7 @@
         <v>70</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>45.46</v>
@@ -7091,7 +7100,7 @@
         <v>60</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7099,10 +7108,10 @@
         <v>69</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>70</v>
@@ -7111,7 +7120,7 @@
         <v>53</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="G6" s="17" t="n">
         <v>32.78</v>
@@ -7123,7 +7132,7 @@
         <v>60</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7131,10 +7140,10 @@
         <v>52</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>53</v>
@@ -7143,7 +7152,7 @@
         <v>54</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>30.27</v>
@@ -7155,23 +7164,23 @@
         <v>60</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="17" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>29.76</v>
@@ -7180,24 +7189,24 @@
         <v>-95.37</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J8" s="21"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="17" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>33.43</v>
@@ -7206,24 +7215,24 @@
         <v>-111.94</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="17" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G10" s="17" t="n">
         <v>32.76</v>
@@ -7238,13 +7247,13 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>90</v>
@@ -7253,7 +7262,7 @@
         <v>90</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>40.81</v>
@@ -7268,22 +7277,22 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="G12" s="17" t="n">
         <v>39.57</v>
@@ -7298,22 +7307,22 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
+        <v>498</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="C13" s="17" t="s">
         <v>495</v>
       </c>
-      <c r="B13" s="17" t="s">
-        <v>385</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>492</v>
-      </c>
       <c r="D13" s="17" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>38.72</v>
@@ -7328,13 +7337,13 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>53</v>
@@ -7343,7 +7352,7 @@
         <v>53</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
@@ -7351,18 +7360,18 @@
         <v>60</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>53</v>
@@ -7371,7 +7380,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="G15" s="17"/>
       <c r="H15" s="17"/>
@@ -7379,18 +7388,18 @@
         <v>60</v>
       </c>
       <c r="J15" s="21" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>53</v>
@@ -7399,7 +7408,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
@@ -7407,18 +7416,18 @@
         <v>60</v>
       </c>
       <c r="J16" s="21" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>71</v>
@@ -7427,7 +7436,7 @@
         <v>71</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>-22.97</v>
@@ -7439,27 +7448,27 @@
         <v>60</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
@@ -7467,27 +7476,27 @@
         <v>60</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>26.71</v>
@@ -7496,28 +7505,28 @@
         <v>-80.04</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="G20" s="17" t="n">
         <v>19.43</v>
@@ -7532,13 +7541,13 @@
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D21" s="17" t="s">
         <v>70</v>
@@ -7547,7 +7556,7 @@
         <v>70</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>41.89</v>
@@ -7559,27 +7568,27 @@
         <v>60</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
@@ -7590,12 +7599,12 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
@@ -7631,33 +7640,33 @@
         <v>24</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F1" s="27" t="s">
         <v>41</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D2" s="32" t="n">
         <v>2026</v>
@@ -7672,13 +7681,13 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="32" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D3" s="32" t="n">
         <v>2026</v>
@@ -7693,13 +7702,13 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>53</v>
@@ -7714,13 +7723,13 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>53</v>
@@ -7735,13 +7744,13 @@
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D6" s="32" t="s">
         <v>53</v>
@@ -7756,13 +7765,13 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>2024</v>
@@ -7777,13 +7786,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>2023</v>
@@ -7798,13 +7807,13 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>2023</v>
@@ -7819,13 +7828,13 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D10" s="32" t="n">
         <v>2022</v>
@@ -7840,13 +7849,13 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D11" s="32" t="n">
         <v>2021</v>
@@ -7861,13 +7870,13 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D12" s="32" t="n">
         <v>2022</v>
@@ -7882,7 +7891,7 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D13" s="28" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E13" s="28" t="n">
         <f aca="false">SUM(E2:E12)</f>
@@ -7891,7 +7900,7 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D14" s="28" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E14" s="28" t="n">
         <f aca="false">COUNTIF(F2:F12,"Yes")</f>
@@ -7900,12 +7909,12 @@
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -7935,19 +7944,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7955,13 +7964,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E2" s="33"/>
     </row>
@@ -7970,13 +7979,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E3" s="33"/>
     </row>
@@ -7985,13 +7994,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E4" s="33"/>
     </row>
@@ -8000,13 +8009,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C5" s="33" t="s">
+        <v>532</v>
+      </c>
+      <c r="D5" s="33" t="s">
         <v>529</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>526</v>
       </c>
       <c r="E5" s="33"/>
     </row>
@@ -8015,13 +8024,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C6" s="33" t="s">
+        <v>532</v>
+      </c>
+      <c r="D6" s="33" t="s">
         <v>529</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>526</v>
       </c>
       <c r="E6" s="33"/>
     </row>
@@ -8030,16 +8039,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8047,16 +8056,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8064,16 +8073,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="33" t="s">
+        <v>538</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>532</v>
+      </c>
+      <c r="D9" s="33" t="s">
         <v>535</v>
       </c>
-      <c r="C9" s="33" t="s">
-        <v>529</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>532</v>
-      </c>
       <c r="E9" s="33" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8081,16 +8090,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="33" t="s">
+        <v>539</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>532</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>535</v>
+      </c>
+      <c r="E10" s="33" t="s">
         <v>536</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>529</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>532</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8098,13 +8107,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C11" s="33" t="s">
+        <v>532</v>
+      </c>
+      <c r="D11" s="33" t="s">
         <v>529</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>526</v>
       </c>
       <c r="E11" s="33"/>
     </row>
@@ -8113,13 +8122,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E12" s="33"/>
     </row>
@@ -8128,13 +8137,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E13" s="33"/>
     </row>
@@ -8143,13 +8152,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E14" s="33"/>
     </row>
@@ -8158,13 +8167,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="33" t="s">
+        <v>545</v>
+      </c>
+      <c r="C15" s="33" t="s">
         <v>542</v>
       </c>
-      <c r="C15" s="33" t="s">
-        <v>539</v>
-      </c>
       <c r="D15" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E15" s="33"/>
     </row>
@@ -8173,16 +8182,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8190,16 +8199,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8207,16 +8216,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8224,16 +8233,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8241,16 +8250,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="33" t="s">
+        <v>549</v>
+      </c>
+      <c r="C20" s="33" t="s">
         <v>546</v>
       </c>
-      <c r="C20" s="33" t="s">
-        <v>543</v>
-      </c>
       <c r="D20" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8258,13 +8267,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E21" s="33"/>
     </row>
@@ -8273,16 +8282,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8290,16 +8299,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8307,16 +8316,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8324,13 +8333,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E25" s="33"/>
     </row>
@@ -8339,13 +8348,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="33" t="s">
+        <v>555</v>
+      </c>
+      <c r="C26" s="33" t="s">
         <v>552</v>
       </c>
-      <c r="C26" s="33" t="s">
-        <v>549</v>
-      </c>
       <c r="D26" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E26" s="33"/>
     </row>
@@ -8354,13 +8363,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E27" s="33"/>
     </row>
@@ -8369,13 +8378,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E28" s="33"/>
     </row>
@@ -8384,13 +8393,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E29" s="33"/>
     </row>
@@ -8399,13 +8408,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E30" s="33"/>
     </row>
@@ -8414,13 +8423,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E31" s="33"/>
     </row>
@@ -8429,13 +8438,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E32" s="33"/>
     </row>
@@ -8444,13 +8453,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E33" s="33"/>
     </row>
@@ -8459,13 +8468,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E34" s="33"/>
     </row>
@@ -8474,19 +8483,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E35" s="33"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="28" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C37" s="28" t="n">
         <f aca="false">COUNTA(B2:B35)</f>
@@ -8495,7 +8504,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C38" s="1" t="n">
         <f aca="false">COUNTIF(D2:D35,"Shaded")</f>
@@ -8504,7 +8513,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C39" s="1" t="n">
         <f aca="false">COUNTIF(D2:D35,"Dot")</f>
@@ -8513,7 +8522,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
     </row>
   </sheetData>
@@ -8544,16 +8553,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E1" s="27" t="s">
         <v>46</v>
@@ -8561,98 +8570,98 @@
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>60</v>
@@ -8663,13 +8672,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>60</v>
@@ -8680,130 +8689,130 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D13" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>60</v>
@@ -8814,13 +8823,13 @@
     </row>
     <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>60</v>
@@ -8831,13 +8840,13 @@
     </row>
     <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>60</v>
@@ -8848,13 +8857,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>60</v>
@@ -8865,140 +8874,140 @@
     </row>
     <row r="20" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="D22" s="21"/>
       <c r="E22" s="17" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="17" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="D24" s="21"/>
       <c r="E24" s="17" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D25" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="D28" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="D29" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
   </sheetData>
@@ -9028,16 +9037,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9045,10 +9054,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>60</v>
@@ -9059,13 +9068,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9073,13 +9082,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9087,13 +9096,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9101,13 +9110,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9115,13 +9124,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9129,13 +9138,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9143,13 +9152,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9157,13 +9166,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9171,13 +9180,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9185,13 +9194,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9199,13 +9208,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9213,13 +9222,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9227,13 +9236,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9241,13 +9250,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9255,13 +9264,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9269,13 +9278,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9283,13 +9292,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9297,13 +9306,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9311,13 +9320,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9325,13 +9334,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9339,10 +9348,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="D23" s="21"/>
     </row>
@@ -9351,7 +9360,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>35</v>
@@ -9363,13 +9372,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9377,10 +9386,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="D26" s="21"/>
     </row>

--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="708">
   <si>
     <t xml:space="preserve">Site artifacts: mapping workbook</t>
   </si>
@@ -472,7 +472,7 @@
     <t xml:space="preserve">Yes (generic massing)</t>
   </si>
   <si>
-    <t xml:space="preserve">Enovis logo (in repo); 3D model of the MPOC (generic massing, six zones) + tile still, in Lens v2</t>
+    <t xml:space="preserve">Enovis logo (in repo); 3D model of the MPOC (generic massing, six zones) + tile still + About hover turntable, in Lens v2</t>
   </si>
   <si>
     <t xml:space="preserve">Public-safe photos or layouts? NDA limits?</t>
@@ -529,96 +529,102 @@
     <t xml:space="preserve">Silo tower (strong hero)</t>
   </si>
   <si>
+    <t xml:space="preserve">Yes (Grant's exterior model, v11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.4: elevation, P&amp;ID, 3D render, tower photo, interior photo. Exterior 3D model (GLB) live in Lens v2 (zones: silo &amp; mixing tower, packaging &amp; warehouse, offices, truck court &amp; site) + tile still + About hover turntable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dates: placeholder for now (About shows it at ~March 2022).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robotic palletizer and bag applicator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tempe, AZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added automated robotic palletizing and bag application to an existing dry mix plant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doubled the plant's total output capacity; removed two manual operations; prefab kept downtime minimal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolidWorks, AutoCAD, MS Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robot cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Have vendor render (portfolio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.4: render + photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dates: placeholder for now.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site development: 315K sq ft brownfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houston, TX (from Dallas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turned a speculative brownfield building into a full production and distribution facility.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315K sq ft; design-build; vendor selection and contracts; multiple concurrent projects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS Project, design-build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building / diorama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate (simple diorama)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.5: building photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lived in Dallas, travelled to Houston for this project. Dates: placeholder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-line static mixing process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milan → Dallas, TX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First production version of a new static mixing technology, prototyped in Milan and built in Dallas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production time −35%; manual operations removed; enabled bulk material purchasing; equipment procured from Europe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">European vendors, electromechanical contractors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixing skid (prototype → production story)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Have CAD (render in portfolio)</t>
   </si>
   <si>
-    <t xml:space="preserve">Portfolio p.4: elevation, P&amp;ID, 3D render, tower photo, interior photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dates: placeholder for now.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robotic palletizer and bag applicator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tempe, AZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added automated robotic palletizing and bag application to an existing dry mix plant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doubled the plant's total output capacity; removed two manual operations; prefab kept downtime minimal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolidWorks, AutoCAD, MS Project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robot cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Have vendor render (portfolio)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.4: render + photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site development: 315K sq ft brownfield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Houston, TX (from Dallas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turned a speculative brownfield building into a full production and distribution facility.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315K sq ft; design-build; vendor selection and contracts; multiple concurrent projects.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS Project, design-build</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Building / diorama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate (simple diorama)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.5: building photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lived in Dallas, travelled to Houston for this project. Dates: placeholder.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-line static mixing process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milan → Dallas, TX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First production version of a new static mixing technology, prototyped in Milan and built in Dallas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production time −35%; manual operations removed; enabled bulk material purchasing; equipment procured from Europe.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">European vendors, electromechanical contractors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mixing skid (prototype → production story)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Portfolio p.5: drawing, 3D render, photo</t>
   </si>
   <si>
@@ -2168,6 +2174,24 @@
   </si>
   <si>
     <t xml:space="preserve">About, contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquid admixtures plant (E7): can you send its 3D model (GLB, like the dry mix plant) or snapshots? It would get the same live model, still and About turntable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E7, 3D models</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The dry mix plant now sits in About (2022 ring, March placeholder) so its 3D tile can turn on hover. Keep it there, and which month did it start?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E3, About</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dry mix plant zone names: "Silo &amp; mixing tower", "Packaging &amp; warehouse", "Offices", "Truck court &amp; site". Rename any?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E3, 3D model</t>
   </si>
 </sst>
 </file>
@@ -3831,7 +3855,9 @@
         <v>151</v>
       </c>
       <c r="K14" s="17"/>
-      <c r="L14" s="20"/>
+      <c r="L14" s="18" t="s">
+        <v>59</v>
+      </c>
       <c r="M14" s="19" t="s">
         <v>58</v>
       </c>
@@ -3913,7 +3939,7 @@
         <v>165</v>
       </c>
       <c r="V15" s="21" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="W15" s="17" t="s">
         <v>156</v>
@@ -3921,10 +3947,10 @@
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>128</v>
@@ -3933,18 +3959,18 @@
         <v>147</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
       <c r="H16" s="17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K16" s="17"/>
       <c r="L16" s="20"/>
@@ -3961,16 +3987,16 @@
         <v>60</v>
       </c>
       <c r="S16" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="V16" s="21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W16" s="17" t="s">
         <v>156</v>
@@ -3978,10 +4004,10 @@
     </row>
     <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>128</v>
@@ -3990,20 +4016,20 @@
         <v>147</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>81</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="20"/>
@@ -4022,16 +4048,16 @@
         <v>60</v>
       </c>
       <c r="S17" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="V17" s="21" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="W17" s="17" t="s">
         <v>156</v>
@@ -4039,10 +4065,10 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>128</v>
@@ -4051,18 +4077,18 @@
         <v>147</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
       <c r="H18" s="17" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K18" s="17"/>
       <c r="L18" s="20"/>
@@ -4077,16 +4103,16 @@
         <v>60</v>
       </c>
       <c r="S18" s="17" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="V18" s="21" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="W18" s="17" t="s">
         <v>65</v>
@@ -4094,7 +4120,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -4121,34 +4147,34 @@
     </row>
     <row r="20" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G20" s="15" t="s">
         <v>71</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K20" s="17"/>
       <c r="L20" s="18" t="s">
@@ -4171,16 +4197,16 @@
         <v>60</v>
       </c>
       <c r="S20" s="17" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="V20" s="21" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="W20" s="17" t="s">
         <v>65</v>
@@ -4188,16 +4214,16 @@
     </row>
     <row r="21" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>69</v>
@@ -4205,10 +4231,10 @@
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
       <c r="H21" s="17" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
@@ -4223,16 +4249,16 @@
       <c r="P21" s="20"/>
       <c r="Q21" s="20"/>
       <c r="R21" s="20" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="S21" s="17" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="T21" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U21" s="17" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="V21" s="21"/>
       <c r="W21" s="17" t="s">
@@ -4241,16 +4267,16 @@
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>148</v>
@@ -4258,10 +4284,10 @@
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
       <c r="H22" s="17" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="J22" s="17"/>
       <c r="K22" s="17"/>
@@ -4276,16 +4302,16 @@
       <c r="P22" s="20"/>
       <c r="Q22" s="20"/>
       <c r="R22" s="20" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="S22" s="17" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="T22" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U22" s="17" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="V22" s="21"/>
       <c r="W22" s="17" t="s">
@@ -4294,27 +4320,27 @@
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
       <c r="H23" s="17" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
@@ -4329,16 +4355,16 @@
       <c r="P23" s="20"/>
       <c r="Q23" s="20"/>
       <c r="R23" s="20" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="S23" s="17" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="T23" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U23" s="17" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="V23" s="21"/>
       <c r="W23" s="17" t="s">
@@ -4347,16 +4373,16 @@
     </row>
     <row r="24" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>69</v>
@@ -4364,10 +4390,10 @@
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
       <c r="H24" s="17" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J24" s="17"/>
       <c r="K24" s="17"/>
@@ -4382,16 +4408,16 @@
       <c r="P24" s="20"/>
       <c r="Q24" s="20"/>
       <c r="R24" s="20" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="S24" s="17" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="T24" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U24" s="17" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="V24" s="21"/>
       <c r="W24" s="17" t="s">
@@ -4400,7 +4426,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -4427,13 +4453,13 @@
     </row>
     <row r="26" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>106</v>
@@ -4442,19 +4468,19 @@
         <v>107</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G26" s="15" t="s">
         <v>90</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K26" s="17"/>
       <c r="L26" s="18" t="s">
@@ -4473,16 +4499,16 @@
         <v>60</v>
       </c>
       <c r="S26" s="17" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="T26" s="17" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="U26" s="17" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="V26" s="21" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="W26" s="17" t="s">
         <v>156</v>
@@ -4490,16 +4516,16 @@
     </row>
     <row r="27" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>107</v>
@@ -4508,16 +4534,16 @@
         <v>97</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K27" s="17"/>
       <c r="L27" s="18" t="s">
@@ -4536,16 +4562,16 @@
         <v>60</v>
       </c>
       <c r="S27" s="17" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="T27" s="17" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="U27" s="17" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="V27" s="21" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="W27" s="17" t="s">
         <v>156</v>
@@ -4553,7 +4579,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -4580,28 +4606,28 @@
     </row>
     <row r="29" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="17" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="K29" s="17"/>
       <c r="L29" s="20"/>
@@ -4618,45 +4644,45 @@
         <v>60</v>
       </c>
       <c r="S29" s="17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="T29" s="17" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="U29" s="17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="V29" s="21" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="W29" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="17" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K30" s="17"/>
       <c r="L30" s="20"/>
@@ -4673,45 +4699,45 @@
         <v>60</v>
       </c>
       <c r="S30" s="17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="T30" s="17" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="U30" s="17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="V30" s="21" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="W30" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
       <c r="H31" s="17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K31" s="17"/>
       <c r="L31" s="20"/>
@@ -4732,24 +4758,24 @@
         <v>60</v>
       </c>
       <c r="S31" s="17" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="T31" s="17" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="U31" s="17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="V31" s="21" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="W31" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -4776,35 +4802,35 @@
     </row>
     <row r="33" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E33" s="17"/>
       <c r="F33" s="15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K33" s="26" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L33" s="20"/>
       <c r="M33" s="20"/>
@@ -4818,52 +4844,52 @@
         <v>60</v>
       </c>
       <c r="S33" s="17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="T33" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="U33" s="17" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="V33" s="21" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="W33" s="17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E34" s="17"/>
       <c r="F34" s="15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K34" s="26" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L34" s="20"/>
       <c r="M34" s="19" t="s">
@@ -4879,52 +4905,52 @@
         <v>60</v>
       </c>
       <c r="S34" s="17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="T34" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="U34" s="17" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="V34" s="21" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="W34" s="17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E35" s="17"/>
       <c r="F35" s="15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="K35" s="26" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L35" s="20"/>
       <c r="M35" s="19" t="s">
@@ -4942,52 +4968,52 @@
         <v>60</v>
       </c>
       <c r="S35" s="17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="T35" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="U35" s="17" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="V35" s="21" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="W35" s="17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E36" s="17"/>
       <c r="F36" s="15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K36" s="26" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L36" s="18" t="s">
         <v>59</v>
@@ -5005,52 +5031,52 @@
         <v>62</v>
       </c>
       <c r="S36" s="17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="T36" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="U36" s="17" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="V36" s="21" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="W36" s="17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E37" s="17"/>
       <c r="F37" s="15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K37" s="26" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L37" s="20"/>
       <c r="M37" s="20"/>
@@ -5066,52 +5092,52 @@
         <v>60</v>
       </c>
       <c r="S37" s="17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="T37" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="U37" s="17" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="V37" s="21" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="W37" s="17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E38" s="17"/>
       <c r="F38" s="15" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I38" s="17" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K38" s="26" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L38" s="20"/>
       <c r="M38" s="20"/>
@@ -5125,49 +5151,49 @@
         <v>62</v>
       </c>
       <c r="S38" s="17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="T38" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="U38" s="17" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="V38" s="21" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="W38" s="17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E39" s="17"/>
       <c r="F39" s="15" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="20"/>
@@ -5182,49 +5208,49 @@
         <v>62</v>
       </c>
       <c r="S39" s="17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="T39" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="U39" s="17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="V39" s="21" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="W39" s="17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E40" s="17"/>
       <c r="F40" s="15" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K40" s="17"/>
       <c r="L40" s="20"/>
@@ -5241,49 +5267,49 @@
         <v>62</v>
       </c>
       <c r="S40" s="17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="T40" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="U40" s="17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="V40" s="21" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="W40" s="17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E41" s="17"/>
       <c r="F41" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K41" s="17"/>
       <c r="L41" s="20"/>
@@ -5298,49 +5324,49 @@
         <v>62</v>
       </c>
       <c r="S41" s="17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="T41" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="U41" s="17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="V41" s="21" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="W41" s="17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E42" s="17"/>
       <c r="F42" s="15" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K42" s="17"/>
       <c r="L42" s="20"/>
@@ -5357,52 +5383,52 @@
         <v>62</v>
       </c>
       <c r="S42" s="17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="T42" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="U42" s="17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="V42" s="21" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="W42" s="17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K43" s="26" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L43" s="20"/>
       <c r="M43" s="19" t="s">
@@ -5418,52 +5444,52 @@
         <v>60</v>
       </c>
       <c r="S43" s="17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="T43" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="U43" s="17" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="V43" s="21" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="W43" s="17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E44" s="17"/>
       <c r="F44" s="15" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J44" s="17" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K44" s="26" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L44" s="20"/>
       <c r="M44" s="20"/>
@@ -5477,49 +5503,49 @@
         <v>62</v>
       </c>
       <c r="S44" s="17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="T44" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="U44" s="17" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="V44" s="21" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="W44" s="17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="15" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="I45" s="17" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K45" s="17"/>
       <c r="L45" s="20"/>
@@ -5536,39 +5562,39 @@
         <v>60</v>
       </c>
       <c r="S45" s="17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="T45" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="U45" s="17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="V45" s="21" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="W45" s="17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E46" s="17"/>
       <c r="F46" s="15"/>
       <c r="G46" s="15"/>
       <c r="H46" s="17" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="I46" s="17"/>
       <c r="J46" s="17"/>
@@ -5585,24 +5611,24 @@
         <v>60</v>
       </c>
       <c r="S46" s="17" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="T46" s="17" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="U46" s="17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="V46" s="21" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="W46" s="17" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -5629,19 +5655,19 @@
     </row>
     <row r="48" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F48" s="15" t="n">
         <v>2026</v>
@@ -5650,11 +5676,11 @@
         <v>2026</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="I48" s="17"/>
       <c r="J48" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K48" s="17"/>
       <c r="L48" s="20"/>
@@ -5671,36 +5697,36 @@
         <v>60</v>
       </c>
       <c r="S48" s="17" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="T48" s="17" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="U48" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="V48" s="21" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="W48" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F49" s="15" t="n">
         <v>2026</v>
@@ -5709,11 +5735,11 @@
         <v>2026</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I49" s="17"/>
       <c r="J49" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K49" s="17"/>
       <c r="L49" s="20"/>
@@ -5730,36 +5756,36 @@
         <v>60</v>
       </c>
       <c r="S49" s="17" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="T49" s="17" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="U49" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="V49" s="21" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="W49" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F50" s="15" t="s">
         <v>53</v>
@@ -5768,11 +5794,11 @@
         <v>53</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I50" s="17"/>
       <c r="J50" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K50" s="17"/>
       <c r="L50" s="20"/>
@@ -5789,36 +5815,36 @@
         <v>60</v>
       </c>
       <c r="S50" s="17" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="T50" s="17" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="U50" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="V50" s="21" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="W50" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F51" s="15" t="s">
         <v>53</v>
@@ -5827,11 +5853,11 @@
         <v>53</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I51" s="17"/>
       <c r="J51" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="20"/>
@@ -5848,36 +5874,36 @@
         <v>60</v>
       </c>
       <c r="S51" s="17" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="T51" s="17" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="U51" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="V51" s="21" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="W51" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F52" s="15" t="s">
         <v>53</v>
@@ -5886,11 +5912,11 @@
         <v>53</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="I52" s="17"/>
       <c r="J52" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K52" s="17"/>
       <c r="L52" s="18"/>
@@ -5907,36 +5933,36 @@
         <v>60</v>
       </c>
       <c r="S52" s="17" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="T52" s="17" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="U52" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="V52" s="21" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="W52" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F53" s="15" t="n">
         <v>2024</v>
@@ -5945,11 +5971,11 @@
         <v>2024</v>
       </c>
       <c r="H53" s="17" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="I53" s="17"/>
       <c r="J53" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K53" s="17"/>
       <c r="L53" s="20"/>
@@ -5966,36 +5992,36 @@
         <v>60</v>
       </c>
       <c r="S53" s="17" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="T53" s="17" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="U53" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="V53" s="21" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="W53" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F54" s="15" t="n">
         <v>2023</v>
@@ -6004,11 +6030,11 @@
         <v>2023</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="I54" s="17"/>
       <c r="J54" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K54" s="17"/>
       <c r="L54" s="20"/>
@@ -6025,36 +6051,36 @@
         <v>60</v>
       </c>
       <c r="S54" s="17" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="T54" s="17" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="U54" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="V54" s="21" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="W54" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F55" s="15" t="n">
         <v>2023</v>
@@ -6063,11 +6089,11 @@
         <v>2023</v>
       </c>
       <c r="H55" s="17" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="I55" s="17"/>
       <c r="J55" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K55" s="17"/>
       <c r="L55" s="20"/>
@@ -6084,36 +6110,36 @@
         <v>60</v>
       </c>
       <c r="S55" s="17" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="T55" s="17" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="U55" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="V55" s="21" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="W55" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F56" s="15" t="n">
         <v>2022</v>
@@ -6122,11 +6148,11 @@
         <v>2022</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="I56" s="17"/>
       <c r="J56" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K56" s="17"/>
       <c r="L56" s="20"/>
@@ -6143,36 +6169,36 @@
         <v>60</v>
       </c>
       <c r="S56" s="17" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="T56" s="17" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="U56" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="V56" s="21" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="W56" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="15" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F57" s="15" t="n">
         <v>2021</v>
@@ -6181,11 +6207,11 @@
         <v>2021</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="I57" s="17"/>
       <c r="J57" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K57" s="17"/>
       <c r="L57" s="20"/>
@@ -6202,36 +6228,36 @@
         <v>60</v>
       </c>
       <c r="S57" s="17" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="T57" s="17" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="U57" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="V57" s="21" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="W57" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="15" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F58" s="15" t="n">
         <v>2022</v>
@@ -6240,11 +6266,11 @@
         <v>2022</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="I58" s="17"/>
       <c r="J58" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K58" s="17"/>
       <c r="L58" s="20"/>
@@ -6261,22 +6287,22 @@
         <v>60</v>
       </c>
       <c r="S58" s="17" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="T58" s="17" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="U58" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="V58" s="21"/>
       <c r="W58" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -6303,24 +6329,24 @@
     </row>
     <row r="60" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D60" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="E60" s="17" t="s">
         <v>427</v>
-      </c>
-      <c r="E60" s="17" t="s">
-        <v>425</v>
       </c>
       <c r="F60" s="15"/>
       <c r="G60" s="15"/>
       <c r="H60" s="17" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="I60" s="17"/>
       <c r="J60" s="17"/>
@@ -6339,31 +6365,31 @@
         <v>60</v>
       </c>
       <c r="S60" s="17" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="T60" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U60" s="17"/>
       <c r="V60" s="21" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="W60" s="17" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="15" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B61" s="16" t="s">
         <v>107</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E61" s="17" t="s">
         <v>107</v>
@@ -6375,7 +6401,7 @@
         <v>90</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="I61" s="17"/>
       <c r="J61" s="17"/>
@@ -6394,31 +6420,31 @@
         <v>60</v>
       </c>
       <c r="S61" s="17" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="T61" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U61" s="17"/>
       <c r="V61" s="21" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="W61" s="17" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="15" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B62" s="16" t="s">
         <v>89</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E62" s="17" t="s">
         <v>89</v>
@@ -6430,7 +6456,7 @@
         <v>81</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="I62" s="17"/>
       <c r="J62" s="17"/>
@@ -6449,31 +6475,31 @@
         <v>60</v>
       </c>
       <c r="S62" s="17" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="T62" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U62" s="17"/>
       <c r="V62" s="21" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="W62" s="17" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B63" s="16" t="s">
         <v>80</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E63" s="17" t="s">
         <v>80</v>
@@ -6485,7 +6511,7 @@
         <v>70</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="I63" s="17"/>
       <c r="J63" s="17"/>
@@ -6504,31 +6530,31 @@
         <v>60</v>
       </c>
       <c r="S63" s="17" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="T63" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U63" s="17"/>
       <c r="V63" s="21" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="W63" s="17" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B64" s="16" t="s">
         <v>69</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E64" s="17" t="s">
         <v>69</v>
@@ -6540,7 +6566,7 @@
         <v>71</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="I64" s="17"/>
       <c r="J64" s="17"/>
@@ -6559,31 +6585,31 @@
         <v>60</v>
       </c>
       <c r="S64" s="17" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="T64" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U64" s="17"/>
       <c r="V64" s="21" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="W64" s="17" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="15" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B65" s="16" t="s">
         <v>52</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E65" s="17" t="s">
         <v>52</v>
@@ -6595,7 +6621,7 @@
         <v>54</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="I65" s="17"/>
       <c r="J65" s="17"/>
@@ -6614,17 +6640,17 @@
         <v>60</v>
       </c>
       <c r="S65" s="17" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="T65" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U65" s="17"/>
       <c r="V65" s="21" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="W65" s="17" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -6680,28 +6706,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6714,7 +6740,7 @@
       </c>
       <c r="C2" s="29" t="n">
         <f aca="false">COUNTIF(Artifacts!$L$2:$L$124,"●")+COUNTIF(Artifacts!$L$2:$L$124,"○")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="29" t="n">
         <f aca="false">COUNTIFS(Artifacts!$L$2:$L$124,"●",Artifacts!$R$2:$R$124,"Yes")</f>
@@ -6731,7 +6757,7 @@
         <v>Add</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6761,7 +6787,7 @@
         <v>OK</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6791,7 +6817,7 @@
         <v>OK</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6821,7 +6847,7 @@
         <v>OK</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6851,7 +6877,7 @@
         <v>OK</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6881,7 +6907,7 @@
         <v>Trim</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6896,7 +6922,7 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">COUNTA(Artifacts!$C$2:$C$124)</f>
@@ -6911,7 +6937,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -6947,52 +6973,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="J1" s="27" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D2" s="17"/>
       <c r="E2" s="17" t="s">
         <v>108</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G2" s="17" t="n">
         <v>42.08</v>
@@ -7004,7 +7030,7 @@
         <v>60</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7012,10 +7038,10 @@
         <v>107</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>108</v>
@@ -7036,7 +7062,7 @@
         <v>60</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7044,10 +7070,10 @@
         <v>89</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D4" s="17" t="s">
         <v>90</v>
@@ -7056,7 +7082,7 @@
         <v>81</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G4" s="17" t="n">
         <v>41.88</v>
@@ -7068,18 +7094,18 @@
         <v>60</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>81</v>
@@ -7088,7 +7114,7 @@
         <v>70</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>45.46</v>
@@ -7100,7 +7126,7 @@
         <v>60</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7108,10 +7134,10 @@
         <v>69</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>70</v>
@@ -7120,7 +7146,7 @@
         <v>53</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="G6" s="17" t="n">
         <v>32.78</v>
@@ -7132,7 +7158,7 @@
         <v>60</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7140,10 +7166,10 @@
         <v>52</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>53</v>
@@ -7152,7 +7178,7 @@
         <v>54</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>30.27</v>
@@ -7164,7 +7190,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7172,15 +7198,15 @@
         <v>148</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="17" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>29.76</v>
@@ -7189,7 +7215,7 @@
         <v>-95.37</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J8" s="21"/>
     </row>
@@ -7198,15 +7224,15 @@
         <v>159</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="17" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>33.43</v>
@@ -7215,24 +7241,24 @@
         <v>-111.94</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="17" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G10" s="17" t="n">
         <v>32.76</v>
@@ -7247,13 +7273,13 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>90</v>
@@ -7262,7 +7288,7 @@
         <v>90</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>40.81</v>
@@ -7277,22 +7303,22 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G12" s="17" t="n">
         <v>39.57</v>
@@ -7307,22 +7333,22 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
+        <v>500</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>497</v>
+      </c>
+      <c r="D13" s="17" t="s">
         <v>498</v>
       </c>
-      <c r="B13" s="17" t="s">
-        <v>388</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>495</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>496</v>
-      </c>
       <c r="E13" s="17" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>38.72</v>
@@ -7337,13 +7363,13 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>53</v>
@@ -7352,7 +7378,7 @@
         <v>53</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
@@ -7360,18 +7386,18 @@
         <v>60</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>53</v>
@@ -7380,7 +7406,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="G15" s="17"/>
       <c r="H15" s="17"/>
@@ -7388,18 +7414,18 @@
         <v>60</v>
       </c>
       <c r="J15" s="21" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>53</v>
@@ -7408,7 +7434,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
@@ -7416,18 +7442,18 @@
         <v>60</v>
       </c>
       <c r="J16" s="21" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>71</v>
@@ -7436,7 +7462,7 @@
         <v>71</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>-22.97</v>
@@ -7448,27 +7474,27 @@
         <v>60</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
@@ -7476,27 +7502,27 @@
         <v>60</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>497</v>
+      </c>
+      <c r="D19" s="17" t="s">
         <v>510</v>
       </c>
-      <c r="B19" s="17" t="s">
-        <v>477</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>495</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>508</v>
-      </c>
       <c r="E19" s="17" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>26.71</v>
@@ -7505,28 +7531,28 @@
         <v>-80.04</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G20" s="17" t="n">
         <v>19.43</v>
@@ -7541,13 +7567,13 @@
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D21" s="17" t="s">
         <v>70</v>
@@ -7556,7 +7582,7 @@
         <v>70</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>41.89</v>
@@ -7568,27 +7594,27 @@
         <v>60</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
@@ -7599,12 +7625,12 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
@@ -7640,33 +7666,33 @@
         <v>24</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F1" s="27" t="s">
         <v>41</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D2" s="32" t="n">
         <v>2026</v>
@@ -7681,13 +7707,13 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="32" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D3" s="32" t="n">
         <v>2026</v>
@@ -7702,13 +7728,13 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>53</v>
@@ -7723,13 +7749,13 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>53</v>
@@ -7744,13 +7770,13 @@
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D6" s="32" t="s">
         <v>53</v>
@@ -7765,13 +7791,13 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>2024</v>
@@ -7786,13 +7812,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>2023</v>
@@ -7807,13 +7833,13 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>2023</v>
@@ -7828,13 +7854,13 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D10" s="32" t="n">
         <v>2022</v>
@@ -7849,13 +7875,13 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D11" s="32" t="n">
         <v>2021</v>
@@ -7870,13 +7896,13 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D12" s="32" t="n">
         <v>2022</v>
@@ -7891,7 +7917,7 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D13" s="28" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E13" s="28" t="n">
         <f aca="false">SUM(E2:E12)</f>
@@ -7900,7 +7926,7 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D14" s="28" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E14" s="28" t="n">
         <f aca="false">COUNTIF(F2:F12,"Yes")</f>
@@ -7909,12 +7935,12 @@
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
   </sheetData>
@@ -7944,19 +7970,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7964,13 +7990,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E2" s="33"/>
     </row>
@@ -7979,13 +8005,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="33" t="s">
+        <v>532</v>
+      </c>
+      <c r="C3" s="33" t="s">
         <v>530</v>
       </c>
-      <c r="C3" s="33" t="s">
-        <v>528</v>
-      </c>
       <c r="D3" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E3" s="33"/>
     </row>
@@ -7994,13 +8020,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E4" s="33"/>
     </row>
@@ -8009,13 +8035,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="33" t="s">
+        <v>533</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="D5" s="33" t="s">
         <v>531</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>532</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>529</v>
       </c>
       <c r="E5" s="33"/>
     </row>
@@ -8024,13 +8050,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E6" s="33"/>
     </row>
@@ -8039,16 +8065,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="C7" s="33" t="s">
         <v>534</v>
       </c>
-      <c r="C7" s="33" t="s">
-        <v>532</v>
-      </c>
       <c r="D7" s="33" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8056,16 +8082,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="33" t="s">
+        <v>539</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="D8" s="33" t="s">
         <v>537</v>
       </c>
-      <c r="C8" s="33" t="s">
-        <v>532</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>535</v>
-      </c>
       <c r="E8" s="33" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8073,16 +8099,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="33" t="s">
+        <v>540</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>537</v>
+      </c>
+      <c r="E9" s="33" t="s">
         <v>538</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>532</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>535</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8090,16 +8116,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8107,13 +8133,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E11" s="33"/>
     </row>
@@ -8122,13 +8148,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E12" s="33"/>
     </row>
@@ -8137,13 +8163,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E13" s="33"/>
     </row>
@@ -8152,13 +8178,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="33" t="s">
+        <v>546</v>
+      </c>
+      <c r="C14" s="33" t="s">
         <v>544</v>
       </c>
-      <c r="C14" s="33" t="s">
-        <v>542</v>
-      </c>
       <c r="D14" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E14" s="33"/>
     </row>
@@ -8167,13 +8193,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E15" s="33"/>
     </row>
@@ -8182,16 +8208,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8199,16 +8225,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8216,16 +8242,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8233,16 +8259,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="33" t="s">
+        <v>550</v>
+      </c>
+      <c r="C19" s="33" t="s">
         <v>548</v>
       </c>
-      <c r="C19" s="33" t="s">
-        <v>546</v>
-      </c>
       <c r="D19" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8250,16 +8276,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8267,13 +8293,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E21" s="33"/>
     </row>
@@ -8282,16 +8308,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8299,16 +8325,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8316,16 +8342,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8333,13 +8359,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="33" t="s">
+        <v>556</v>
+      </c>
+      <c r="C25" s="33" t="s">
         <v>554</v>
       </c>
-      <c r="C25" s="33" t="s">
-        <v>552</v>
-      </c>
       <c r="D25" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E25" s="33"/>
     </row>
@@ -8348,13 +8374,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E26" s="33"/>
     </row>
@@ -8363,13 +8389,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E27" s="33"/>
     </row>
@@ -8378,13 +8404,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E28" s="33"/>
     </row>
@@ -8393,13 +8419,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E29" s="33"/>
     </row>
@@ -8408,13 +8434,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E30" s="33"/>
     </row>
@@ -8423,13 +8449,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E31" s="33"/>
     </row>
@@ -8438,13 +8464,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E32" s="33"/>
     </row>
@@ -8453,13 +8479,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E33" s="33"/>
     </row>
@@ -8468,13 +8494,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E34" s="33"/>
     </row>
@@ -8483,19 +8509,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E35" s="33"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="28" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C37" s="28" t="n">
         <f aca="false">COUNTA(B2:B35)</f>
@@ -8504,7 +8530,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C38" s="1" t="n">
         <f aca="false">COUNTIF(D2:D35,"Shaded")</f>
@@ -8513,7 +8539,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C39" s="1" t="n">
         <f aca="false">COUNTIF(D2:D35,"Dot")</f>
@@ -8522,7 +8548,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
   </sheetData>
@@ -8553,16 +8579,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E1" s="27" t="s">
         <v>46</v>
@@ -8570,98 +8596,98 @@
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>60</v>
@@ -8672,13 +8698,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>60</v>
@@ -8689,130 +8715,130 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D13" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>60</v>
@@ -8823,13 +8849,13 @@
     </row>
     <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>60</v>
@@ -8840,13 +8866,13 @@
     </row>
     <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>60</v>
@@ -8857,13 +8883,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>60</v>
@@ -8874,140 +8900,140 @@
     </row>
     <row r="20" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D22" s="21"/>
       <c r="E22" s="17" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="17" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D24" s="21"/>
       <c r="E24" s="17" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D25" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D28" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D29" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
   </sheetData>
@@ -9026,7 +9052,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
@@ -9037,16 +9063,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9054,10 +9080,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>60</v>
@@ -9068,13 +9094,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9082,13 +9108,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9096,13 +9122,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9110,13 +9136,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9124,13 +9150,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9138,13 +9164,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9152,13 +9178,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9166,13 +9192,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9180,13 +9206,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9194,13 +9220,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9208,13 +9234,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9222,13 +9248,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9236,13 +9262,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9250,13 +9276,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9264,13 +9290,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9278,13 +9304,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9292,13 +9318,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9306,13 +9332,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9320,13 +9346,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9334,13 +9360,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9348,10 +9374,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="D23" s="21"/>
     </row>
@@ -9360,7 +9386,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>35</v>
@@ -9372,13 +9398,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9386,12 +9412,48 @@
         <v>25</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D26" s="21"/>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>702</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>703</v>
+      </c>
+      <c r="D27" s="21"/>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>704</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>705</v>
+      </c>
+      <c r="D28" s="21"/>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>706</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>707</v>
+      </c>
+      <c r="D29" s="21"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="719">
   <si>
     <t xml:space="preserve">Site artifacts: mapping workbook</t>
   </si>
@@ -469,10 +469,10 @@
     <t xml:space="preserve">Miniature diorama of the building</t>
   </si>
   <si>
-    <t xml:space="preserve">Yes (generic massing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enovis logo (in repo); 3D model of the MPOC (generic massing, six zones) + tile still + About hover turntable, in Lens v2</t>
+    <t xml:space="preserve">Yes (generic massing, real proportions)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enovis logo (in repo); MPOC model (block massing at real proportions, six zones + mezzanine, from the updated plan; no rooms) + tile still + About hover turntable, in Lens v2. MPOC, CPS and the AM lab are one plant.</t>
   </si>
   <si>
     <t xml:space="preserve">Public-safe photos or layouts? NDA limits?</t>
@@ -496,7 +496,7 @@
     <t xml:space="preserve">Printer / lattice part</t>
   </si>
   <si>
-    <t xml:space="preserve">Yes (shares the MPOC model)</t>
+    <t xml:space="preserve">Yes (shares the MPOC model, lab lit)</t>
   </si>
   <si>
     <t xml:space="preserve">Shares the MPOC 3D model, opening with the additive &amp; subtractive manufacturing lab highlighted</t>
@@ -529,10 +529,10 @@
     <t xml:space="preserve">Silo tower (strong hero)</t>
   </si>
   <si>
-    <t xml:space="preserve">Yes (Grant's exterior model, v11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.4: elevation, P&amp;ID, 3D render, tower photo, interior photo. Exterior 3D model (GLB) live in Lens v2 (zones: silo &amp; mixing tower, packaging &amp; warehouse, offices, truck court &amp; site) + tile still + About hover turntable</t>
+    <t xml:space="preserve">Yes (Grant's exterior model of MAPEI Houston, v12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio p.4: elevation, P&amp;ID, 3D render, tower photo, interior photo. MAPEI Houston exterior model (GLB v12) live in Lens v2 (zones: silo &amp; mixing tower, production &amp; warehouse, offices, site), opens with the tower lit; tile still + About hover turntable</t>
   </si>
   <si>
     <t xml:space="preserve">Dates: placeholder for now (About shows it at ~March 2022).</t>
@@ -577,7 +577,7 @@
     <t xml:space="preserve">Site development: 315K sq ft brownfield</t>
   </si>
   <si>
-    <t xml:space="preserve">Houston, TX (from Dallas)</t>
+    <t xml:space="preserve">Houston, TX (from Dallas); same facility as E3 and E7</t>
   </si>
   <si>
     <t xml:space="preserve">Turned a speculative brownfield building into a full production and distribution facility.</t>
@@ -592,10 +592,10 @@
     <t xml:space="preserve">Building / diorama</t>
   </si>
   <si>
-    <t xml:space="preserve">Generate (simple diorama)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.5: building photo</t>
+    <t xml:space="preserve">Yes (shares the MAPEI Houston model)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPEI Houston model; tile still from higher up, with the site</t>
   </si>
   <si>
     <t xml:space="preserve">Lived in Dallas, travelled to Houston for this project. Dates: placeholder.</t>
@@ -634,7 +634,7 @@
     <t xml:space="preserve">Liquid admixtures plant expansion ($5M)</t>
   </si>
   <si>
-    <t xml:space="preserve">TX (verify)</t>
+    <t xml:space="preserve">Houston, TX (in the MAPEI Houston facility, with E3)</t>
   </si>
   <si>
     <t xml:space="preserve">Plant expansion introducing automated blending and bulk transfer systems to the Southern U.S.</t>
@@ -649,69 +649,75 @@
     <t xml:space="preserve">Process skid</t>
   </si>
   <si>
+    <t xml:space="preserve">Yes (shares the MAPEI Houston model, plant building lit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPEI Houston model; tile still with the plant building lit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dates: placeholder for now. Where inside the building is the admixtures plant?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Startup: OnlyChargeEV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnlyChargeEV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallas, TX (Austin, Houston, San Antonio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial EV charging service company across major Texas hubs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partners: ChargePoint, Ford Pro, Xeal Energy, Verdek. Commercial, fleet and multifamily clients. Automated payments, accounting, compliance, estimating and proposals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRM automation, email campaigns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charger pedestal + Texas map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate (charger)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio pp.2–3; OnlyChargeEV logo (in repo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logo coming; use a lightning-bolt placeholder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FedEx Office HQ workplace charging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV install</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modernized workplace charging for FedEx Office HQ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 Enel X JuiceBox Pro 40 L2 chargers on dual stands (4 replaced + 4 added = 8 ports); trenching, concrete, electrical; permits.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Maybe</t>
   </si>
   <si>
-    <t xml:space="preserve">You have photos (to send)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Startup: OnlyChargeEV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnlyChargeEV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Founder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallas, TX (Austin, Houston, San Antonio)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial EV charging service company across major Texas hubs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partners: ChargePoint, Ford Pro, Xeal Energy, Verdek. Commercial, fleet and multifamily clients. Automated payments, accounting, compliance, estimating and proposals.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRM automation, email campaigns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charger pedestal + Texas map</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate (charger)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio pp.2–3; OnlyChargeEV logo (in repo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logo coming; use a lightning-bolt placeholder.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S1a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FedEx Office HQ workplace charging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EV install</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modernized workplace charging for FedEx Office HQ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 Enel X JuiceBox Pro 40 L2 chargers on dual stands (4 replaced + 4 added = 8 ports); trenching, concrete, electrical; permits.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Case inside S1</t>
   </si>
   <si>
@@ -1540,7 +1546,7 @@
     <t xml:space="preserve">Work site</t>
   </si>
   <si>
-    <t xml:space="preserve">Dry mix plant (E3), site development (E5), Stallion EV (S1b)</t>
+    <t xml:space="preserve">MAPEI Houston, one facility: dry mix plant (E3), liquid admixtures plant (E7), site development (E5); Stallion EV (S1b)</t>
   </si>
   <si>
     <t xml:space="preserve">Robotic palletizer (E4)</t>
@@ -2182,16 +2188,43 @@
     <t xml:space="preserve">E7, 3D models</t>
   </si>
   <si>
+    <t xml:space="preserve">Same facility as the dry mix plant: the MAPEI Houston model (v12) is used for it, with the plant building lit.</t>
+  </si>
+  <si>
     <t xml:space="preserve">The dry mix plant now sits in About (2022 ring, March placeholder) so its 3D tile can turn on hover. Keep it there, and which month did it start?</t>
   </si>
   <si>
     <t xml:space="preserve">E3, About</t>
   </si>
   <si>
-    <t xml:space="preserve">Dry mix plant zone names: "Silo &amp; mixing tower", "Packaging &amp; warehouse", "Offices", "Truck court &amp; site". Rename any?</t>
+    <t xml:space="preserve">MAPEI Houston zone names (v12): "Silo &amp; mixing tower", "Production &amp; warehouse" (packaging and the admixtures plant inside), "Offices", "Site". Rename any?</t>
   </si>
   <si>
     <t xml:space="preserve">E3, 3D model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPOC: your Pascal handoff traces the real floor plan (rooms, names, drawing references). The public repo only uses its proportions and block layout. Do you want the detailed layout shown on the site (it would be public)?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E1, E2, 3D model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPOC: where is the additive &amp; subtractive manufacturing lab? It is placed at the east end, behind the offices, as a guess.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2, 3D model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPEI Houston: where inside the building is the liquid admixtures plant (and any outdoor tanks)? It could get its own zone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E7, 3D model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean pack &amp; sterilization: should it be its own project tile (it would open the MPOC model with that zone lit), or stay part of the facility build-out?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E1, 3D model</t>
   </si>
 </sst>
 </file>
@@ -4112,7 +4145,7 @@
         <v>194</v>
       </c>
       <c r="V18" s="21" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="W18" s="17" t="s">
         <v>65</v>
@@ -4120,7 +4153,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -4147,34 +4180,34 @@
     </row>
     <row r="20" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G20" s="15" t="s">
         <v>71</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K20" s="17"/>
       <c r="L20" s="18" t="s">
@@ -4197,16 +4230,16 @@
         <v>60</v>
       </c>
       <c r="S20" s="17" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="V20" s="21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="W20" s="17" t="s">
         <v>65</v>
@@ -4214,16 +4247,16 @@
     </row>
     <row r="21" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>69</v>
@@ -4231,10 +4264,10 @@
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
       <c r="H21" s="17" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
@@ -4249,16 +4282,16 @@
       <c r="P21" s="20"/>
       <c r="Q21" s="20"/>
       <c r="R21" s="20" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="S21" s="17" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="T21" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U21" s="17" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="V21" s="21"/>
       <c r="W21" s="17" t="s">
@@ -4267,16 +4300,16 @@
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>148</v>
@@ -4284,10 +4317,10 @@
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
       <c r="H22" s="17" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="J22" s="17"/>
       <c r="K22" s="17"/>
@@ -4302,16 +4335,16 @@
       <c r="P22" s="20"/>
       <c r="Q22" s="20"/>
       <c r="R22" s="20" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="S22" s="17" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="T22" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U22" s="17" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="V22" s="21"/>
       <c r="W22" s="17" t="s">
@@ -4320,27 +4353,27 @@
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
       <c r="H23" s="17" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
@@ -4355,16 +4388,16 @@
       <c r="P23" s="20"/>
       <c r="Q23" s="20"/>
       <c r="R23" s="20" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="S23" s="17" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="T23" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U23" s="17" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="V23" s="21"/>
       <c r="W23" s="17" t="s">
@@ -4373,16 +4406,16 @@
     </row>
     <row r="24" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>69</v>
@@ -4390,10 +4423,10 @@
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
       <c r="H24" s="17" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J24" s="17"/>
       <c r="K24" s="17"/>
@@ -4408,16 +4441,16 @@
       <c r="P24" s="20"/>
       <c r="Q24" s="20"/>
       <c r="R24" s="20" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="S24" s="17" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="T24" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U24" s="17" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="V24" s="21"/>
       <c r="W24" s="17" t="s">
@@ -4426,7 +4459,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -4453,13 +4486,13 @@
     </row>
     <row r="26" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>106</v>
@@ -4468,19 +4501,19 @@
         <v>107</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G26" s="15" t="s">
         <v>90</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K26" s="17"/>
       <c r="L26" s="18" t="s">
@@ -4499,16 +4532,16 @@
         <v>60</v>
       </c>
       <c r="S26" s="17" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="T26" s="17" t="s">
         <v>184</v>
       </c>
       <c r="U26" s="17" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="V26" s="21" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="W26" s="17" t="s">
         <v>156</v>
@@ -4516,16 +4549,16 @@
     </row>
     <row r="27" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>107</v>
@@ -4534,16 +4567,16 @@
         <v>97</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K27" s="17"/>
       <c r="L27" s="18" t="s">
@@ -4562,16 +4595,16 @@
         <v>60</v>
       </c>
       <c r="S27" s="17" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="T27" s="17" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="U27" s="17" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="V27" s="21" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="W27" s="17" t="s">
         <v>156</v>
@@ -4579,7 +4612,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -4606,28 +4639,28 @@
     </row>
     <row r="29" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="17" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K29" s="17"/>
       <c r="L29" s="20"/>
@@ -4644,45 +4677,45 @@
         <v>60</v>
       </c>
       <c r="S29" s="17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="T29" s="17" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="U29" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="V29" s="21" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="W29" s="17" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="17" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K30" s="17"/>
       <c r="L30" s="20"/>
@@ -4699,45 +4732,45 @@
         <v>60</v>
       </c>
       <c r="S30" s="17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="T30" s="17" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="U30" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="V30" s="21" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="W30" s="17" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
       <c r="H31" s="17" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K31" s="17"/>
       <c r="L31" s="20"/>
@@ -4758,24 +4791,24 @@
         <v>60</v>
       </c>
       <c r="S31" s="17" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="T31" s="17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="U31" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="V31" s="21" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="W31" s="17" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -4802,35 +4835,35 @@
     </row>
     <row r="33" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E33" s="17"/>
       <c r="F33" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K33" s="26" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L33" s="20"/>
       <c r="M33" s="20"/>
@@ -4844,52 +4877,52 @@
         <v>60</v>
       </c>
       <c r="S33" s="17" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="T33" s="17" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="U33" s="17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="V33" s="21" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="W33" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E34" s="17"/>
       <c r="F34" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K34" s="26" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L34" s="20"/>
       <c r="M34" s="19" t="s">
@@ -4905,52 +4938,52 @@
         <v>60</v>
       </c>
       <c r="S34" s="17" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="T34" s="17" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="U34" s="17" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="V34" s="21" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="W34" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E35" s="17"/>
       <c r="F35" s="15" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K35" s="26" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L35" s="20"/>
       <c r="M35" s="19" t="s">
@@ -4968,52 +5001,52 @@
         <v>60</v>
       </c>
       <c r="S35" s="17" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="T35" s="17" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="U35" s="17" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="V35" s="21" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="W35" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E36" s="17"/>
       <c r="F36" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K36" s="26" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L36" s="18" t="s">
         <v>59</v>
@@ -5031,52 +5064,52 @@
         <v>62</v>
       </c>
       <c r="S36" s="17" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="T36" s="17" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="U36" s="17" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="V36" s="21" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="W36" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E37" s="17"/>
       <c r="F37" s="15" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K37" s="26" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L37" s="20"/>
       <c r="M37" s="20"/>
@@ -5092,52 +5125,52 @@
         <v>60</v>
       </c>
       <c r="S37" s="17" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="T37" s="17" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="U37" s="17" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="V37" s="21" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="W37" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E38" s="17"/>
       <c r="F38" s="15" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I38" s="17" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K38" s="26" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L38" s="20"/>
       <c r="M38" s="20"/>
@@ -5151,49 +5184,49 @@
         <v>62</v>
       </c>
       <c r="S38" s="17" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="T38" s="17" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="U38" s="17" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="V38" s="21" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="W38" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E39" s="17"/>
       <c r="F39" s="15" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="20"/>
@@ -5208,49 +5241,49 @@
         <v>62</v>
       </c>
       <c r="S39" s="17" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="T39" s="17" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="U39" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="V39" s="21" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="W39" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E40" s="17"/>
       <c r="F40" s="15" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K40" s="17"/>
       <c r="L40" s="20"/>
@@ -5267,49 +5300,49 @@
         <v>62</v>
       </c>
       <c r="S40" s="17" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="T40" s="17" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="U40" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="V40" s="21" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="W40" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E41" s="17"/>
       <c r="F41" s="15" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K41" s="17"/>
       <c r="L41" s="20"/>
@@ -5324,49 +5357,49 @@
         <v>62</v>
       </c>
       <c r="S41" s="17" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="T41" s="17" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="U41" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="V41" s="21" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="W41" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E42" s="17"/>
       <c r="F42" s="15" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="K42" s="17"/>
       <c r="L42" s="20"/>
@@ -5383,52 +5416,52 @@
         <v>62</v>
       </c>
       <c r="S42" s="17" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="T42" s="17" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="U42" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="V42" s="21" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="W42" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="15" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K43" s="26" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L43" s="20"/>
       <c r="M43" s="19" t="s">
@@ -5444,52 +5477,52 @@
         <v>60</v>
       </c>
       <c r="S43" s="17" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="T43" s="17" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="U43" s="17" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="V43" s="21" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="W43" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E44" s="17"/>
       <c r="F44" s="15" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J44" s="17" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K44" s="26" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L44" s="20"/>
       <c r="M44" s="20"/>
@@ -5503,49 +5536,49 @@
         <v>62</v>
       </c>
       <c r="S44" s="17" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="T44" s="17" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="U44" s="17" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="V44" s="21" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="W44" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="15" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="I45" s="17" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="K45" s="17"/>
       <c r="L45" s="20"/>
@@ -5562,39 +5595,39 @@
         <v>60</v>
       </c>
       <c r="S45" s="17" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="T45" s="17" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="U45" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="V45" s="21" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="W45" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E46" s="17"/>
       <c r="F46" s="15"/>
       <c r="G46" s="15"/>
       <c r="H46" s="17" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="I46" s="17"/>
       <c r="J46" s="17"/>
@@ -5611,24 +5644,24 @@
         <v>60</v>
       </c>
       <c r="S46" s="17" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="T46" s="17" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="U46" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="V46" s="21" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="W46" s="17" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -5655,19 +5688,19 @@
     </row>
     <row r="48" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F48" s="15" t="n">
         <v>2026</v>
@@ -5676,11 +5709,11 @@
         <v>2026</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I48" s="17"/>
       <c r="J48" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K48" s="17"/>
       <c r="L48" s="20"/>
@@ -5697,36 +5730,36 @@
         <v>60</v>
       </c>
       <c r="S48" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="T48" s="17" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="U48" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="V48" s="21" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="W48" s="17" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F49" s="15" t="n">
         <v>2026</v>
@@ -5735,11 +5768,11 @@
         <v>2026</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="I49" s="17"/>
       <c r="J49" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K49" s="17"/>
       <c r="L49" s="20"/>
@@ -5756,36 +5789,36 @@
         <v>60</v>
       </c>
       <c r="S49" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="T49" s="17" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="U49" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="V49" s="21" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="W49" s="17" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F50" s="15" t="s">
         <v>53</v>
@@ -5794,11 +5827,11 @@
         <v>53</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="I50" s="17"/>
       <c r="J50" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K50" s="17"/>
       <c r="L50" s="20"/>
@@ -5815,36 +5848,36 @@
         <v>60</v>
       </c>
       <c r="S50" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="T50" s="17" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="U50" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="V50" s="21" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="W50" s="17" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F51" s="15" t="s">
         <v>53</v>
@@ -5853,11 +5886,11 @@
         <v>53</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="I51" s="17"/>
       <c r="J51" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="20"/>
@@ -5874,36 +5907,36 @@
         <v>60</v>
       </c>
       <c r="S51" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="T51" s="17" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="U51" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="V51" s="21" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="W51" s="17" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F52" s="15" t="s">
         <v>53</v>
@@ -5912,11 +5945,11 @@
         <v>53</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I52" s="17"/>
       <c r="J52" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K52" s="17"/>
       <c r="L52" s="18"/>
@@ -5933,36 +5966,36 @@
         <v>60</v>
       </c>
       <c r="S52" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="T52" s="17" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="U52" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="V52" s="21" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="W52" s="17" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F53" s="15" t="n">
         <v>2024</v>
@@ -5971,11 +6004,11 @@
         <v>2024</v>
       </c>
       <c r="H53" s="17" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I53" s="17"/>
       <c r="J53" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K53" s="17"/>
       <c r="L53" s="20"/>
@@ -5992,36 +6025,36 @@
         <v>60</v>
       </c>
       <c r="S53" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="T53" s="17" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="U53" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="V53" s="21" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="W53" s="17" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F54" s="15" t="n">
         <v>2023</v>
@@ -6030,11 +6063,11 @@
         <v>2023</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="I54" s="17"/>
       <c r="J54" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K54" s="17"/>
       <c r="L54" s="20"/>
@@ -6051,36 +6084,36 @@
         <v>60</v>
       </c>
       <c r="S54" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="T54" s="17" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="U54" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="V54" s="21" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="W54" s="17" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F55" s="15" t="n">
         <v>2023</v>
@@ -6089,11 +6122,11 @@
         <v>2023</v>
       </c>
       <c r="H55" s="17" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I55" s="17"/>
       <c r="J55" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K55" s="17"/>
       <c r="L55" s="20"/>
@@ -6110,36 +6143,36 @@
         <v>60</v>
       </c>
       <c r="S55" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="T55" s="17" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="U55" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="V55" s="21" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="W55" s="17" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F56" s="15" t="n">
         <v>2022</v>
@@ -6148,11 +6181,11 @@
         <v>2022</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="I56" s="17"/>
       <c r="J56" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K56" s="17"/>
       <c r="L56" s="20"/>
@@ -6169,36 +6202,36 @@
         <v>60</v>
       </c>
       <c r="S56" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="T56" s="17" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="U56" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="V56" s="21" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="W56" s="17" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="15" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F57" s="15" t="n">
         <v>2021</v>
@@ -6207,11 +6240,11 @@
         <v>2021</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="I57" s="17"/>
       <c r="J57" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K57" s="17"/>
       <c r="L57" s="20"/>
@@ -6228,36 +6261,36 @@
         <v>60</v>
       </c>
       <c r="S57" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="T57" s="17" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="U57" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="V57" s="21" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="W57" s="17" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="15" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F58" s="15" t="n">
         <v>2022</v>
@@ -6266,11 +6299,11 @@
         <v>2022</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="I58" s="17"/>
       <c r="J58" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K58" s="17"/>
       <c r="L58" s="20"/>
@@ -6287,22 +6320,22 @@
         <v>60</v>
       </c>
       <c r="S58" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="T58" s="17" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="U58" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="V58" s="21"/>
       <c r="W58" s="17" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -6329,24 +6362,24 @@
     </row>
     <row r="60" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D60" s="17" t="s">
+        <v>431</v>
+      </c>
+      <c r="E60" s="17" t="s">
         <v>429</v>
-      </c>
-      <c r="E60" s="17" t="s">
-        <v>427</v>
       </c>
       <c r="F60" s="15"/>
       <c r="G60" s="15"/>
       <c r="H60" s="17" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I60" s="17"/>
       <c r="J60" s="17"/>
@@ -6365,31 +6398,31 @@
         <v>60</v>
       </c>
       <c r="S60" s="17" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="T60" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U60" s="17"/>
       <c r="V60" s="21" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="W60" s="17" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="15" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B61" s="16" t="s">
         <v>107</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E61" s="17" t="s">
         <v>107</v>
@@ -6401,7 +6434,7 @@
         <v>90</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="I61" s="17"/>
       <c r="J61" s="17"/>
@@ -6420,31 +6453,31 @@
         <v>60</v>
       </c>
       <c r="S61" s="17" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="T61" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U61" s="17"/>
       <c r="V61" s="21" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="W61" s="17" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="15" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B62" s="16" t="s">
         <v>89</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E62" s="17" t="s">
         <v>89</v>
@@ -6456,7 +6489,7 @@
         <v>81</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="I62" s="17"/>
       <c r="J62" s="17"/>
@@ -6475,31 +6508,31 @@
         <v>60</v>
       </c>
       <c r="S62" s="17" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="T62" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U62" s="17"/>
       <c r="V62" s="21" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="W62" s="17" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B63" s="16" t="s">
         <v>80</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E63" s="17" t="s">
         <v>80</v>
@@ -6511,7 +6544,7 @@
         <v>70</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="I63" s="17"/>
       <c r="J63" s="17"/>
@@ -6530,31 +6563,31 @@
         <v>60</v>
       </c>
       <c r="S63" s="17" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="T63" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U63" s="17"/>
       <c r="V63" s="21" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="W63" s="17" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B64" s="16" t="s">
         <v>69</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E64" s="17" t="s">
         <v>69</v>
@@ -6566,7 +6599,7 @@
         <v>71</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="I64" s="17"/>
       <c r="J64" s="17"/>
@@ -6585,31 +6618,31 @@
         <v>60</v>
       </c>
       <c r="S64" s="17" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="T64" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U64" s="17"/>
       <c r="V64" s="21" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="W64" s="17" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="15" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B65" s="16" t="s">
         <v>52</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E65" s="17" t="s">
         <v>52</v>
@@ -6621,7 +6654,7 @@
         <v>54</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="I65" s="17"/>
       <c r="J65" s="17"/>
@@ -6640,17 +6673,17 @@
         <v>60</v>
       </c>
       <c r="S65" s="17" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="T65" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U65" s="17"/>
       <c r="V65" s="21" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="W65" s="17" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -6706,28 +6739,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6757,7 +6790,7 @@
         <v>Add</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6787,7 +6820,7 @@
         <v>OK</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6817,7 +6850,7 @@
         <v>OK</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6847,7 +6880,7 @@
         <v>OK</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6877,7 +6910,7 @@
         <v>OK</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6907,7 +6940,7 @@
         <v>Trim</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6922,7 +6955,7 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">COUNTA(Artifacts!$C$2:$C$124)</f>
@@ -6937,7 +6970,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -6973,52 +7006,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="J1" s="27" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D2" s="17"/>
       <c r="E2" s="17" t="s">
         <v>108</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="G2" s="17" t="n">
         <v>42.08</v>
@@ -7030,7 +7063,7 @@
         <v>60</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7038,10 +7071,10 @@
         <v>107</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>108</v>
@@ -7062,7 +7095,7 @@
         <v>60</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7070,10 +7103,10 @@
         <v>89</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D4" s="17" t="s">
         <v>90</v>
@@ -7082,7 +7115,7 @@
         <v>81</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="G4" s="17" t="n">
         <v>41.88</v>
@@ -7094,18 +7127,18 @@
         <v>60</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>81</v>
@@ -7114,7 +7147,7 @@
         <v>70</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>45.46</v>
@@ -7126,7 +7159,7 @@
         <v>60</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7134,10 +7167,10 @@
         <v>69</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>70</v>
@@ -7146,7 +7179,7 @@
         <v>53</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G6" s="17" t="n">
         <v>32.78</v>
@@ -7158,7 +7191,7 @@
         <v>60</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7166,10 +7199,10 @@
         <v>52</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>53</v>
@@ -7178,7 +7211,7 @@
         <v>54</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>30.27</v>
@@ -7190,7 +7223,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7198,15 +7231,15 @@
         <v>148</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="17" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>29.76</v>
@@ -7215,7 +7248,7 @@
         <v>-95.37</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="J8" s="21"/>
     </row>
@@ -7224,15 +7257,15 @@
         <v>159</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="17" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>33.43</v>
@@ -7241,24 +7274,24 @@
         <v>-111.94</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="J9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="17" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G10" s="17" t="n">
         <v>32.76</v>
@@ -7273,13 +7306,13 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>90</v>
@@ -7288,7 +7321,7 @@
         <v>90</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>40.81</v>
@@ -7303,22 +7336,22 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G12" s="17" t="n">
         <v>39.57</v>
@@ -7333,22 +7366,22 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
+        <v>502</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="D13" s="17" t="s">
         <v>500</v>
       </c>
-      <c r="B13" s="17" t="s">
-        <v>390</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>497</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>498</v>
-      </c>
       <c r="E13" s="17" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>38.72</v>
@@ -7363,13 +7396,13 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>53</v>
@@ -7378,7 +7411,7 @@
         <v>53</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
@@ -7386,18 +7419,18 @@
         <v>60</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>53</v>
@@ -7406,7 +7439,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G15" s="17"/>
       <c r="H15" s="17"/>
@@ -7414,18 +7447,18 @@
         <v>60</v>
       </c>
       <c r="J15" s="21" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>53</v>
@@ -7434,7 +7467,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
@@ -7442,18 +7475,18 @@
         <v>60</v>
       </c>
       <c r="J16" s="21" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>71</v>
@@ -7462,7 +7495,7 @@
         <v>71</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>-22.97</v>
@@ -7474,27 +7507,27 @@
         <v>60</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
@@ -7502,27 +7535,27 @@
         <v>60</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
+        <v>514</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>481</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="D19" s="17" t="s">
         <v>512</v>
       </c>
-      <c r="B19" s="17" t="s">
-        <v>479</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>497</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>510</v>
-      </c>
       <c r="E19" s="17" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>26.71</v>
@@ -7531,28 +7564,28 @@
         <v>-80.04</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="J19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G20" s="17" t="n">
         <v>19.43</v>
@@ -7567,13 +7600,13 @@
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D21" s="17" t="s">
         <v>70</v>
@@ -7582,7 +7615,7 @@
         <v>70</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>41.89</v>
@@ -7594,27 +7627,27 @@
         <v>60</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
@@ -7625,12 +7658,12 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
@@ -7666,33 +7699,33 @@
         <v>24</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F1" s="27" t="s">
         <v>41</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D2" s="32" t="n">
         <v>2026</v>
@@ -7707,13 +7740,13 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="32" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D3" s="32" t="n">
         <v>2026</v>
@@ -7728,13 +7761,13 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>53</v>
@@ -7749,13 +7782,13 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>53</v>
@@ -7770,13 +7803,13 @@
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D6" s="32" t="s">
         <v>53</v>
@@ -7791,13 +7824,13 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>2024</v>
@@ -7812,13 +7845,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>2023</v>
@@ -7833,13 +7866,13 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>2023</v>
@@ -7854,13 +7887,13 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D10" s="32" t="n">
         <v>2022</v>
@@ -7875,13 +7908,13 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D11" s="32" t="n">
         <v>2021</v>
@@ -7896,13 +7929,13 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D12" s="32" t="n">
         <v>2022</v>
@@ -7917,7 +7950,7 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D13" s="28" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E13" s="28" t="n">
         <f aca="false">SUM(E2:E12)</f>
@@ -7926,7 +7959,7 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D14" s="28" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E14" s="28" t="n">
         <f aca="false">COUNTIF(F2:F12,"Yes")</f>
@@ -7935,12 +7968,12 @@
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>
@@ -7970,19 +8003,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7990,13 +8023,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E2" s="33"/>
     </row>
@@ -8005,13 +8038,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="C3" s="33" t="s">
         <v>532</v>
       </c>
-      <c r="C3" s="33" t="s">
-        <v>530</v>
-      </c>
       <c r="D3" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E3" s="33"/>
     </row>
@@ -8020,13 +8053,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E4" s="33"/>
     </row>
@@ -8035,13 +8068,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="33" t="s">
+        <v>535</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="D5" s="33" t="s">
         <v>533</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>534</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>531</v>
       </c>
       <c r="E5" s="33"/>
     </row>
@@ -8050,13 +8083,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E6" s="33"/>
     </row>
@@ -8065,16 +8098,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="33" t="s">
+        <v>538</v>
+      </c>
+      <c r="C7" s="33" t="s">
         <v>536</v>
       </c>
-      <c r="C7" s="33" t="s">
-        <v>534</v>
-      </c>
       <c r="D7" s="33" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8082,16 +8115,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="33" t="s">
+        <v>541</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="D8" s="33" t="s">
         <v>539</v>
       </c>
-      <c r="C8" s="33" t="s">
-        <v>534</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>537</v>
-      </c>
       <c r="E8" s="33" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8099,16 +8132,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="33" t="s">
+        <v>542</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>539</v>
+      </c>
+      <c r="E9" s="33" t="s">
         <v>540</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>534</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>537</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8116,16 +8149,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8133,13 +8166,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E11" s="33"/>
     </row>
@@ -8148,13 +8181,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E12" s="33"/>
     </row>
@@ -8163,13 +8196,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E13" s="33"/>
     </row>
@@ -8178,13 +8211,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="33" t="s">
+        <v>548</v>
+      </c>
+      <c r="C14" s="33" t="s">
         <v>546</v>
       </c>
-      <c r="C14" s="33" t="s">
-        <v>544</v>
-      </c>
       <c r="D14" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E14" s="33"/>
     </row>
@@ -8193,13 +8226,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E15" s="33"/>
     </row>
@@ -8208,16 +8241,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8225,16 +8258,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8242,16 +8275,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8259,16 +8292,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="33" t="s">
+        <v>552</v>
+      </c>
+      <c r="C19" s="33" t="s">
         <v>550</v>
       </c>
-      <c r="C19" s="33" t="s">
-        <v>548</v>
-      </c>
       <c r="D19" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8276,16 +8309,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8293,13 +8326,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E21" s="33"/>
     </row>
@@ -8308,16 +8341,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8325,16 +8358,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8342,16 +8375,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8359,13 +8392,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="33" t="s">
+        <v>558</v>
+      </c>
+      <c r="C25" s="33" t="s">
         <v>556</v>
       </c>
-      <c r="C25" s="33" t="s">
-        <v>554</v>
-      </c>
       <c r="D25" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E25" s="33"/>
     </row>
@@ -8374,13 +8407,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E26" s="33"/>
     </row>
@@ -8389,13 +8422,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E27" s="33"/>
     </row>
@@ -8404,13 +8437,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E28" s="33"/>
     </row>
@@ -8419,13 +8452,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E29" s="33"/>
     </row>
@@ -8434,13 +8467,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E30" s="33"/>
     </row>
@@ -8449,13 +8482,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E31" s="33"/>
     </row>
@@ -8464,13 +8497,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E32" s="33"/>
     </row>
@@ -8479,13 +8512,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E33" s="33"/>
     </row>
@@ -8494,13 +8527,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E34" s="33"/>
     </row>
@@ -8509,19 +8542,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E35" s="33"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="28" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C37" s="28" t="n">
         <f aca="false">COUNTA(B2:B35)</f>
@@ -8530,7 +8563,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C38" s="1" t="n">
         <f aca="false">COUNTIF(D2:D35,"Shaded")</f>
@@ -8539,7 +8572,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C39" s="1" t="n">
         <f aca="false">COUNTIF(D2:D35,"Dot")</f>
@@ -8548,7 +8581,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
   </sheetData>
@@ -8579,16 +8612,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E1" s="27" t="s">
         <v>46</v>
@@ -8596,98 +8629,98 @@
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>60</v>
@@ -8698,13 +8731,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>60</v>
@@ -8715,130 +8748,130 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D13" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>60</v>
@@ -8849,13 +8882,13 @@
     </row>
     <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>60</v>
@@ -8866,13 +8899,13 @@
     </row>
     <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>60</v>
@@ -8883,13 +8916,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>60</v>
@@ -8900,140 +8933,140 @@
     </row>
     <row r="20" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D22" s="21"/>
       <c r="E22" s="17" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="17" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D24" s="21"/>
       <c r="E24" s="17" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D25" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D28" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D29" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
   </sheetData>
@@ -9052,7 +9085,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
@@ -9063,16 +9096,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9080,10 +9113,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>60</v>
@@ -9094,13 +9127,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9108,13 +9141,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9122,13 +9155,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9136,13 +9169,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9150,13 +9183,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9164,13 +9197,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9178,13 +9211,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>186</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9192,13 +9225,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9206,13 +9239,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9220,13 +9253,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9234,13 +9267,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9248,13 +9281,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9262,13 +9295,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9276,13 +9309,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9290,13 +9323,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9304,13 +9337,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9318,13 +9351,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9332,13 +9365,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9346,13 +9379,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9360,13 +9393,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9374,10 +9407,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="D23" s="21"/>
     </row>
@@ -9386,7 +9419,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>35</v>
@@ -9398,13 +9431,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9412,10 +9445,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D26" s="21"/>
     </row>
@@ -9424,22 +9457,24 @@
         <v>26</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>703</v>
-      </c>
-      <c r="D27" s="21"/>
+        <v>705</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>706</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="D28" s="21"/>
     </row>
@@ -9448,12 +9483,60 @@
         <v>28</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D29" s="21"/>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>711</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>712</v>
+      </c>
+      <c r="D30" s="21"/>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>713</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>714</v>
+      </c>
+      <c r="D31" s="21"/>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>715</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>716</v>
+      </c>
+      <c r="D32" s="21"/>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>717</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>718</v>
+      </c>
+      <c r="D33" s="21"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="724">
   <si>
     <t xml:space="preserve">Site artifacts: mapping workbook</t>
   </si>
@@ -823,13 +823,16 @@
     <t xml:space="preserve">SolidWorks, 3D printing, CNC</t>
   </si>
   <si>
+    <t xml:space="preserve">Video: youtube.com/watch?v=KiA2okjlkbE · The Kansas City Star: kansascity.com/news/local/article217177885.html · KSHB 41: kshb.com/news/local-news/ku-engineering-students-create-device-to-help-change-the-tune-for-young-teen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pedal device</t>
   </si>
   <si>
-    <t xml:space="preserve">Have CAD (renders in portfolio)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio p.6: renders, photos, news still</t>
+    <t xml:space="preserve">Yes (reconstruction from photos, GLB; exploded build)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3D model of the device live in Lens v2 (six part zones) + tile still + About hover turntable; 5 photos from the portfolio (device, with the pianist, in CAD, two CAD renders) in the photo viewer; video and two news links</t>
   </si>
   <si>
     <t xml:space="preserve">News links: dummy placeholders until you send real ones.</t>
@@ -2225,6 +2228,18 @@
   </si>
   <si>
     <t xml:space="preserve">E1, 3D model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedal photos: the ones you sent are thumbnails; the portfolio copies used are still small (largest 558 px). Larger originals? Also: the photo with the pianist shows her (a teen at the time) and her home; OK on the public site?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U2, photos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photos for other projects: send them and they go in the same photo viewer. The portfolio already has Formula SAE photos (car, battery box, motor controller). Add those?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U1, photos</t>
   </si>
 </sst>
 </file>
@@ -4578,7 +4593,9 @@
       <c r="J27" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="K27" s="17"/>
+      <c r="K27" s="17" t="s">
+        <v>251</v>
+      </c>
       <c r="L27" s="18" t="s">
         <v>59</v>
       </c>
@@ -4595,16 +4612,16 @@
         <v>60</v>
       </c>
       <c r="S27" s="17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="T27" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="U27" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="V27" s="21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="W27" s="17" t="s">
         <v>156</v>
@@ -4612,7 +4629,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -4639,28 +4656,28 @@
     </row>
     <row r="29" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K29" s="17"/>
       <c r="L29" s="20"/>
@@ -4677,45 +4694,45 @@
         <v>60</v>
       </c>
       <c r="S29" s="17" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="T29" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="U29" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="V29" s="21" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W29" s="17" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K30" s="17"/>
       <c r="L30" s="20"/>
@@ -4732,45 +4749,45 @@
         <v>60</v>
       </c>
       <c r="S30" s="17" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="T30" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="U30" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="V30" s="21" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W30" s="17" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
       <c r="H31" s="17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K31" s="17"/>
       <c r="L31" s="20"/>
@@ -4791,24 +4808,24 @@
         <v>60</v>
       </c>
       <c r="S31" s="17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="T31" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="U31" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="V31" s="21" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="W31" s="17" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -4835,35 +4852,35 @@
     </row>
     <row r="33" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E33" s="17"/>
       <c r="F33" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K33" s="26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L33" s="20"/>
       <c r="M33" s="20"/>
@@ -4877,52 +4894,52 @@
         <v>60</v>
       </c>
       <c r="S33" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="T33" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="U33" s="17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="V33" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="W33" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E34" s="17"/>
       <c r="F34" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K34" s="26" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L34" s="20"/>
       <c r="M34" s="19" t="s">
@@ -4938,52 +4955,52 @@
         <v>60</v>
       </c>
       <c r="S34" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="T34" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="U34" s="17" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="V34" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="W34" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E35" s="17"/>
       <c r="F35" s="15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K35" s="26" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L35" s="20"/>
       <c r="M35" s="19" t="s">
@@ -5001,52 +5018,52 @@
         <v>60</v>
       </c>
       <c r="S35" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="T35" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="U35" s="17" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="V35" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="W35" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E36" s="17"/>
       <c r="F36" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K36" s="26" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L36" s="18" t="s">
         <v>59</v>
@@ -5064,52 +5081,52 @@
         <v>62</v>
       </c>
       <c r="S36" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="T36" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="U36" s="17" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="V36" s="21" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="W36" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E37" s="17"/>
       <c r="F37" s="15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K37" s="26" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L37" s="20"/>
       <c r="M37" s="20"/>
@@ -5125,52 +5142,52 @@
         <v>60</v>
       </c>
       <c r="S37" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="T37" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="U37" s="17" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="V37" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="W37" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E38" s="17"/>
       <c r="F38" s="15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I38" s="17" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K38" s="26" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L38" s="20"/>
       <c r="M38" s="20"/>
@@ -5184,49 +5201,49 @@
         <v>62</v>
       </c>
       <c r="S38" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="T38" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="U38" s="17" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="V38" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="W38" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E39" s="17"/>
       <c r="F39" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="20"/>
@@ -5241,49 +5258,49 @@
         <v>62</v>
       </c>
       <c r="S39" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="T39" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="U39" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="V39" s="21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="W39" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E40" s="17"/>
       <c r="F40" s="15" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K40" s="17"/>
       <c r="L40" s="20"/>
@@ -5300,49 +5317,49 @@
         <v>62</v>
       </c>
       <c r="S40" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="T40" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="U40" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="V40" s="21" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="W40" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E41" s="17"/>
       <c r="F41" s="15" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K41" s="17"/>
       <c r="L41" s="20"/>
@@ -5357,49 +5374,49 @@
         <v>62</v>
       </c>
       <c r="S41" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="T41" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="U41" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="V41" s="21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="W41" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E42" s="17"/>
       <c r="F42" s="15" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K42" s="17"/>
       <c r="L42" s="20"/>
@@ -5416,52 +5433,52 @@
         <v>62</v>
       </c>
       <c r="S42" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="T42" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="U42" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="V42" s="21" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="W42" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K43" s="26" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L43" s="20"/>
       <c r="M43" s="19" t="s">
@@ -5477,52 +5494,52 @@
         <v>60</v>
       </c>
       <c r="S43" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="T43" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="U43" s="17" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="V43" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="W43" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E44" s="17"/>
       <c r="F44" s="15" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J44" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K44" s="26" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L44" s="20"/>
       <c r="M44" s="20"/>
@@ -5536,49 +5553,49 @@
         <v>62</v>
       </c>
       <c r="S44" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="T44" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="U44" s="17" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="V44" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="W44" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="15" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I45" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K45" s="17"/>
       <c r="L45" s="20"/>
@@ -5595,39 +5612,39 @@
         <v>60</v>
       </c>
       <c r="S45" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="T45" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="U45" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="V45" s="21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="W45" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E46" s="17"/>
       <c r="F46" s="15"/>
       <c r="G46" s="15"/>
       <c r="H46" s="17" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I46" s="17"/>
       <c r="J46" s="17"/>
@@ -5644,24 +5661,24 @@
         <v>60</v>
       </c>
       <c r="S46" s="17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T46" s="17" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="U46" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="V46" s="21" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="W46" s="17" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -5688,19 +5705,19 @@
     </row>
     <row r="48" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F48" s="15" t="n">
         <v>2026</v>
@@ -5709,11 +5726,11 @@
         <v>2026</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I48" s="17"/>
       <c r="J48" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K48" s="17"/>
       <c r="L48" s="20"/>
@@ -5730,36 +5747,36 @@
         <v>60</v>
       </c>
       <c r="S48" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="T48" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U48" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="V48" s="21" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="W48" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F49" s="15" t="n">
         <v>2026</v>
@@ -5768,11 +5785,11 @@
         <v>2026</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I49" s="17"/>
       <c r="J49" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K49" s="17"/>
       <c r="L49" s="20"/>
@@ -5789,36 +5806,36 @@
         <v>60</v>
       </c>
       <c r="S49" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="T49" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U49" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="V49" s="21" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="W49" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F50" s="15" t="s">
         <v>53</v>
@@ -5827,11 +5844,11 @@
         <v>53</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I50" s="17"/>
       <c r="J50" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K50" s="17"/>
       <c r="L50" s="20"/>
@@ -5848,36 +5865,36 @@
         <v>60</v>
       </c>
       <c r="S50" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="T50" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U50" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="V50" s="21" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="W50" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F51" s="15" t="s">
         <v>53</v>
@@ -5886,11 +5903,11 @@
         <v>53</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="I51" s="17"/>
       <c r="J51" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="20"/>
@@ -5907,36 +5924,36 @@
         <v>60</v>
       </c>
       <c r="S51" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="T51" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U51" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="V51" s="21" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="W51" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F52" s="15" t="s">
         <v>53</v>
@@ -5945,11 +5962,11 @@
         <v>53</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="I52" s="17"/>
       <c r="J52" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K52" s="17"/>
       <c r="L52" s="18"/>
@@ -5966,36 +5983,36 @@
         <v>60</v>
       </c>
       <c r="S52" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="T52" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U52" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="V52" s="21" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="W52" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F53" s="15" t="n">
         <v>2024</v>
@@ -6004,11 +6021,11 @@
         <v>2024</v>
       </c>
       <c r="H53" s="17" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="I53" s="17"/>
       <c r="J53" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K53" s="17"/>
       <c r="L53" s="20"/>
@@ -6025,36 +6042,36 @@
         <v>60</v>
       </c>
       <c r="S53" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="T53" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U53" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="V53" s="21" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="W53" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F54" s="15" t="n">
         <v>2023</v>
@@ -6063,11 +6080,11 @@
         <v>2023</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I54" s="17"/>
       <c r="J54" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K54" s="17"/>
       <c r="L54" s="20"/>
@@ -6084,36 +6101,36 @@
         <v>60</v>
       </c>
       <c r="S54" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="T54" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U54" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="V54" s="21" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="W54" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F55" s="15" t="n">
         <v>2023</v>
@@ -6122,11 +6139,11 @@
         <v>2023</v>
       </c>
       <c r="H55" s="17" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="I55" s="17"/>
       <c r="J55" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K55" s="17"/>
       <c r="L55" s="20"/>
@@ -6143,36 +6160,36 @@
         <v>60</v>
       </c>
       <c r="S55" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="T55" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U55" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="V55" s="21" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="W55" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F56" s="15" t="n">
         <v>2022</v>
@@ -6181,11 +6198,11 @@
         <v>2022</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I56" s="17"/>
       <c r="J56" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K56" s="17"/>
       <c r="L56" s="20"/>
@@ -6202,36 +6219,36 @@
         <v>60</v>
       </c>
       <c r="S56" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="T56" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U56" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="V56" s="21" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="W56" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="15" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F57" s="15" t="n">
         <v>2021</v>
@@ -6240,11 +6257,11 @@
         <v>2021</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I57" s="17"/>
       <c r="J57" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K57" s="17"/>
       <c r="L57" s="20"/>
@@ -6261,36 +6278,36 @@
         <v>60</v>
       </c>
       <c r="S57" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="T57" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U57" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="V57" s="21" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="W57" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="15" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F58" s="15" t="n">
         <v>2022</v>
@@ -6299,11 +6316,11 @@
         <v>2022</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I58" s="17"/>
       <c r="J58" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K58" s="17"/>
       <c r="L58" s="20"/>
@@ -6320,22 +6337,22 @@
         <v>60</v>
       </c>
       <c r="S58" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="T58" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U58" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="V58" s="21"/>
       <c r="W58" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -6362,24 +6379,24 @@
     </row>
     <row r="60" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C60" s="17" t="s">
+        <v>431</v>
+      </c>
+      <c r="D60" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="E60" s="17" t="s">
         <v>430</v>
-      </c>
-      <c r="D60" s="17" t="s">
-        <v>431</v>
-      </c>
-      <c r="E60" s="17" t="s">
-        <v>429</v>
       </c>
       <c r="F60" s="15"/>
       <c r="G60" s="15"/>
       <c r="H60" s="17" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I60" s="17"/>
       <c r="J60" s="17"/>
@@ -6398,31 +6415,31 @@
         <v>60</v>
       </c>
       <c r="S60" s="17" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="T60" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U60" s="17"/>
       <c r="V60" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="W60" s="17" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="15" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B61" s="16" t="s">
         <v>107</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E61" s="17" t="s">
         <v>107</v>
@@ -6434,7 +6451,7 @@
         <v>90</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="I61" s="17"/>
       <c r="J61" s="17"/>
@@ -6453,31 +6470,31 @@
         <v>60</v>
       </c>
       <c r="S61" s="17" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="T61" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U61" s="17"/>
       <c r="V61" s="21" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="W61" s="17" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="15" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B62" s="16" t="s">
         <v>89</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E62" s="17" t="s">
         <v>89</v>
@@ -6489,7 +6506,7 @@
         <v>81</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="I62" s="17"/>
       <c r="J62" s="17"/>
@@ -6508,31 +6525,31 @@
         <v>60</v>
       </c>
       <c r="S62" s="17" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="T62" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U62" s="17"/>
       <c r="V62" s="21" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="W62" s="17" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B63" s="16" t="s">
         <v>80</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E63" s="17" t="s">
         <v>80</v>
@@ -6544,7 +6561,7 @@
         <v>70</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="I63" s="17"/>
       <c r="J63" s="17"/>
@@ -6563,31 +6580,31 @@
         <v>60</v>
       </c>
       <c r="S63" s="17" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="T63" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U63" s="17"/>
       <c r="V63" s="21" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="W63" s="17" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B64" s="16" t="s">
         <v>69</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E64" s="17" t="s">
         <v>69</v>
@@ -6599,7 +6616,7 @@
         <v>71</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="I64" s="17"/>
       <c r="J64" s="17"/>
@@ -6618,31 +6635,31 @@
         <v>60</v>
       </c>
       <c r="S64" s="17" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="T64" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U64" s="17"/>
       <c r="V64" s="21" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="W64" s="17" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="15" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B65" s="16" t="s">
         <v>52</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E65" s="17" t="s">
         <v>52</v>
@@ -6654,7 +6671,7 @@
         <v>54</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I65" s="17"/>
       <c r="J65" s="17"/>
@@ -6673,17 +6690,17 @@
         <v>60</v>
       </c>
       <c r="S65" s="17" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="T65" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U65" s="17"/>
       <c r="V65" s="21" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="W65" s="17" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
   </sheetData>
@@ -6739,28 +6756,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6790,7 +6807,7 @@
         <v>Add</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6820,7 +6837,7 @@
         <v>OK</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6850,7 +6867,7 @@
         <v>OK</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6880,7 +6897,7 @@
         <v>OK</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6910,7 +6927,7 @@
         <v>OK</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6940,7 +6957,7 @@
         <v>Trim</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6955,7 +6972,7 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">COUNTA(Artifacts!$C$2:$C$124)</f>
@@ -6970,7 +6987,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>
@@ -7006,52 +7023,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J1" s="27" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D2" s="17"/>
       <c r="E2" s="17" t="s">
         <v>108</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G2" s="17" t="n">
         <v>42.08</v>
@@ -7063,7 +7080,7 @@
         <v>60</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7071,10 +7088,10 @@
         <v>107</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>108</v>
@@ -7095,7 +7112,7 @@
         <v>60</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7103,10 +7120,10 @@
         <v>89</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D4" s="17" t="s">
         <v>90</v>
@@ -7115,7 +7132,7 @@
         <v>81</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G4" s="17" t="n">
         <v>41.88</v>
@@ -7127,18 +7144,18 @@
         <v>60</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>81</v>
@@ -7147,7 +7164,7 @@
         <v>70</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>45.46</v>
@@ -7159,7 +7176,7 @@
         <v>60</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7167,10 +7184,10 @@
         <v>69</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>70</v>
@@ -7179,7 +7196,7 @@
         <v>53</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G6" s="17" t="n">
         <v>32.78</v>
@@ -7191,7 +7208,7 @@
         <v>60</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7199,10 +7216,10 @@
         <v>52</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>53</v>
@@ -7211,7 +7228,7 @@
         <v>54</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>30.27</v>
@@ -7223,7 +7240,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7231,15 +7248,15 @@
         <v>148</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="17" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>29.76</v>
@@ -7257,15 +7274,15 @@
         <v>159</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="17" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>33.43</v>
@@ -7283,15 +7300,15 @@
         <v>225</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="17" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G10" s="17" t="n">
         <v>32.76</v>
@@ -7306,13 +7323,13 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>90</v>
@@ -7321,7 +7338,7 @@
         <v>90</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>40.81</v>
@@ -7336,22 +7353,22 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G12" s="17" t="n">
         <v>39.57</v>
@@ -7366,22 +7383,22 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>38.72</v>
@@ -7396,13 +7413,13 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>53</v>
@@ -7411,7 +7428,7 @@
         <v>53</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
@@ -7419,18 +7436,18 @@
         <v>60</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>53</v>
@@ -7439,7 +7456,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G15" s="17"/>
       <c r="H15" s="17"/>
@@ -7447,18 +7464,18 @@
         <v>60</v>
       </c>
       <c r="J15" s="21" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>53</v>
@@ -7467,7 +7484,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
@@ -7475,18 +7492,18 @@
         <v>60</v>
       </c>
       <c r="J16" s="21" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>71</v>
@@ -7495,7 +7512,7 @@
         <v>71</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>-22.97</v>
@@ -7507,27 +7524,27 @@
         <v>60</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
@@ -7535,27 +7552,27 @@
         <v>60</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>26.71</v>
@@ -7570,13 +7587,13 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D20" s="17" t="s">
         <v>202</v>
@@ -7585,7 +7602,7 @@
         <v>202</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G20" s="17" t="n">
         <v>19.43</v>
@@ -7600,13 +7617,13 @@
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D21" s="17" t="s">
         <v>70</v>
@@ -7615,7 +7632,7 @@
         <v>70</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>41.89</v>
@@ -7627,18 +7644,18 @@
         <v>60</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D22" s="17" t="s">
         <v>202</v>
@@ -7647,7 +7664,7 @@
         <v>202</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
@@ -7658,12 +7675,12 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
@@ -7699,33 +7716,33 @@
         <v>24</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F1" s="27" t="s">
         <v>41</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D2" s="32" t="n">
         <v>2026</v>
@@ -7740,13 +7757,13 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="32" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D3" s="32" t="n">
         <v>2026</v>
@@ -7761,13 +7778,13 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>53</v>
@@ -7782,13 +7799,13 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>53</v>
@@ -7803,13 +7820,13 @@
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D6" s="32" t="s">
         <v>53</v>
@@ -7824,13 +7841,13 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>2024</v>
@@ -7845,13 +7862,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>2023</v>
@@ -7866,13 +7883,13 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>2023</v>
@@ -7887,13 +7904,13 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D10" s="32" t="n">
         <v>2022</v>
@@ -7908,13 +7925,13 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D11" s="32" t="n">
         <v>2021</v>
@@ -7929,13 +7946,13 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D12" s="32" t="n">
         <v>2022</v>
@@ -7950,7 +7967,7 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D13" s="28" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E13" s="28" t="n">
         <f aca="false">SUM(E2:E12)</f>
@@ -7959,7 +7976,7 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D14" s="28" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E14" s="28" t="n">
         <f aca="false">COUNTIF(F2:F12,"Yes")</f>
@@ -7968,12 +7985,12 @@
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
   </sheetData>
@@ -8003,19 +8020,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8023,13 +8040,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E2" s="33"/>
     </row>
@@ -8038,13 +8055,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="33" t="s">
+        <v>535</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>533</v>
+      </c>
+      <c r="D3" s="33" t="s">
         <v>534</v>
-      </c>
-      <c r="C3" s="33" t="s">
-        <v>532</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>533</v>
       </c>
       <c r="E3" s="33"/>
     </row>
@@ -8053,13 +8070,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E4" s="33"/>
     </row>
@@ -8068,13 +8085,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E5" s="33"/>
     </row>
@@ -8083,13 +8100,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="33" t="s">
+        <v>538</v>
+      </c>
+      <c r="C6" s="33" t="s">
         <v>537</v>
       </c>
-      <c r="C6" s="33" t="s">
-        <v>536</v>
-      </c>
       <c r="D6" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E6" s="33"/>
     </row>
@@ -8098,16 +8115,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8115,16 +8132,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="33" t="s">
+        <v>542</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>537</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>540</v>
+      </c>
+      <c r="E8" s="33" t="s">
         <v>541</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>536</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>539</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8132,16 +8149,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8149,16 +8166,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8166,13 +8183,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E11" s="33"/>
     </row>
@@ -8181,13 +8198,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E12" s="33"/>
     </row>
@@ -8196,13 +8213,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="33" t="s">
+        <v>548</v>
+      </c>
+      <c r="C13" s="33" t="s">
         <v>547</v>
       </c>
-      <c r="C13" s="33" t="s">
-        <v>546</v>
-      </c>
       <c r="D13" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E13" s="33"/>
     </row>
@@ -8211,13 +8228,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E14" s="33"/>
     </row>
@@ -8226,13 +8243,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E15" s="33"/>
     </row>
@@ -8241,16 +8258,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8258,16 +8275,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8275,16 +8292,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8292,16 +8309,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8309,16 +8326,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8326,13 +8343,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E21" s="33"/>
     </row>
@@ -8341,16 +8358,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8358,16 +8375,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8375,16 +8392,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8392,13 +8409,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E25" s="33"/>
     </row>
@@ -8407,13 +8424,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E26" s="33"/>
     </row>
@@ -8422,13 +8439,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E27" s="33"/>
     </row>
@@ -8437,13 +8454,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E28" s="33"/>
     </row>
@@ -8452,13 +8469,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E29" s="33"/>
     </row>
@@ -8467,13 +8484,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E30" s="33"/>
     </row>
@@ -8482,13 +8499,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E31" s="33"/>
     </row>
@@ -8497,13 +8514,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E32" s="33"/>
     </row>
@@ -8512,13 +8529,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E33" s="33"/>
     </row>
@@ -8527,13 +8544,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E34" s="33"/>
     </row>
@@ -8542,19 +8559,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E35" s="33"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="28" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C37" s="28" t="n">
         <f aca="false">COUNTA(B2:B35)</f>
@@ -8563,7 +8580,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C38" s="1" t="n">
         <f aca="false">COUNTIF(D2:D35,"Shaded")</f>
@@ -8572,7 +8589,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C39" s="1" t="n">
         <f aca="false">COUNTIF(D2:D35,"Dot")</f>
@@ -8581,7 +8598,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
   </sheetData>
@@ -8612,16 +8629,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E1" s="27" t="s">
         <v>46</v>
@@ -8629,98 +8646,98 @@
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>60</v>
@@ -8731,13 +8748,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>60</v>
@@ -8748,130 +8765,130 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D13" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>60</v>
@@ -8882,13 +8899,13 @@
     </row>
     <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>60</v>
@@ -8899,13 +8916,13 @@
     </row>
     <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>60</v>
@@ -8916,13 +8933,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>60</v>
@@ -8933,140 +8950,140 @@
     </row>
     <row r="20" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D22" s="21"/>
       <c r="E22" s="17" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="17" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D24" s="21"/>
       <c r="E24" s="17" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D25" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D28" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D29" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
   </sheetData>
@@ -9085,7 +9102,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
@@ -9096,16 +9113,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9113,10 +9130,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>60</v>
@@ -9127,13 +9144,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9141,13 +9158,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9155,13 +9172,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9169,13 +9186,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9183,13 +9200,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>218</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9197,13 +9214,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9211,13 +9228,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>186</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9225,13 +9242,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9239,13 +9256,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9253,13 +9270,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>245</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9267,13 +9284,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9281,13 +9298,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9295,13 +9312,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9309,13 +9326,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9323,13 +9340,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9337,13 +9354,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9351,13 +9368,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9365,13 +9382,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9379,13 +9396,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9393,13 +9410,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9407,10 +9424,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D23" s="21"/>
     </row>
@@ -9419,7 +9436,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>35</v>
@@ -9431,13 +9448,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9445,10 +9462,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D26" s="21"/>
     </row>
@@ -9457,13 +9474,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9471,10 +9488,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D28" s="21"/>
     </row>
@@ -9483,10 +9500,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D29" s="21"/>
     </row>
@@ -9495,10 +9512,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D30" s="21"/>
     </row>
@@ -9507,10 +9524,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D31" s="21"/>
     </row>
@@ -9519,10 +9536,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D32" s="21"/>
     </row>
@@ -9531,12 +9548,36 @@
         <v>32</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D33" s="21"/>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>720</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>721</v>
+      </c>
+      <c r="D34" s="21"/>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>722</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>723</v>
+      </c>
+      <c r="D35" s="21"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="728">
   <si>
     <t xml:space="preserve">Site artifacts: mapping workbook</t>
   </si>
@@ -565,7 +565,7 @@
     <t xml:space="preserve">Have vendor render (portfolio)</t>
   </si>
   <si>
-    <t xml:space="preserve">Portfolio p.4: render + photo</t>
+    <t xml:space="preserve">Cover picture: render of the robot cell (portfolio p.4); photo viewer: the robot lifting bags (portfolio p.4)</t>
   </si>
   <si>
     <t xml:space="preserve">Dates: placeholder for now.</t>
@@ -796,10 +796,13 @@
     <t xml:space="preserve">SolidWorks, MATLAB, FEA, 3D printing, CNC, laser, water jet</t>
   </si>
   <si>
+    <t xml:space="preserve">Video: youtube.com/watch?v=QBBdbAZleAo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Racecar</t>
   </si>
   <si>
-    <t xml:space="preserve">Portfolio p.6: car render, controller and PCB photos</t>
+    <t xml:space="preserve">Cover picture: Grant's render of the car; photo viewer: the nose in the rain (portfolio copy); video link</t>
   </si>
   <si>
     <t xml:space="preserve">CAD file? Race results?</t>
@@ -2240,6 +2243,15 @@
   </si>
   <si>
     <t xml:space="preserve">U1, photos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Racecar: cover is the render, the rain photo is in the photo viewer, plus the video link.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The portfolio has more MAPEI images: the Houston silo tower and plant interior photos, tower CAD, elevation, P&amp;ID, the static mixer (photo and drawing) and the Houston building. Add them to the dry mix, static mixing and site development photo viewers? Larger originals of the palletizer images (345 px) would also look sharper.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E3, E4, E5, E6, photos</t>
   </si>
 </sst>
 </file>
@@ -4530,7 +4542,9 @@
       <c r="J26" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="K26" s="17"/>
+      <c r="K26" s="17" t="s">
+        <v>242</v>
+      </c>
       <c r="L26" s="18" t="s">
         <v>59</v>
       </c>
@@ -4547,16 +4561,16 @@
         <v>60</v>
       </c>
       <c r="S26" s="17" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="T26" s="17" t="s">
         <v>184</v>
       </c>
       <c r="U26" s="17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="V26" s="21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="W26" s="17" t="s">
         <v>156</v>
@@ -4564,16 +4578,16 @@
     </row>
     <row r="27" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>237</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>107</v>
@@ -4585,16 +4599,16 @@
         <v>238</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K27" s="17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L27" s="18" t="s">
         <v>59</v>
@@ -4612,16 +4626,16 @@
         <v>60</v>
       </c>
       <c r="S27" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="T27" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="U27" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="V27" s="21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="W27" s="17" t="s">
         <v>156</v>
@@ -4629,7 +4643,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -4656,28 +4670,28 @@
     </row>
     <row r="29" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K29" s="17"/>
       <c r="L29" s="20"/>
@@ -4694,45 +4708,45 @@
         <v>60</v>
       </c>
       <c r="S29" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="T29" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="U29" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="V29" s="21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W29" s="17" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="17" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K30" s="17"/>
       <c r="L30" s="20"/>
@@ -4749,45 +4763,45 @@
         <v>60</v>
       </c>
       <c r="S30" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="T30" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="U30" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="V30" s="21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W30" s="17" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
       <c r="H31" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K31" s="17"/>
       <c r="L31" s="20"/>
@@ -4808,24 +4822,24 @@
         <v>60</v>
       </c>
       <c r="S31" s="17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T31" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U31" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="V31" s="21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="W31" s="17" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -4852,35 +4866,35 @@
     </row>
     <row r="33" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E33" s="17"/>
       <c r="F33" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K33" s="26" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L33" s="20"/>
       <c r="M33" s="20"/>
@@ -4894,52 +4908,52 @@
         <v>60</v>
       </c>
       <c r="S33" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="T33" s="17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="U33" s="17" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="V33" s="21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="W33" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E34" s="17"/>
       <c r="F34" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K34" s="26" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L34" s="20"/>
       <c r="M34" s="19" t="s">
@@ -4955,52 +4969,52 @@
         <v>60</v>
       </c>
       <c r="S34" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="T34" s="17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="U34" s="17" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="V34" s="21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="W34" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E35" s="17"/>
       <c r="F35" s="15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K35" s="26" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L35" s="20"/>
       <c r="M35" s="19" t="s">
@@ -5018,52 +5032,52 @@
         <v>60</v>
       </c>
       <c r="S35" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="T35" s="17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="U35" s="17" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="V35" s="21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="W35" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E36" s="17"/>
       <c r="F36" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K36" s="26" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L36" s="18" t="s">
         <v>59</v>
@@ -5081,52 +5095,52 @@
         <v>62</v>
       </c>
       <c r="S36" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="T36" s="17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="U36" s="17" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="V36" s="21" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="W36" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E37" s="17"/>
       <c r="F37" s="15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K37" s="26" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L37" s="20"/>
       <c r="M37" s="20"/>
@@ -5142,52 +5156,52 @@
         <v>60</v>
       </c>
       <c r="S37" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="T37" s="17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="U37" s="17" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="V37" s="21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="W37" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E38" s="17"/>
       <c r="F38" s="15" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I38" s="17" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K38" s="26" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L38" s="20"/>
       <c r="M38" s="20"/>
@@ -5201,49 +5215,49 @@
         <v>62</v>
       </c>
       <c r="S38" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="T38" s="17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="U38" s="17" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="V38" s="21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="W38" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E39" s="17"/>
       <c r="F39" s="15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="20"/>
@@ -5258,49 +5272,49 @@
         <v>62</v>
       </c>
       <c r="S39" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="T39" s="17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="U39" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="V39" s="21" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="W39" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E40" s="17"/>
       <c r="F40" s="15" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K40" s="17"/>
       <c r="L40" s="20"/>
@@ -5317,49 +5331,49 @@
         <v>62</v>
       </c>
       <c r="S40" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="T40" s="17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="U40" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="V40" s="21" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="W40" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E41" s="17"/>
       <c r="F41" s="15" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K41" s="17"/>
       <c r="L41" s="20"/>
@@ -5374,49 +5388,49 @@
         <v>62</v>
       </c>
       <c r="S41" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="T41" s="17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="U41" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="V41" s="21" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="W41" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E42" s="17"/>
       <c r="F42" s="15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K42" s="17"/>
       <c r="L42" s="20"/>
@@ -5433,52 +5447,52 @@
         <v>62</v>
       </c>
       <c r="S42" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="T42" s="17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="U42" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="V42" s="21" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="W42" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="15" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K43" s="26" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L43" s="20"/>
       <c r="M43" s="19" t="s">
@@ -5494,52 +5508,52 @@
         <v>60</v>
       </c>
       <c r="S43" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="T43" s="17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="U43" s="17" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="V43" s="21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="W43" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E44" s="17"/>
       <c r="F44" s="15" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J44" s="17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K44" s="26" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L44" s="20"/>
       <c r="M44" s="20"/>
@@ -5553,49 +5567,49 @@
         <v>62</v>
       </c>
       <c r="S44" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="T44" s="17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="U44" s="17" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="V44" s="21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="W44" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="15" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I45" s="17" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K45" s="17"/>
       <c r="L45" s="20"/>
@@ -5612,39 +5626,39 @@
         <v>60</v>
       </c>
       <c r="S45" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="T45" s="17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="U45" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="V45" s="21" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="W45" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E46" s="17"/>
       <c r="F46" s="15"/>
       <c r="G46" s="15"/>
       <c r="H46" s="17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I46" s="17"/>
       <c r="J46" s="17"/>
@@ -5661,24 +5675,24 @@
         <v>60</v>
       </c>
       <c r="S46" s="17" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="T46" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="U46" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="V46" s="21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="W46" s="17" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -5705,19 +5719,19 @@
     </row>
     <row r="48" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F48" s="15" t="n">
         <v>2026</v>
@@ -5726,11 +5740,11 @@
         <v>2026</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I48" s="17"/>
       <c r="J48" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K48" s="17"/>
       <c r="L48" s="20"/>
@@ -5747,36 +5761,36 @@
         <v>60</v>
       </c>
       <c r="S48" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="T48" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="U48" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="V48" s="21" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="W48" s="17" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F49" s="15" t="n">
         <v>2026</v>
@@ -5785,11 +5799,11 @@
         <v>2026</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I49" s="17"/>
       <c r="J49" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K49" s="17"/>
       <c r="L49" s="20"/>
@@ -5806,36 +5820,36 @@
         <v>60</v>
       </c>
       <c r="S49" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="T49" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="U49" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="V49" s="21" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="W49" s="17" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F50" s="15" t="s">
         <v>53</v>
@@ -5844,11 +5858,11 @@
         <v>53</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I50" s="17"/>
       <c r="J50" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K50" s="17"/>
       <c r="L50" s="20"/>
@@ -5865,36 +5879,36 @@
         <v>60</v>
       </c>
       <c r="S50" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="T50" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="U50" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="V50" s="21" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="W50" s="17" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F51" s="15" t="s">
         <v>53</v>
@@ -5903,11 +5917,11 @@
         <v>53</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="I51" s="17"/>
       <c r="J51" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="20"/>
@@ -5924,36 +5938,36 @@
         <v>60</v>
       </c>
       <c r="S51" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="T51" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="U51" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="V51" s="21" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="W51" s="17" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F52" s="15" t="s">
         <v>53</v>
@@ -5962,11 +5976,11 @@
         <v>53</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I52" s="17"/>
       <c r="J52" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K52" s="17"/>
       <c r="L52" s="18"/>
@@ -5983,36 +5997,36 @@
         <v>60</v>
       </c>
       <c r="S52" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="T52" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="U52" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="V52" s="21" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="W52" s="17" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F53" s="15" t="n">
         <v>2024</v>
@@ -6021,11 +6035,11 @@
         <v>2024</v>
       </c>
       <c r="H53" s="17" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I53" s="17"/>
       <c r="J53" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K53" s="17"/>
       <c r="L53" s="20"/>
@@ -6042,36 +6056,36 @@
         <v>60</v>
       </c>
       <c r="S53" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="T53" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="U53" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="V53" s="21" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="W53" s="17" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F54" s="15" t="n">
         <v>2023</v>
@@ -6080,11 +6094,11 @@
         <v>2023</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="I54" s="17"/>
       <c r="J54" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K54" s="17"/>
       <c r="L54" s="20"/>
@@ -6101,36 +6115,36 @@
         <v>60</v>
       </c>
       <c r="S54" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="T54" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="U54" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="V54" s="21" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="W54" s="17" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F55" s="15" t="n">
         <v>2023</v>
@@ -6139,11 +6153,11 @@
         <v>2023</v>
       </c>
       <c r="H55" s="17" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I55" s="17"/>
       <c r="J55" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K55" s="17"/>
       <c r="L55" s="20"/>
@@ -6160,36 +6174,36 @@
         <v>60</v>
       </c>
       <c r="S55" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="T55" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="U55" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="V55" s="21" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="W55" s="17" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F56" s="15" t="n">
         <v>2022</v>
@@ -6198,11 +6212,11 @@
         <v>2022</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I56" s="17"/>
       <c r="J56" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K56" s="17"/>
       <c r="L56" s="20"/>
@@ -6219,36 +6233,36 @@
         <v>60</v>
       </c>
       <c r="S56" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="T56" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="U56" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="V56" s="21" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="W56" s="17" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="15" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F57" s="15" t="n">
         <v>2021</v>
@@ -6257,11 +6271,11 @@
         <v>2021</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I57" s="17"/>
       <c r="J57" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K57" s="17"/>
       <c r="L57" s="20"/>
@@ -6278,36 +6292,36 @@
         <v>60</v>
       </c>
       <c r="S57" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="T57" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="U57" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="V57" s="21" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="W57" s="17" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="15" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F58" s="15" t="n">
         <v>2022</v>
@@ -6316,11 +6330,11 @@
         <v>2022</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I58" s="17"/>
       <c r="J58" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K58" s="17"/>
       <c r="L58" s="20"/>
@@ -6337,22 +6351,22 @@
         <v>60</v>
       </c>
       <c r="S58" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="T58" s="17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="U58" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="V58" s="21"/>
       <c r="W58" s="17" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -6379,24 +6393,24 @@
     </row>
     <row r="60" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C60" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="D60" s="17" t="s">
+        <v>433</v>
+      </c>
+      <c r="E60" s="17" t="s">
         <v>431</v>
-      </c>
-      <c r="D60" s="17" t="s">
-        <v>432</v>
-      </c>
-      <c r="E60" s="17" t="s">
-        <v>430</v>
       </c>
       <c r="F60" s="15"/>
       <c r="G60" s="15"/>
       <c r="H60" s="17" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I60" s="17"/>
       <c r="J60" s="17"/>
@@ -6415,31 +6429,31 @@
         <v>60</v>
       </c>
       <c r="S60" s="17" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="T60" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U60" s="17"/>
       <c r="V60" s="21" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="W60" s="17" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="15" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B61" s="16" t="s">
         <v>107</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E61" s="17" t="s">
         <v>107</v>
@@ -6451,7 +6465,7 @@
         <v>90</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="I61" s="17"/>
       <c r="J61" s="17"/>
@@ -6470,31 +6484,31 @@
         <v>60</v>
       </c>
       <c r="S61" s="17" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="T61" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U61" s="17"/>
       <c r="V61" s="21" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="W61" s="17" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="15" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B62" s="16" t="s">
         <v>89</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E62" s="17" t="s">
         <v>89</v>
@@ -6506,7 +6520,7 @@
         <v>81</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I62" s="17"/>
       <c r="J62" s="17"/>
@@ -6525,31 +6539,31 @@
         <v>60</v>
       </c>
       <c r="S62" s="17" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="T62" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U62" s="17"/>
       <c r="V62" s="21" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="W62" s="17" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B63" s="16" t="s">
         <v>80</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E63" s="17" t="s">
         <v>80</v>
@@ -6561,7 +6575,7 @@
         <v>70</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="I63" s="17"/>
       <c r="J63" s="17"/>
@@ -6580,31 +6594,31 @@
         <v>60</v>
       </c>
       <c r="S63" s="17" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="T63" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U63" s="17"/>
       <c r="V63" s="21" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="W63" s="17" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B64" s="16" t="s">
         <v>69</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E64" s="17" t="s">
         <v>69</v>
@@ -6616,7 +6630,7 @@
         <v>71</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I64" s="17"/>
       <c r="J64" s="17"/>
@@ -6635,31 +6649,31 @@
         <v>60</v>
       </c>
       <c r="S64" s="17" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="T64" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U64" s="17"/>
       <c r="V64" s="21" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="W64" s="17" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="15" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B65" s="16" t="s">
         <v>52</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E65" s="17" t="s">
         <v>52</v>
@@ -6671,7 +6685,7 @@
         <v>54</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="I65" s="17"/>
       <c r="J65" s="17"/>
@@ -6690,17 +6704,17 @@
         <v>60</v>
       </c>
       <c r="S65" s="17" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="T65" s="17" t="s">
         <v>62</v>
       </c>
       <c r="U65" s="17"/>
       <c r="V65" s="21" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="W65" s="17" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -6756,28 +6770,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6807,7 +6821,7 @@
         <v>Add</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6837,7 +6851,7 @@
         <v>OK</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6867,7 +6881,7 @@
         <v>OK</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6897,7 +6911,7 @@
         <v>OK</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6927,7 +6941,7 @@
         <v>OK</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6957,7 +6971,7 @@
         <v>Trim</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6972,7 +6986,7 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">COUNTA(Artifacts!$C$2:$C$124)</f>
@@ -6987,7 +7001,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -7023,52 +7037,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J1" s="27" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D2" s="17"/>
       <c r="E2" s="17" t="s">
         <v>108</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G2" s="17" t="n">
         <v>42.08</v>
@@ -7080,7 +7094,7 @@
         <v>60</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7088,10 +7102,10 @@
         <v>107</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>108</v>
@@ -7112,7 +7126,7 @@
         <v>60</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7120,10 +7134,10 @@
         <v>89</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D4" s="17" t="s">
         <v>90</v>
@@ -7132,7 +7146,7 @@
         <v>81</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G4" s="17" t="n">
         <v>41.88</v>
@@ -7144,18 +7158,18 @@
         <v>60</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>81</v>
@@ -7164,7 +7178,7 @@
         <v>70</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>45.46</v>
@@ -7176,7 +7190,7 @@
         <v>60</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7184,10 +7198,10 @@
         <v>69</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>70</v>
@@ -7196,7 +7210,7 @@
         <v>53</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G6" s="17" t="n">
         <v>32.78</v>
@@ -7208,7 +7222,7 @@
         <v>60</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7216,10 +7230,10 @@
         <v>52</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>53</v>
@@ -7228,7 +7242,7 @@
         <v>54</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>30.27</v>
@@ -7240,7 +7254,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7248,15 +7262,15 @@
         <v>148</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="17" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>29.76</v>
@@ -7274,15 +7288,15 @@
         <v>159</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="17" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>33.43</v>
@@ -7300,15 +7314,15 @@
         <v>225</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="17" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G10" s="17" t="n">
         <v>32.76</v>
@@ -7323,13 +7337,13 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>90</v>
@@ -7338,7 +7352,7 @@
         <v>90</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>40.81</v>
@@ -7353,22 +7367,22 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G12" s="17" t="n">
         <v>39.57</v>
@@ -7383,22 +7397,22 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>38.72</v>
@@ -7413,13 +7427,13 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>53</v>
@@ -7428,7 +7442,7 @@
         <v>53</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
@@ -7436,18 +7450,18 @@
         <v>60</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>53</v>
@@ -7456,7 +7470,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G15" s="17"/>
       <c r="H15" s="17"/>
@@ -7464,18 +7478,18 @@
         <v>60</v>
       </c>
       <c r="J15" s="21" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>53</v>
@@ -7484,7 +7498,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
@@ -7492,18 +7506,18 @@
         <v>60</v>
       </c>
       <c r="J16" s="21" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>71</v>
@@ -7512,7 +7526,7 @@
         <v>71</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>-22.97</v>
@@ -7524,27 +7538,27 @@
         <v>60</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
@@ -7552,27 +7566,27 @@
         <v>60</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>26.71</v>
@@ -7587,13 +7601,13 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D20" s="17" t="s">
         <v>202</v>
@@ -7602,7 +7616,7 @@
         <v>202</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G20" s="17" t="n">
         <v>19.43</v>
@@ -7617,13 +7631,13 @@
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D21" s="17" t="s">
         <v>70</v>
@@ -7632,7 +7646,7 @@
         <v>70</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>41.89</v>
@@ -7644,18 +7658,18 @@
         <v>60</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D22" s="17" t="s">
         <v>202</v>
@@ -7664,7 +7678,7 @@
         <v>202</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
@@ -7675,12 +7689,12 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -7716,33 +7730,33 @@
         <v>24</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F1" s="27" t="s">
         <v>41</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D2" s="32" t="n">
         <v>2026</v>
@@ -7757,13 +7771,13 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="32" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D3" s="32" t="n">
         <v>2026</v>
@@ -7778,13 +7792,13 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>53</v>
@@ -7799,13 +7813,13 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>53</v>
@@ -7820,13 +7834,13 @@
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D6" s="32" t="s">
         <v>53</v>
@@ -7841,13 +7855,13 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>2024</v>
@@ -7862,13 +7876,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>2023</v>
@@ -7883,13 +7897,13 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>2023</v>
@@ -7904,13 +7918,13 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D10" s="32" t="n">
         <v>2022</v>
@@ -7925,13 +7939,13 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D11" s="32" t="n">
         <v>2021</v>
@@ -7946,13 +7960,13 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D12" s="32" t="n">
         <v>2022</v>
@@ -7967,7 +7981,7 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D13" s="28" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E13" s="28" t="n">
         <f aca="false">SUM(E2:E12)</f>
@@ -7976,7 +7990,7 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D14" s="28" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E14" s="28" t="n">
         <f aca="false">COUNTIF(F2:F12,"Yes")</f>
@@ -7985,12 +7999,12 @@
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>
@@ -8020,19 +8034,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8040,13 +8054,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E2" s="33"/>
     </row>
@@ -8055,13 +8069,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="D3" s="33" t="s">
         <v>535</v>
-      </c>
-      <c r="C3" s="33" t="s">
-        <v>533</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>534</v>
       </c>
       <c r="E3" s="33"/>
     </row>
@@ -8070,13 +8084,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E4" s="33"/>
     </row>
@@ -8085,13 +8099,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E5" s="33"/>
     </row>
@@ -8100,13 +8114,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="33" t="s">
+        <v>539</v>
+      </c>
+      <c r="C6" s="33" t="s">
         <v>538</v>
       </c>
-      <c r="C6" s="33" t="s">
-        <v>537</v>
-      </c>
       <c r="D6" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E6" s="33"/>
     </row>
@@ -8115,16 +8129,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8132,16 +8146,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="33" t="s">
+        <v>543</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>538</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>541</v>
+      </c>
+      <c r="E8" s="33" t="s">
         <v>542</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>537</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>540</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8149,16 +8163,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8166,16 +8180,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8183,13 +8197,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E11" s="33"/>
     </row>
@@ -8198,13 +8212,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E12" s="33"/>
     </row>
@@ -8213,13 +8227,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="33" t="s">
+        <v>549</v>
+      </c>
+      <c r="C13" s="33" t="s">
         <v>548</v>
       </c>
-      <c r="C13" s="33" t="s">
-        <v>547</v>
-      </c>
       <c r="D13" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E13" s="33"/>
     </row>
@@ -8228,13 +8242,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E14" s="33"/>
     </row>
@@ -8243,13 +8257,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E15" s="33"/>
     </row>
@@ -8258,16 +8272,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8275,16 +8289,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8292,16 +8306,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8309,16 +8323,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8326,16 +8340,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8343,13 +8357,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E21" s="33"/>
     </row>
@@ -8358,16 +8372,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8375,16 +8389,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8392,16 +8406,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8409,13 +8423,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E25" s="33"/>
     </row>
@@ -8424,13 +8438,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E26" s="33"/>
     </row>
@@ -8439,13 +8453,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E27" s="33"/>
     </row>
@@ -8454,13 +8468,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E28" s="33"/>
     </row>
@@ -8469,13 +8483,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E29" s="33"/>
     </row>
@@ -8484,13 +8498,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E30" s="33"/>
     </row>
@@ -8499,13 +8513,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E31" s="33"/>
     </row>
@@ -8514,13 +8528,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E32" s="33"/>
     </row>
@@ -8529,13 +8543,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E33" s="33"/>
     </row>
@@ -8544,13 +8558,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E34" s="33"/>
     </row>
@@ -8559,19 +8573,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E35" s="33"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="28" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C37" s="28" t="n">
         <f aca="false">COUNTA(B2:B35)</f>
@@ -8580,7 +8594,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C38" s="1" t="n">
         <f aca="false">COUNTIF(D2:D35,"Shaded")</f>
@@ -8589,7 +8603,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C39" s="1" t="n">
         <f aca="false">COUNTIF(D2:D35,"Dot")</f>
@@ -8598,7 +8612,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
   </sheetData>
@@ -8629,16 +8643,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E1" s="27" t="s">
         <v>46</v>
@@ -8646,98 +8660,98 @@
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>60</v>
@@ -8748,13 +8762,13 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>60</v>
@@ -8765,130 +8779,130 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D13" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>60</v>
@@ -8899,13 +8913,13 @@
     </row>
     <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>60</v>
@@ -8916,13 +8930,13 @@
     </row>
     <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>60</v>
@@ -8933,13 +8947,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>60</v>
@@ -8950,140 +8964,140 @@
     </row>
     <row r="20" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D22" s="21"/>
       <c r="E22" s="17" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="17" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D24" s="21"/>
       <c r="E24" s="17" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D25" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D28" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D29" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
   </sheetData>
@@ -9102,7 +9116,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
@@ -9113,16 +9127,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9130,10 +9144,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>60</v>
@@ -9144,13 +9158,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9158,13 +9172,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9172,13 +9186,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9186,13 +9200,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9200,13 +9214,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>218</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9214,13 +9228,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9228,13 +9242,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>186</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9242,13 +9256,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9256,13 +9270,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9270,13 +9284,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9284,13 +9298,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9298,13 +9312,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9312,13 +9326,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9326,13 +9340,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9340,13 +9354,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9354,13 +9368,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9368,13 +9382,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9382,13 +9396,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9396,13 +9410,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9410,13 +9424,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9424,10 +9438,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D23" s="21"/>
     </row>
@@ -9436,7 +9450,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>35</v>
@@ -9448,13 +9462,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9462,10 +9476,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D26" s="21"/>
     </row>
@@ -9474,13 +9488,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9488,10 +9502,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D28" s="21"/>
     </row>
@@ -9500,10 +9514,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D29" s="21"/>
     </row>
@@ -9512,10 +9526,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D30" s="21"/>
     </row>
@@ -9524,10 +9538,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D31" s="21"/>
     </row>
@@ -9536,10 +9550,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D32" s="21"/>
     </row>
@@ -9548,10 +9562,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D33" s="21"/>
     </row>
@@ -9560,10 +9574,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D34" s="21"/>
     </row>
@@ -9572,12 +9586,26 @@
         <v>34</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>723</v>
-      </c>
-      <c r="D35" s="21"/>
+        <v>724</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>726</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>727</v>
+      </c>
+      <c r="D36" s="21"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="729">
   <si>
     <t xml:space="preserve">Site artifacts: mapping workbook</t>
   </si>
@@ -532,7 +532,7 @@
     <t xml:space="preserve">Yes (Grant's exterior model of MAPEI Houston, v12)</t>
   </si>
   <si>
-    <t xml:space="preserve">Portfolio p.4: elevation, P&amp;ID, 3D render, tower photo, interior photo. MAPEI Houston exterior model (GLB v12) live in Lens v2 (zones: silo &amp; mixing tower, production &amp; warehouse, offices, site), opens with the tower lit; tile still + About hover turntable</t>
+    <t xml:space="preserve">Portfolio p.4: elevation, P&amp;ID, 3D render, tower photo, interior photo. MAPEI Houston exterior model (GLB v12) live in Lens v2 (zones: silo &amp; mixing tower, production &amp; warehouse, offices, site), opens with the tower lit; tile still + About hover turntable; photo viewer: the Houston silo tower and the plant interior (portfolio p.4)</t>
   </si>
   <si>
     <t xml:space="preserve">Dates: placeholder for now (About shows it at ~March 2022).</t>
@@ -625,7 +625,7 @@
     <t xml:space="preserve">Have CAD (render in portfolio)</t>
   </si>
   <si>
-    <t xml:space="preserve">Portfolio p.5: drawing, 3D render, photo</t>
+    <t xml:space="preserve">Photo viewer: the static mixer as installed and its piping drawing (portfolio p.5). Picture still a placeholder.</t>
   </si>
   <si>
     <t xml:space="preserve">E7</t>
@@ -2252,6 +2252,9 @@
   </si>
   <si>
     <t xml:space="preserve">E3, E4, E5, E6, photos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes: dry mix plant (tower and interior photos) and static mixing (mixer photo and piping drawing). Site development stays as it is.</t>
   </si>
 </sst>
 </file>
@@ -9605,7 +9608,9 @@
       <c r="C36" s="17" t="s">
         <v>727</v>
       </c>
-      <c r="D36" s="21"/>
+      <c r="D36" s="21" t="s">
+        <v>728</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -565,7 +565,7 @@
     <t xml:space="preserve">Have vendor render (portfolio)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cover picture: render of the robot cell (portfolio p.4); photo viewer: the robot lifting bags (portfolio p.4)</t>
+    <t xml:space="preserve">Cover picture: render of the robot cell on white (sent by Grant), framed 3:2; photo viewer: the robot lifting bags (portfolio p.4)</t>
   </si>
   <si>
     <t xml:space="preserve">Dates: placeholder for now.</t>

--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -532,7 +532,7 @@
     <t xml:space="preserve">Yes (Grant's exterior model of MAPEI Houston, v12)</t>
   </si>
   <si>
-    <t xml:space="preserve">Portfolio p.4: elevation, P&amp;ID, 3D render, tower photo, interior photo. MAPEI Houston exterior model (GLB v12) live in Lens v2 (zones: silo &amp; mixing tower, production &amp; warehouse, offices, site), opens with the tower lit; tile still + About hover turntable; photo viewer: the Houston silo tower and the plant interior (portfolio p.4)</t>
+    <t xml:space="preserve">Portfolio p.4: elevation, P&amp;ID, 3D render, tower photo, interior photo. MAPEI Houston exterior model (GLB v12) live in Lens v2 (zones: silo &amp; mixing tower, production &amp; warehouse, offices, site), opens with the tower lit; tile still + About hover turntable; photo viewer: the Houston silo tower and plant interior photos, the tower in CAD (portfolio p.4) and the plant structure in CAD (sent by Grant)</t>
   </si>
   <si>
     <t xml:space="preserve">Dates: placeholder for now (About shows it at ~March 2022).</t>
@@ -625,7 +625,7 @@
     <t xml:space="preserve">Have CAD (render in portfolio)</t>
   </si>
   <si>
-    <t xml:space="preserve">Photo viewer: the static mixer as installed and its piping drawing (portfolio p.5). Picture still a placeholder.</t>
+    <t xml:space="preserve">Cover picture: CAD render of the mixing skid (portfolio p.5), framed 3:2; photo viewer: the static mixer as installed and its piping drawing (portfolio p.5)</t>
   </si>
   <si>
     <t xml:space="preserve">E7</t>

--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="730">
   <si>
     <t xml:space="preserve">Site artifacts: mapping workbook</t>
   </si>
@@ -2213,6 +2213,9 @@
   </si>
   <si>
     <t xml:space="preserve">E1, E2, 3D model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep plain blocks (no detailed layout on the public site).</t>
   </si>
   <si>
     <t xml:space="preserve">MPOC: where is the additive &amp; subtractive manufacturing lab? It is placed at the east end, behind the offices, as a guess.</t>
@@ -9534,17 +9537,19 @@
       <c r="C30" s="17" t="s">
         <v>714</v>
       </c>
-      <c r="D30" s="21"/>
+      <c r="D30" s="21" t="s">
+        <v>715</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D31" s="21"/>
     </row>
@@ -9553,10 +9558,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D32" s="21"/>
     </row>
@@ -9565,10 +9570,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D33" s="21"/>
     </row>
@@ -9577,10 +9582,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D34" s="21"/>
     </row>
@@ -9589,13 +9594,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9603,13 +9608,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
   </sheetData>

--- a/planning/site-artifacts.xlsx
+++ b/planning/site-artifacts.xlsx
@@ -469,10 +469,10 @@
     <t xml:space="preserve">Miniature diorama of the building</t>
   </si>
   <si>
-    <t xml:space="preserve">Yes (generic massing, real proportions)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enovis logo (in repo); MPOC model (block massing at real proportions, six zones + mezzanine, from the updated plan; no rooms) + tile still + About hover turntable, in Lens v2. MPOC, CPS and the AM lab are one plant.</t>
+    <t xml:space="preserve">Yes (Grant's concept model, geometry only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enovis logo (in repo); MPOC model from Grant's concept model (walls, doors, rooms, mezzanine, roof framing; no names or numbers), six zones, + tile still + About hover turntable, in Lens v2. MPOC, CPS and the AM lab are one plant.</t>
   </si>
   <si>
     <t xml:space="preserve">Public-safe photos or layouts? NDA limits?</t>
@@ -2215,7 +2215,7 @@
     <t xml:space="preserve">E1, E2, 3D model</t>
   </si>
   <si>
-    <t xml:space="preserve">Keep plain blocks (no detailed layout on the public site).</t>
+    <t xml:space="preserve">Changed: use Grant's concept model (the 'all layers on' file), geometry only, with no room names, numbers or drawing references. (Earlier: keep plain blocks.)</t>
   </si>
   <si>
     <t xml:space="preserve">MPOC: where is the additive &amp; subtractive manufacturing lab? It is placed at the east end, behind the offices, as a guess.</t>
